--- a/workspaces/btc_daily_14days/roc/roc_spread_5_14.xlsx
+++ b/workspaces/btc_daily_14days/roc/roc_spread_5_14.xlsx
@@ -575,46 +575,46 @@
         <v>19</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-10.38817516231524</v>
+        <v>-10.35538206353375</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-1.473842879328863</v>
+        <v>-1.468514263522103</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>8.662177597881083</v>
+        <v>8.635114842619764</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>8.794756409114896</v>
+        <v>8.766636631552799</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>8.257886435048825</v>
+        <v>8.231755068609239</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>3.288150024617231</v>
+        <v>3.277698110331684</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>8.474978085545516</v>
+        <v>8.448059742804013</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>2.736913048748612</v>
+        <v>2.728184278198718</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>13.22344155439263</v>
+        <v>13.18133340134025</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>22.9240939026991</v>
+        <v>22.85133080330164</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>22.72443552446873</v>
+        <v>22.6523253050962</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>12.20952892309069</v>
+        <v>12.17112523277407</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>11.79074854117342</v>
+        <v>11.75394807693578</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>12.04404968228488</v>
+        <v>12.00650021415196</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>32</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>3.756561679792867</v>
+        <v>3.744275824862484</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>17.77433504449284</v>
+        <v>17.71782433481525</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>17.38365081872706</v>
+        <v>17.32819633848015</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>30.02770278738809</v>
+        <v>29.93093817766721</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>13.8556327290388</v>
+        <v>13.81116801239699</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>20.41464957936969</v>
+        <v>20.34898303326034</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>20.33484505533304</v>
+        <v>20.26944301489474</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>26.13275279836329</v>
+        <v>26.04866750033863</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>35.47175013430221</v>
+        <v>35.35755501258436</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>34.62842217922757</v>
+        <v>34.51709718332141</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>28.16623011312886</v>
+        <v>28.07570798113063</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>18.80684039173619</v>
+        <v>18.74673367388115</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>21.52402092722492</v>
+        <v>21.45545169389005</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>24.91486633307903</v>
+        <v>24.8354475825754</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>30</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>24.17322834645366</v>
+        <v>24.09459693078909</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>9.230606010823095</v>
+        <v>9.200906072192716</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>18.84284340819511</v>
+        <v>18.78180376308399</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>15.64229108328686</v>
+        <v>15.59064385800175</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>11.77043185993863</v>
+        <v>11.73203663454018</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>5.396323124305916</v>
+        <v>5.378305361360496</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>11.98949761928844</v>
+        <v>11.95012613472529</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>24.88126894201694</v>
+        <v>24.79993937720744</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>24.82660952068789</v>
+        <v>24.74514289608944</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>23.98072755303831</v>
+        <v>23.90218368384976</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>17.09805183794072</v>
+        <v>17.0419947970164</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>20.47887737188094</v>
+        <v>20.41242391991719</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>23.40562699471457</v>
+        <v>23.32990118826259</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>23.66203411565918</v>
+        <v>23.58544758257692</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>34</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-5.434614790798214</v>
+        <v>-5.417753609636272</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-7.04795918528432</v>
+        <v>-7.024939025504231</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-10.38738772718187</v>
+        <v>-10.35388577664976</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-13.20280003877921</v>
+        <v>-13.16101318609343</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-4.912820256168047</v>
+        <v>-4.897312770887233</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-4.616150192040493</v>
+        <v>-4.601737332490515</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>7.080424853195446</v>
+        <v>7.056462662486233</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>3.668174694200857</v>
+        <v>3.654860497181971</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>12.44958396191873</v>
+        <v>12.40725445855707</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>8.652806186847272</v>
+        <v>8.623089911961955</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>11.39814249602034</v>
+        <v>11.35981073685296</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>5.536502456329927</v>
+        <v>5.51781115946369</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>5.11628600824281</v>
+        <v>5.099110976354048</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>5.368188349733181</v>
+        <v>5.35015346492834</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>39</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>16.73733091056042</v>
+        <v>16.68132983533917</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>12.56483026382558</v>
+        <v>12.52354836948661</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>14.73839636797044</v>
+        <v>14.68959581765345</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>9.740588783678909</v>
+        <v>9.707429301140714</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>11.77069986531248</v>
+        <v>11.73143362245114</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>12.07159646054194</v>
+        <v>12.03120135671512</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>11.99006911226642</v>
+        <v>11.9494593929203</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>11.5254079081941</v>
+        <v>11.48591550143569</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>11.46768034086904</v>
+        <v>11.42780696681226</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>8.048488432797157</v>
+        <v>8.020215885439413</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>12.98643156953001</v>
+        <v>12.94214754420879</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>18.16633394218545</v>
+        <v>18.10561363440436</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>22.89321008828498</v>
+        <v>22.81704704157884</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>12.85930910266538</v>
+        <v>12.81621681334579</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>41</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1.165098265155883</v>
+        <v>1.15988193554157</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-10.20517366411001</v>
+        <v>-10.17136384487406</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>4.038876839406392</v>
+        <v>4.024758102799943</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-3.152228715717285</v>
+        <v>-3.143070633122392</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-1.250544228997143</v>
+        <v>-1.247189929581104</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.9529214255714749</v>
+        <v>-0.9507082368839903</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-5.923298248337169</v>
+        <v>-5.904999553586734</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-3.949099138507357</v>
+        <v>-3.937793905689631</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-6.454777809869846</v>
+        <v>-6.43569733938218</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.02536261003693596</v>
+        <v>0.02326728995397787</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>7.156038208338295</v>
+        <v>7.130289942809569</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-5.037554202124376</v>
+        <v>-5.022134714816808</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1.879367695886188</v>
+        <v>1.871723609508415</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>7.024599404863181</v>
+        <v>7.000081728915752</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>60</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>2.506561679790032</v>
+        <v>2.496664299190073</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>17.56622144007817</v>
+        <v>17.50685425446502</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>13.8407897910834</v>
+        <v>13.79309865719463</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>10.63898347237977</v>
+        <v>10.60166922769356</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>11.77113000436756</v>
+        <v>11.73046580956992</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>7.065632521249299</v>
+        <v>7.040743659583796</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>11.99066351336673</v>
+        <v>11.94876592496512</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>18.20496786690028</v>
+        <v>18.14153077492495</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>11.46845157574779</v>
+        <v>11.42732494501299</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>10.61934906955814</v>
+        <v>10.58131486169313</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>12.08810924330248</v>
+        <v>12.0449775754106</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>13.79657028755695</v>
+        <v>13.74860096555138</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>13.3789228526824</v>
+        <v>13.33212653343315</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>11.96066313426142</v>
+        <v>11.91878091590873</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>56</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>2.863704536932886</v>
+        <v>2.852275968260031</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>11.96964361986503</v>
+        <v>11.92769285892891</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>9.791254305692334</v>
+        <v>9.756020017329917</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>11.71152693117104</v>
+        <v>11.66938150791652</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>7.600436003740185</v>
+        <v>7.572860644322688</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>6.112284801955994</v>
+        <v>6.089909534260485</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>11.3950736447857</v>
+        <v>11.35393823196329</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>3.774544782012093</v>
+        <v>3.758764167413055</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>5.504230867430671</v>
+        <v>5.482343840091254</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.716342583808526</v>
+        <v>-0.7165787950098803</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>8.030779824907171</v>
+        <v>8.000271639025144</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>8.066864586687913</v>
+        <v>8.037118885189273</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>4.064981042950045</v>
+        <v>4.048764541387861</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>2.52475143713302</v>
+        <v>2.514019011147639</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>67</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-1.747169663493558</v>
+        <v>-1.742841664021277</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.119281798053237</v>
+        <v>1.113911053292227</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2.218060313510613</v>
+        <v>2.20816053508868</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>2.349277921494505</v>
+        <v>2.338498675915645</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-4.165683187585145</v>
+        <v>-4.152998040870592</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-8.352527382626526</v>
+        <v>-8.325026364864314</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-5.449199738017541</v>
+        <v>-5.432753482415421</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-2.927567816636255</v>
+        <v>-2.920418027956138</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-4.484851055757908</v>
+        <v>-4.472507676465021</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.646238888753814</v>
+        <v>0.6412267386237787</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.551298914413785</v>
+        <v>-2.545787041951201</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>1.972894804392155</v>
+        <v>1.963489045257532</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>6.044151116671436</v>
+        <v>6.020471939296009</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>3.300743335395239</v>
+        <v>3.28694011988815</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>93</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>4.495808991617984</v>
+        <v>4.477921021294229</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>7.187417386615145</v>
+        <v>7.160029777742338</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>4.642833542925842</v>
+        <v>4.623793505937137</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.622443463001943</v>
+        <v>2.610207610208349</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.06889024190965642</v>
+        <v>-0.07034885135686153</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>3.459170273489136</v>
+        <v>3.445491858151598</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>4.452921848591032</v>
+        <v>4.434554139607293</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>6.141305539219744</v>
+        <v>6.116221372230314</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>3.926908947708299</v>
+        <v>3.909606291838578</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>4.153743525221167</v>
+        <v>4.135920910072791</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>2.871928471475989</v>
+        <v>2.858218903733274</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>5.064001412335045</v>
+        <v>5.0430856290807</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>7.880763393273249</v>
+        <v>7.849446273330479</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>2.737624360500178</v>
+        <v>2.725232528811958</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>135</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>2.321376494605005</v>
+        <v>2.31042548018231</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>5.155909221053221</v>
+        <v>5.1343045864649</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>8.46839727613559</v>
+        <v>8.433850082001726</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>5.635973433655224</v>
+        <v>5.611702690108288</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>7.323131168021881</v>
+        <v>7.294018746907341</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>7.623191134705934</v>
+        <v>7.593094322496434</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>6.057192375330303</v>
+        <v>6.031642746503046</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.880349468335787</v>
+        <v>1.869510566286806</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>2.562467642533818</v>
+        <v>2.549120458826671</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.259660725096587</v>
+        <v>-1.258466793356405</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.464788928869865</v>
+        <v>-1.463227047011706</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.430837610158648</v>
+        <v>-1.428907362810719</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.108856366156211</v>
+        <v>-1.108706679811213</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>2.858359037280536</v>
+        <v>2.84470684183465</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>128</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>3.756561679789847</v>
+        <v>3.739198779627415</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>2.927366629190573</v>
+        <v>2.912695318447753</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>2.533566769740773</v>
+        <v>2.519283607915582</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.883060158158798</v>
+        <v>1.871413608428483</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-2.566416470651767</v>
+        <v>-2.559533788298118</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.07814416507776656</v>
+        <v>0.07489169612351532</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.571251351564605</v>
+        <v>-1.569277843723903</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-5.170925129553304</v>
+        <v>-5.155322847162267</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-6.799463979431508</v>
+        <v>-6.777623666333554</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-6.087475755061455</v>
+        <v>-6.067503734771961</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-11.7791544689351</v>
+        <v>-11.73755164425155</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-10.18068416548606</v>
+        <v>-10.14473913389573</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-5.116239082125574</v>
+        <v>-5.10056830533221</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-3.298660187002056</v>
+        <v>-3.289552417424602</v>
       </c>
     </row>
     <row r="18">
@@ -1196,49 +1196,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.310909505876978</v>
+        <v>1.327466454995431</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.8440907649420311</v>
+        <v>-0.8428642009745602</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.6951533091771367</v>
+        <v>-0.6906430440779303</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.2759287545171176</v>
+        <v>-0.268704599681314</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>3.835992879753292</v>
+        <v>3.870102752800051</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.7647491241099047</v>
+        <v>-0.7645281341945989</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.395204694932879</v>
+        <v>-1.397849696524453</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.857629171432713</v>
+        <v>-1.864155163463074</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-3.006967738211948</v>
+        <v>-3.022432694046771</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.669814942817958</v>
+        <v>-1.676848011549971</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-3.506780369575402</v>
+        <v>-3.528391904945487</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-2.927911182431025</v>
+        <v>-2.945794556424119</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-4.984146507946988</v>
+        <v>-5.014625713503051</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-4.191774943353636</v>
+        <v>-4.216750219622398</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>197</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-2.239631213610998</v>
+        <v>-2.235158964434305</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.313233091612958</v>
+        <v>-1.312140450310295</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.847432662403818</v>
+        <v>1.835686657804551</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>4.517526094074086</v>
+        <v>4.496049307573159</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>3.978533017631015</v>
+        <v>3.9602014686687</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.737122695248104</v>
+        <v>1.727766041005864</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>3.178320825514227</v>
+        <v>3.162808012985522</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.8476557767955697</v>
+        <v>-0.8479798623054933</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.125576808434928</v>
+        <v>1.11838476970528</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.779100256211919</v>
+        <v>-2.771331631588339</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-3.494696041048208</v>
+        <v>-3.483459654436849</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-6.516308657921748</v>
+        <v>-6.493719042562304</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-4.392486534952589</v>
+        <v>-4.378762115845802</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-3.633649531787121</v>
+        <v>-3.622674244835764</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>305</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-3.313110451357517</v>
+        <v>-3.303380686018613</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.97422966438841</v>
+        <v>-1.970211670211192</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-4.338037606144169</v>
+        <v>-4.32653494682863</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-3.223240122253472</v>
+        <v>-3.216895329421725</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-4.746683742416515</v>
+        <v>-4.732551787158478</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-4.778823225636671</v>
+        <v>-4.763122504383013</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-4.536250084709259</v>
+        <v>-4.522929059556212</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-3.363776783585891</v>
+        <v>-3.353807326204439</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-4.74022762485118</v>
+        <v>-4.724631244080847</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-3.622713928374012</v>
+        <v>-3.610014664036889</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-3.172390207282383</v>
+        <v>-3.160369944162703</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-2.810873458082597</v>
+        <v>-2.799290127903909</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-2.573929590332249</v>
+        <v>-2.565111444326256</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.336167033186072</v>
+        <v>-1.332585204309844</v>
       </c>
     </row>
     <row r="21">
@@ -1352,49 +1352,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.684459253914014</v>
+        <v>1.687978960992709</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.7554154600178364</v>
+        <v>0.7578605573839567</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>2.121552926909679</v>
+        <v>2.126535122536161</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.1762900632589819</v>
+        <v>-0.1743105301752834</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.447677804369029</v>
+        <v>1.451204956014543</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>2.016279670000486</v>
+        <v>2.020068974405589</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.931217787303652</v>
+        <v>1.935478599009677</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>4.976891747358849</v>
+        <v>4.985293426612849</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>3.569052981970508</v>
+        <v>3.57513929721096</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>6.506323246398537</v>
+        <v>6.516287616921815</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>5.495061239902348</v>
+        <v>5.503122742413495</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>5.802659298044517</v>
+        <v>5.810816663090812</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>4.032207926967565</v>
+        <v>4.038490685093251</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>3.471331171144286</v>
+        <v>3.477046498564562</v>
       </c>
     </row>
     <row r="22">
@@ -1404,49 +1404,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.042250985117626</v>
+        <v>-1.042277915136246</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-2.917676840826068</v>
+        <v>-2.914981565651026</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-2.520988819190293</v>
+        <v>-2.519832577092373</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-2.654587929326937</v>
+        <v>-2.653161687561735</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-2.665304658910948</v>
+        <v>-2.663225451629415</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.6761275595018077</v>
+        <v>0.6736644912724614</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.4645042287757306</v>
+        <v>-0.4659177439342628</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.1257571618260158</v>
+        <v>0.1231638832648443</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2.444518402046612</v>
+        <v>2.438993884464956</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>2.12551193048126</v>
+        <v>2.120342140895126</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>3.245251766558106</v>
+        <v>3.239094394581315</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>4.869712763756439</v>
+        <v>4.861432257591112</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>2.068832896664794</v>
+        <v>2.064354486974942</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2.0556951198067</v>
+        <v>2.051056048183916</v>
       </c>
     </row>
     <row r="23">
@@ -1456,49 +1456,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2.268466441694791</v>
+        <v>2.260863723593715</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.1807023525401021</v>
+        <v>0.1784579826926134</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.0239288840386962</v>
+        <v>0.02019194043701589</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.036294173829987</v>
+        <v>-1.03743331018763</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.1461439603306829</v>
+        <v>-0.1481696566809205</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.039178213091262</v>
+        <v>-1.039674042532624</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.7593363394611785</v>
+        <v>-0.7611943352405959</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.03448262950671221</v>
+        <v>-0.03875998725458629</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1.336325202806599</v>
+        <v>1.32896283446776</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.7041938984569498</v>
+        <v>-0.7069929593668434</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.7628306645088259</v>
+        <v>0.7574709934828761</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.08218388863543424</v>
+        <v>0.07828283443252815</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1.574492778285041</v>
+        <v>1.567602648440143</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.8702847312967208</v>
+        <v>0.8646838594249857</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>344</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-2.202740645791373</v>
+        <v>-2.201482552390878</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-2.360825886662631</v>
+        <v>-2.3530764051226</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-3.627787616515008</v>
+        <v>-3.618387544469122</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.462650762977212</v>
+        <v>-1.463933387446772</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-3.163862675723891</v>
+        <v>-3.152496613712387</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.412932365915182</v>
+        <v>-1.412354133572336</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.6255730599316465</v>
+        <v>-0.6326730522139457</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.673496644898087</v>
+        <v>-1.678082783464085</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.733325142477462</v>
+        <v>-1.739718071870755</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.420277281110295</v>
+        <v>-1.425431381053961</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-3.375335672337272</v>
+        <v>-3.368492961598925</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-3.050422611762194</v>
+        <v>-3.04471356350691</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.8428343845549833</v>
+        <v>-0.8515679074577065</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.8718663508843534</v>
+        <v>0.8528894430405174</v>
       </c>
     </row>
     <row r="25">
@@ -1560,49 +1560,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.758144202562896</v>
+        <v>-1.758684924154245</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-2.266776639056545</v>
+        <v>-2.261911127864913</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-3.029292404476706</v>
+        <v>-3.024891913853608</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-5.472568683633952</v>
+        <v>-5.460994292189419</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-7.481578134000152</v>
+        <v>-7.460632545813155</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-4.610606784519852</v>
+        <v>-4.600311445421355</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-5.062987560615639</v>
+        <v>-5.053959476301081</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-4.969493320465865</v>
+        <v>-4.962329952211697</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.353468803992065</v>
+        <v>-1.358900353836908</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.094143644053091</v>
+        <v>-1.098584295326262</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.54744126633382</v>
+        <v>0.5398369857801697</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.953876148201104</v>
+        <v>0.9452647961017391</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.20175776614645</v>
+        <v>-0.2095564953049873</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-2.167802380446602</v>
+        <v>-2.17100998200025</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>200</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.493438320210011</v>
+        <v>-1.49774113180689</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.8949880668257748</v>
+        <v>0.8852895097938145</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.5001193602291849</v>
+        <v>0.4854976778002893</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.1303724928366847</v>
+        <v>0.1240561229524317</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>5.091951277764508</v>
+        <v>5.059261725128891</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>5.889393215480169</v>
+        <v>5.835598224267983</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>6.30465949820789</v>
+        <v>6.238620694133523</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>4.837476099426389</v>
+        <v>4.778201669647409</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.283648027471209</v>
+        <v>1.240617142108334</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>1.439176299361364</v>
+        <v>1.400700485925725</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.272349267602593</v>
+        <v>-1.284455324600302</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.273155772409666</v>
+        <v>0.2473934056611782</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-5.176550899074805</v>
+        <v>-5.161818319826118</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.396001211596229</v>
+        <v>-1.414552417424595</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>137</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2.251087227235281</v>
+        <v>2.20329859601501</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>1.369440621570334</v>
+        <v>1.348623648087028</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.215209106924064</v>
+        <v>-1.220077218763123</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2.564679062179785</v>
+        <v>2.527936408537236</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2.026257847107573</v>
+        <v>2.006982442373314</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.8638457702247351</v>
+        <v>0.8319132747088389</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>2.238966067550955</v>
+        <v>2.176816506405423</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.417998353128354</v>
+        <v>-0.4562593940349871</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.93313476950464</v>
+        <v>-1.967439675931878</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>1.611896342297882</v>
+        <v>1.547961129979761</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>1.410225390089288</v>
+        <v>1.361437170992673</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.7212447068447005</v>
+        <v>0.6748087924582435</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>1.773267306115763</v>
+        <v>1.721210739865718</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.9048235250637262</v>
+        <v>-0.9400998626800785</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>126</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-4.080739907511564</v>
+        <v>-4.068569687794167</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.1367579649203137</v>
+        <v>-0.1491732226185363</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>2.642976503086253</v>
+        <v>2.580491817960088</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-1.988675126210985</v>
+        <v>-1.983774366593217</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.6475068333200866</v>
+        <v>0.6357858499009907</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-3.023305197218235</v>
+        <v>-3.020038024139694</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-5.488991295442908</v>
+        <v>-5.480333286784862</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-5.162523900573632</v>
+        <v>-5.157378102974981</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-8.404124787377825</v>
+        <v>-8.368137831265358</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-5.277966484815487</v>
+        <v>-5.284061564768123</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-6.293383602037068</v>
+        <v>-6.263420990165784</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-3.856089607969238</v>
+        <v>-3.866555332720722</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-4.284468288071089</v>
+        <v>-4.283091984884017</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-4.825575518850201</v>
+        <v>-4.827250830123006</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>97</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-6.101685742890389</v>
+        <v>-6.044134379413784</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-2.55862018059694</v>
+        <v>-2.535064273685563</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-10.16998373255429</v>
+        <v>-10.03998010994135</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-12.10158627004989</v>
+        <v>-11.90778539955206</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-6.454440474812841</v>
+        <v>-6.343843707325668</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-5.126070702045602</v>
+        <v>-5.081992603506968</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-5.210804419317853</v>
+        <v>-5.201346365785263</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-4.647059983047804</v>
+        <v>-4.647863025328853</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-10.91138242065131</v>
+        <v>-10.80484917397995</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-8.668287245026661</v>
+        <v>-8.616331188184702</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-3.702511151632763</v>
+        <v>-3.699654265312375</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-10.95833677031219</v>
+        <v>-10.84562320957586</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-8.273590321217448</v>
+        <v>-8.198080538490331</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-10.11707374891331</v>
+        <v>-10.02279984010502</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>82</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-6.151974905575827</v>
+        <v>-6.051144239901667</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-2.885499738052246</v>
+        <v>-2.836728383459899</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-5.719392834892744</v>
+        <v>-5.603401036517518</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>7.825494444056154</v>
+        <v>7.672878463674294</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>1.189512253374268</v>
+        <v>1.193713531110689</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-2.17158239427593</v>
+        <v>-2.167655112913657</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-4.695340501792145</v>
+        <v>-4.691595884679266</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-5.162523900573589</v>
+        <v>-5.151290049234909</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-8.90459736959275</v>
+        <v>-8.769375384767059</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-8.541611201263684</v>
+        <v>-8.454797683555867</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-8.782097787601799</v>
+        <v>-8.652755585088812</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-6.297973893839902</v>
+        <v>-6.217041761214027</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-10.47666959881467</v>
+        <v>-10.29203848231713</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-13.98961491188093</v>
+        <v>-13.73162558815628</v>
       </c>
     </row>
     <row r="31">
@@ -1872,49 +1872,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>5.506561679790018</v>
+        <v>5.799089820342473</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>7.894988066825732</v>
+        <v>8.28050528516971</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.4998806397708719</v>
+        <v>-0.5521869960286523</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-2.369627507163322</v>
+        <v>-2.458742040046836</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1.091951277764515</v>
+        <v>1.076453098132568</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-10.61060678451983</v>
+        <v>-11.02130854476571</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-16.69534050179211</v>
+        <v>-17.27458496553506</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-5.162523900573639</v>
+        <v>-5.191582987383498</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-2.149753294952596</v>
+        <v>-2.178931476380519</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-3.024351105762136</v>
+        <v>-2.987048686723881</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-4.108767806879328</v>
+        <v>-4.221531770268456</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>1.032363630632688</v>
+        <v>1.170934093144091</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.7223842813871855</v>
+        <v>0.7763336805714189</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>3.019940260399608</v>
+        <v>3.159915667681723</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>49</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>4.649418822647199</v>
+        <v>4.507916489364014</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>3.037845209682942</v>
+        <v>2.927955099792833</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>4.683792829616898</v>
+        <v>4.605729992258603</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>2.773229635693816</v>
+        <v>2.716026564792116</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>6.316441073682874</v>
+        <v>6.21751846986789</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.4914340318066905</v>
+        <v>0.4867029507547187</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.4067003145344117</v>
+        <v>0.3703570100893643</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-2.101299410777692</v>
+        <v>-2.148395172159177</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>3.960149682631844</v>
+        <v>3.850474621880466</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.950641361345383</v>
+        <v>-1.013541743681103</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.8781666948081579</v>
+        <v>0.8370311506509296</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-1.131676299024988</v>
+        <v>-1.162582369238365</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>6.70251510746548</v>
+        <v>6.550291005389404</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>9.092485187827293</v>
+        <v>8.891570031554991</v>
       </c>
     </row>
     <row r="33">
@@ -1976,49 +1976,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-3.775489602261288</v>
+        <v>-3.711094332386544</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-7.951165779328058</v>
+        <v>-8.271678599840875</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.6537267936169258</v>
+        <v>-0.6756797265287844</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-8.215781353317169</v>
+        <v>-8.821682301683857</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-3.625997440184214</v>
+        <v>-3.918703212342024</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.7644529383659631</v>
+        <v>-0.8434834968485703</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-8.541494347945935</v>
+        <v>-9.090317670741854</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-9.008677746727436</v>
+        <v>-9.329190567240254</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-1.377369940602044</v>
+        <v>-1.22808999680155</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-6.04712377284482</v>
+        <v>-6.13112023615161</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-1.035254639160648</v>
+        <v>-0.9718888861397303</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-8.728546106041577</v>
+        <v>-9.19421070963719</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-12.89646748189461</v>
+        <v>-13.70516881142928</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-13.91858684453595</v>
+        <v>-14.74788575075793</v>
       </c>
     </row>
     <row r="34">
@@ -2213,10 +2213,8 @@
           <t>X &gt; -0.2952</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4080~4093</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4080</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-0.1113225127337927</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; -0.2779</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>4061~4074</t>
-        </is>
+      <c r="B7" t="n">
+        <v>4061</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-0.06339413758846746</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; -0.2607</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>4029~4042</t>
-        </is>
+      <c r="B8" t="n">
+        <v>4029</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-0.09363624203086118</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; -0.2434</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3999~4012</t>
-        </is>
+      <c r="B9" t="n">
+        <v>3999</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-0.2750933551052839</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; -0.2262</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3965~3978</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3965</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-0.2309948812959419</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; -0.2089</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3926~3939</t>
-        </is>
+      <c r="B11" t="n">
+        <v>3926</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-0.3989981069578832</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; -0.1916</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3885~3898</t>
-        </is>
+      <c r="B12" t="n">
+        <v>3885</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-0.4154496080498902</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; -0.1744</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3825~3838</t>
-        </is>
+      <c r="B13" t="n">
+        <v>3825</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-0.4611298262026793</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; -0.1571</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3769~3782</t>
-        </is>
+      <c r="B14" t="n">
+        <v>3769</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-0.5103605835627008</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; -0.1399</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>3702~3715</t>
-        </is>
+      <c r="B15" t="n">
+        <v>3702</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-0.4880547401292219</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; -0.1226</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>3609~3622</t>
-        </is>
+      <c r="B16" t="n">
+        <v>3609</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-0.6160225278300757</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; -0.1053</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>3474~3487</t>
-        </is>
+      <c r="B17" t="n">
+        <v>3474</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-0.7297446006802986</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; -0.08808</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>3346~3359</t>
-        </is>
+      <c r="B18" t="n">
+        <v>3346</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-0.9007023868964907</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; -0.07082</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>3164~3175</t>
-        </is>
+      <c r="B19" t="n">
+        <v>3164</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-1.028871391076116</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; -0.05356</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2967~2978</t>
-        </is>
+      <c r="B20" t="n">
+        <v>2967</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-0.9487774740044728</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; -0.03629</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2662~2673</t>
-        </is>
+      <c r="B21" t="n">
+        <v>2662</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-0.6789976168803875</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; -0.01903</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2293~2302</t>
-        </is>
+      <c r="B22" t="n">
+        <v>2293</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-1.059902264606151</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; -0.001772</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1915~1923</t>
-        </is>
+      <c r="B23" t="n">
+        <v>1915</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-1.063381117921885</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 0.01549</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1496~1503</t>
-        </is>
+      <c r="B24" t="n">
+        <v>1496</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-1.994436324201992</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 0.03275</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1152~1159</t>
-        </is>
+      <c r="B25" t="n">
+        <v>1152</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-1.932610019951134</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 0.05001</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>881~887</t>
-        </is>
+      <c r="B26" t="n">
+        <v>881</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-1.986110248056654</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 0.06727</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>681~687</t>
-        </is>
+      <c r="B27" t="n">
+        <v>681</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-2.129537301287122</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 0.08453</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>544~550</t>
-        </is>
+      <c r="B28" t="n">
+        <v>544</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-3.220711047482702</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 0.1018</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>418~424</t>
-        </is>
+      <c r="B29" t="n">
+        <v>418</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-2.96513643341752</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 0.1191</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>321~327</t>
-        </is>
+      <c r="B30" t="n">
+        <v>321</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-2.034722723879703</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 0.1363</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>239~245</t>
-        </is>
+      <c r="B31" t="n">
+        <v>239</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-0.6567036263324226</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 0.1536</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>192~195</t>
-        </is>
+      <c r="B32" t="n">
+        <v>192</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-2.23702806379972</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 0.1708</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>143~146</t>
-        </is>
+      <c r="B33" t="n">
+        <v>143</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-4.548232840757926</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 0.1881</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>107~107</t>
-        </is>
+      <c r="B34" t="n">
+        <v>107</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-4.829886918340819</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 0.2054</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B35" t="n">
+        <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-3.683914510686165</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; -0.2952</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B6" t="n">
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>5.83989501312336</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; -0.2779</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>103~103</t>
-        </is>
+      <c r="B7" t="n">
+        <v>103</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>2.846367505032738</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; -0.2607</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>135~135</t>
-        </is>
+      <c r="B8" t="n">
+        <v>135</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>3.062117235345582</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; -0.2434</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>165~165</t>
-        </is>
+      <c r="B9" t="n">
+        <v>165</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>6.900501073729423</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; -0.2262</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>199~199</t>
-        </is>
+      <c r="B10" t="n">
+        <v>199</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>4.79299384059405</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; -0.2089</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>238~238</t>
-        </is>
+      <c r="B11" t="n">
+        <v>238</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>6.750259158781624</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; -0.1916</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>279~279</t>
-        </is>
+      <c r="B12" t="n">
+        <v>279</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>5.92950074789038</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; -0.1744</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>339~339</t>
-        </is>
+      <c r="B13" t="n">
+        <v>339</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>5.323670824332801</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; -0.1571</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>395~395</t>
-        </is>
+      <c r="B14" t="n">
+        <v>395</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>4.974916110169765</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; -0.1399</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>462~462</t>
-        </is>
+      <c r="B15" t="n">
+        <v>462</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>4.000068173296519</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; -0.1226</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>555~555</t>
-        </is>
+      <c r="B16" t="n">
+        <v>555</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>4.083138256366603</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; -0.1053</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>690~690</t>
-        </is>
+      <c r="B17" t="n">
+        <v>690</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>3.73844573776104</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; -0.08808</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>818~818</t>
-        </is>
+      <c r="B18" t="n">
+        <v>818</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>3.741280506195899</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; -0.07082</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1000~1002</t>
-        </is>
+      <c r="B19" t="n">
+        <v>1000</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>3.294984833482637</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; -0.05356</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1197~1199</t>
-        </is>
+      <c r="B20" t="n">
+        <v>1197</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>2.385627568030223</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; -0.03629</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1502~1504</t>
-        </is>
+      <c r="B21" t="n">
+        <v>1502</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>1.229965935109178</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; -0.01903</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1871~1875</t>
-        </is>
+      <c r="B22" t="n">
+        <v>1871</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>1.319895013123357</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; -0.001772</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2249~2254</t>
-        </is>
+      <c r="B23" t="n">
+        <v>2249</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>0.9227107481130048</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 0.01549</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2668~2674</t>
-        </is>
+      <c r="B24" t="n">
+        <v>2668</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>1.134085987942612</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 0.03275</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>3012~3018</t>
-        </is>
+      <c r="B25" t="n">
+        <v>3012</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>0.7537452450650406</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 0.05001</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>3283~3290</t>
-        </is>
+      <c r="B26" t="n">
+        <v>3283</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>0.5460753576015662</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 0.06727</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3483~3490</t>
-        </is>
+      <c r="B27" t="n">
+        <v>3483</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>0.4291977829418911</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 0.08453</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3620~3627</t>
-        </is>
+      <c r="B28" t="n">
+        <v>3620</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>0.4980146712430198</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 0.1018</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3746~3753</t>
-        </is>
+      <c r="B29" t="n">
+        <v>3746</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>0.3442914959371066</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 0.1191</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3843~3850</t>
-        </is>
+      <c r="B30" t="n">
+        <v>3843</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>0.181886355114699</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 0.1363</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3925~3932</t>
-        </is>
+      <c r="B31" t="n">
+        <v>3925</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>0.04979667470355764</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 0.1536</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>3972~3982</t>
-        </is>
+      <c r="B32" t="n">
+        <v>3972</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>0.1183145677860011</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 0.1708</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>4021~4031</t>
-        </is>
+      <c r="B33" t="n">
+        <v>4021</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>0.1733937313901208</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 0.1881</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>4057~4070</t>
-        </is>
+      <c r="B34" t="n">
+        <v>4057</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>0.1355543087826589</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 0.2054</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4080~4093</t>
-        </is>
+      <c r="B35" t="n">
+        <v>4080</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>0.08413314326425336</v>

--- a/workspaces/btc_daily_14days/roc/roc_spread_5_14.xlsx
+++ b/workspaces/btc_daily_14days/roc/roc_spread_5_14.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that ROC Spread-5-14 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that ROC Spread-5-14 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -575,46 +575,46 @@
         <v>19</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-10.35538206353375</v>
+        <v>-10.34290863916792</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-1.468514263522103</v>
+        <v>-1.455644738805205</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>8.635114842619764</v>
+        <v>8.648091506886324</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>8.766636631552799</v>
+        <v>8.779588458850377</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>8.231755068609239</v>
+        <v>8.244840600364256</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>3.277698110331684</v>
+        <v>3.290716329282368</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>8.448059742804013</v>
+        <v>8.461106525737222</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>2.728184278198718</v>
+        <v>2.741346370121448</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>13.18133340134025</v>
+        <v>13.19451949840241</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>22.85133080330164</v>
+        <v>22.86472790415152</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>22.6523253050962</v>
+        <v>22.66577649978042</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>12.17112523277407</v>
+        <v>12.18457217515881</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>11.75394807693578</v>
+        <v>11.7675013878959</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>12.00650021415196</v>
+        <v>11.99607057845619</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>32</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>3.744275824862484</v>
+        <v>3.756759782693031</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>17.71782433481525</v>
+        <v>17.73070747357002</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>17.32819633848015</v>
+        <v>17.3411785632404</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>29.93093817766721</v>
+        <v>29.94390273037373</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>13.81116801239699</v>
+        <v>13.82425636748257</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>20.34898303326034</v>
+        <v>20.36200935515063</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>20.26944301489474</v>
+        <v>20.28249468485792</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>26.04866750033863</v>
+        <v>26.0618379706409</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>35.35755501258436</v>
+        <v>35.37074782117324</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>34.51709718332141</v>
+        <v>34.5304971239938</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>28.07570798113063</v>
+        <v>28.08916015222421</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>18.74673367388115</v>
+        <v>18.7601813767485</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>21.45545169389005</v>
+        <v>21.46900557647702</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>24.8354475825754</v>
+        <v>24.82501794687582</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>30</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>24.09459693078909</v>
+        <v>24.10709682906593</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>9.200906072192716</v>
+        <v>9.213782630189243</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>18.78180376308399</v>
+        <v>18.79478678108523</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>15.59064385800175</v>
+        <v>15.6035995303498</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>11.73203663454018</v>
+        <v>11.74512359431053</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>5.378305361360496</v>
+        <v>5.39132411091159</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>11.95012613472529</v>
+        <v>11.96317408103384</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>24.79993937720744</v>
+        <v>24.81310936690419</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>24.74514289608944</v>
+        <v>24.75833246982963</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>23.90218368384976</v>
+        <v>23.91558102510017</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>17.0419947970164</v>
+        <v>17.05544490189253</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>20.41242391991719</v>
+        <v>20.4258717957205</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>23.32990118826259</v>
+        <v>23.34345517491489</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>23.58544758257692</v>
+        <v>23.57501794687877</v>
       </c>
     </row>
     <row r="9">
@@ -731,98 +731,98 @@
         <v>34</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-5.417753609636272</v>
+        <v>-5.405278070659293</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-7.024939025504231</v>
+        <v>-7.012075235934766</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-10.35388577664976</v>
+        <v>-10.34092326153933</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-13.16101318609343</v>
+        <v>-13.14807596808507</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-4.897312770887233</v>
+        <v>-4.884235583020065</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-4.601737332490515</v>
+        <v>-4.588723993780199</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>7.056462662486233</v>
+        <v>7.069508225450541</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>3.654860497181971</v>
+        <v>3.668022406075991</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>12.40725445855707</v>
+        <v>12.42044009391877</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>8.623089911961955</v>
+        <v>8.63648334333638</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>11.35981073685296</v>
+        <v>11.37325969520207</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>5.51781115946369</v>
+        <v>5.531257112271881</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>5.099110976354048</v>
+        <v>5.112663794431469</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>5.35015346492834</v>
+        <v>5.339723829228845</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.2176</t>
+          <t>X ≈ -0.2175</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>39</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>16.68132983533917</v>
+        <v>16.69382300107984</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>12.52354836948661</v>
+        <v>12.53642637491795</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>14.68959581765345</v>
+        <v>14.70257518994718</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>9.707429301140714</v>
+        <v>9.720380385176377</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>11.73143362245114</v>
+        <v>11.74451982105675</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>12.03120135671512</v>
+        <v>12.04422271836472</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>11.9494593929203</v>
+        <v>11.96250685054218</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>11.48591550143569</v>
+        <v>11.49908012782563</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>11.42780696681226</v>
+        <v>11.44099211864378</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>8.020215885439413</v>
+        <v>8.03360898660361</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>12.94214754420879</v>
+        <v>12.95559669724882</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>18.10561363440436</v>
+        <v>18.1190611152055</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>22.81704704157884</v>
+        <v>22.83060095483656</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>12.81621681334579</v>
+        <v>12.80578717764764</v>
       </c>
     </row>
     <row r="11">
@@ -832,49 +832,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1.15988193554157</v>
+        <v>-0.1009632759000141</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-10.17136384487406</v>
+        <v>-8.826952940354559</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>4.024758102799943</v>
+        <v>5.022163119961348</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-3.143070633122392</v>
+        <v>-1.971668370159129</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-1.247189929581104</v>
+        <v>-0.1332932049185374</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.9507082368839903</v>
+        <v>0.1634070787884241</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-5.904999553586734</v>
+        <v>-4.674639277684236</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-3.937793905689631</v>
+        <v>-2.764985083033217</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-6.43569733938218</v>
+        <v>-5.204571714136186</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.02326728995397787</v>
+        <v>1.080878939940824</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>7.130289942809569</v>
+        <v>8.014144307444795</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-5.022134714816808</v>
+        <v>-3.847847154026816</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1.871723609508415</v>
+        <v>2.872246082259544</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>7.000081728915752</v>
+        <v>7.860732232591538</v>
       </c>
     </row>
     <row r="12">
@@ -884,49 +884,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>2.496664299190073</v>
+        <v>3.438235837856126</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>17.50685425446502</v>
+        <v>17.04097361029737</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>13.79309865719463</v>
+        <v>13.27085824842835</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>10.60166922769356</v>
+        <v>10.02291504029764</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>11.73046580956992</v>
+        <v>11.17987781509914</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>7.040743659583796</v>
+        <v>6.405375134421853</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>11.94876592496512</v>
+        <v>11.39785116784529</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>18.14153077492495</v>
+        <v>17.70340947209416</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>11.42732494501299</v>
+        <v>10.87625987877932</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>10.58131486169313</v>
+        <v>10.03031448744696</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>12.0449775754106</v>
+        <v>11.52211467275326</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>13.74860096555138</v>
+        <v>13.25383282520078</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>13.33212653343315</v>
+        <v>12.83733508501233</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>11.91878091590873</v>
+        <v>11.37162811636876</v>
       </c>
     </row>
     <row r="13">
@@ -939,150 +939,150 @@
         <v>56</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>2.852275968260031</v>
+        <v>2.864754702988769</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>11.92769285892891</v>
+        <v>11.94056837227141</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>9.756020017329917</v>
+        <v>9.768994059246559</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>11.66938150791652</v>
+        <v>11.68233210982596</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>7.572860644322688</v>
+        <v>7.585942663876502</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>6.089909534260485</v>
+        <v>6.102926133053941</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>11.35393823196329</v>
+        <v>11.36698418115913</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>3.758764167413055</v>
+        <v>3.771924570316877</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>5.482343840091254</v>
+        <v>5.495526014846561</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.7165787950098803</v>
+        <v>-0.7031889482184823</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>8.000271639025144</v>
+        <v>8.013719287466898</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>8.037118885189273</v>
+        <v>8.050564677959606</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>4.048764541387861</v>
+        <v>4.062317037367734</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>2.514019011147639</v>
+        <v>2.503589375447866</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.1485</t>
+          <t>X ≈ -0.1484</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>67</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-1.742841664021277</v>
+        <v>-1.730368611160785</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.113911053292227</v>
+        <v>1.126776341976267</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2.20816053508868</v>
+        <v>2.221127709235056</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>2.338498675915645</v>
+        <v>2.351441834165726</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-4.152998040870592</v>
+        <v>-4.139924483921988</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-8.325026364864314</v>
+        <v>-8.312018908536764</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-5.432753482415421</v>
+        <v>-5.419716563688716</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-2.920418027956138</v>
+        <v>-2.907261161814731</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-4.472507676465021</v>
+        <v>-4.459329601747065</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.6412267386237787</v>
+        <v>0.6546164748064811</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.545787041951201</v>
+        <v>-2.532341956568224</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>1.963489045257532</v>
+        <v>1.976933777778925</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>6.020471939296009</v>
+        <v>6.034024472357821</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>3.28694011988815</v>
+        <v>3.276510484191363</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.1313</t>
+          <t>X ≈ -0.1312</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>93</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>4.477921021294229</v>
+        <v>4.490398031670018</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>7.160029777742338</v>
+        <v>7.172898710799032</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>4.623793505937137</v>
+        <v>4.636761050394966</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.610207610208349</v>
+        <v>2.623149487519775</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.07034885135686153</v>
+        <v>-0.05727423548443511</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>3.445491858151598</v>
+        <v>3.458504751402742</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>4.434554139607293</v>
+        <v>4.447594943401889</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>6.116221372230314</v>
+        <v>6.12938128436349</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>3.909606291838578</v>
+        <v>3.922786606125477</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>4.135920910072791</v>
+        <v>4.14931105551036</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>2.858218903733274</v>
+        <v>2.871664676187834</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>5.0430856290807</v>
+        <v>5.056530517134348</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>7.849446273330479</v>
+        <v>7.862998813429385</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>2.725232528811958</v>
+        <v>2.714802893113564</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>135</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>2.31042548018231</v>
+        <v>2.322897541981931</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>5.1343045864649</v>
+        <v>5.14716931591456</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>8.433850082001726</v>
+        <v>8.446818801335361</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>5.611702690108288</v>
+        <v>5.624644785833709</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>7.294018746907341</v>
+        <v>7.307096489635903</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>7.593094322496434</v>
+        <v>7.606108152566094</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>6.031642746503046</v>
+        <v>6.044682994431085</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.869510566286806</v>
+        <v>1.882667207840321</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>2.549120458826671</v>
+        <v>2.562299128814914</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.258466793356405</v>
+        <v>-1.245079311669585</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.463227047011706</v>
+        <v>-1.449783043110592</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.428907362810719</v>
+        <v>-1.415463970910942</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.108706679811213</v>
+        <v>-1.095155066049784</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>2.84470684183465</v>
+        <v>2.834277206136669</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>128</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>3.739198779627415</v>
+        <v>3.751668818198439</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>2.912695318447753</v>
+        <v>2.925554612927343</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>2.519283607915582</v>
+        <v>2.532244212637089</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.871413608428483</v>
+        <v>1.884349909040473</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-2.559533788298118</v>
+        <v>-2.54646606192852</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.07489169612351532</v>
+        <v>0.08789832380452367</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.569277843723903</v>
+        <v>-1.556244053705178</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-5.155322847162267</v>
+        <v>-5.142171756560863</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-6.777623666333554</v>
+        <v>-6.764450608454545</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-6.067503734771961</v>
+        <v>-6.054119362235333</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-11.73755164425155</v>
+        <v>-11.72411144197289</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-10.14473913389573</v>
+        <v>-10.1312980032405</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-5.10056830533221</v>
+        <v>-5.087017396379736</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-3.289552417424602</v>
+        <v>-3.299982053122577</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>182</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.327466454995431</v>
+        <v>1.340106153770627</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.8428642009745602</v>
+        <v>-0.8298308535303391</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.6906430440779303</v>
+        <v>-0.677506683345598</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.268704599681314</v>
+        <v>-0.5464646839571472</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>3.870102752800051</v>
+        <v>3.587727773394711</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.7645281341945989</v>
+        <v>-0.7515256570319835</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.397849696524453</v>
+        <v>-1.384818992500911</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.864155163463074</v>
+        <v>-1.851005252042192</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-3.022432694046771</v>
+        <v>-3.009260535192475</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.676848011549971</v>
+        <v>-1.663464107746194</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-3.528391904945487</v>
+        <v>-3.51495121508399</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-2.945794556424119</v>
+        <v>-2.932353252191362</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-5.014625713503051</v>
+        <v>-5.001075336306407</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-4.216750219622398</v>
+        <v>-4.22717985532055</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>197</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-2.235158964434305</v>
+        <v>-2.22269801028925</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.312140450310295</v>
+        <v>-1.299287121025579</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.835686657804551</v>
+        <v>1.848646376486705</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>4.496049307573159</v>
+        <v>4.510980885108097</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>3.9602014686687</v>
+        <v>3.974978777494712</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.727766041005864</v>
+        <v>1.740765632010785</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>3.162808012985522</v>
+        <v>3.175837771040129</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.8479798623054933</v>
+        <v>-0.8348332944889876</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.11838476970528</v>
+        <v>1.131555745964704</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.771331631588339</v>
+        <v>-2.757950982235648</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-3.483459654436849</v>
+        <v>-3.470021185942777</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-6.493719042562304</v>
+        <v>-6.480280010733111</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-4.378762115845802</v>
+        <v>-4.365212445923007</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-3.622674244835764</v>
+        <v>-3.633103880534151</v>
       </c>
     </row>
     <row r="20">
@@ -1303,410 +1303,410 @@
         <v>305</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-3.303380686018613</v>
+        <v>-3.290933212783145</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.970211670211192</v>
+        <v>-1.957369943065665</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-4.32653494682863</v>
+        <v>-4.313591254653339</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-3.216895329421725</v>
+        <v>-3.204492986371534</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-4.732551787158478</v>
+        <v>-4.720725705988833</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-4.763122504383013</v>
+        <v>-4.75013787511601</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-4.522929059556212</v>
+        <v>-4.509913035554256</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-3.353807326204439</v>
+        <v>-3.340669339985098</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-4.724631244080847</v>
+        <v>-4.711469373985459</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-3.610014664036889</v>
+        <v>-3.596639294423888</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-3.160369944162703</v>
+        <v>-3.146935100591101</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-2.799290127903909</v>
+        <v>-2.785852842346976</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-2.565111444326256</v>
+        <v>-2.551562808540908</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.332585204309844</v>
+        <v>-1.343014840007854</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ -0.02766</t>
+          <t>X ≈ -0.02767</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.687978960992709</v>
+        <v>1.437266838750276</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.7578605573839567</v>
+        <v>0.7759988137839073</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>2.126535122536161</v>
+        <v>1.879306635017869</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.1743105301752834</v>
+        <v>-0.2847715380296023</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.451204956014543</v>
+        <v>1.3472019716232</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>2.020068974405589</v>
+        <v>1.915631290415774</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.935478599009677</v>
+        <v>1.831022248082725</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>4.985293426612849</v>
+        <v>4.890462521531241</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>3.57513929721096</v>
+        <v>3.476608659258339</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>6.516287616921815</v>
+        <v>6.428217254604043</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>5.503122742413495</v>
+        <v>5.412858888500871</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>5.810816663090812</v>
+        <v>5.721245547050437</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>4.038490685093251</v>
+        <v>3.945304651189794</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>3.477046498564562</v>
+        <v>3.357626642529361</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ -0.0104</t>
+          <t>X ≈ -0.01041</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.042277915136246</v>
+        <v>-0.9020943809501247</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-2.914981565651026</v>
+        <v>-3.037571127150024</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-2.519832577092373</v>
+        <v>-2.380951019867162</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-2.653161687561735</v>
+        <v>-2.513705476746139</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-2.663225451629415</v>
+        <v>-2.525245464160626</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.6736644912724614</v>
+        <v>0.6639820784096102</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.4659177439342628</v>
+        <v>-0.3325419849088931</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.1231638832648443</v>
+        <v>0.2539353482744815</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2.438993884464956</v>
+        <v>2.563581175876244</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>2.120342140895126</v>
+        <v>2.243799910505075</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>3.239094394581315</v>
+        <v>3.359177889857484</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>4.861432257591112</v>
+        <v>4.97738454390565</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>2.064354486974942</v>
+        <v>2.186743295971148</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2.051056048183916</v>
+        <v>2.150215836059367</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.006859</t>
+          <t>X ≈ 0.006843</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2.260863723593715</v>
+        <v>2.406122612469119</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.1784579826926134</v>
+        <v>0.321384008130515</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.02019194043701589</v>
+        <v>0.1642243242193189</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.03743331018763</v>
+        <v>-0.897034361758152</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.1481696566809205</v>
+        <v>-0.003972682386617521</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.039674042532624</v>
+        <v>-0.8988343830032903</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.7611943352405959</v>
+        <v>-0.9839624648726968</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.03875998725458629</v>
+        <v>-0.1325927853715783</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1.32896283446776</v>
+        <v>1.238513545081119</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.7069929593668434</v>
+        <v>-0.8001447365083934</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.7574709934828761</v>
+        <v>0.6683092473298231</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.07828283443252815</v>
+        <v>-0.01264713369125303</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1.567602648440143</v>
+        <v>1.481289899642448</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.8646838594249857</v>
+        <v>0.7520514397001818</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.02412</t>
+          <t>X ≈ 0.0241</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-2.201482552390878</v>
+        <v>-2.334329315722542</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-2.3530764051226</v>
+        <v>-2.490662891770278</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-3.618387544469122</v>
+        <v>-3.753595727072373</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.463933387446772</v>
+        <v>-1.603512054980257</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-3.152496613712387</v>
+        <v>-3.290400821035256</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.412354133572336</v>
+        <v>-1.552975184926922</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.6326730522139457</v>
+        <v>-0.4859884662363925</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.678082783464085</v>
+        <v>-1.530798788722088</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.739718071870755</v>
+        <v>-1.592295156793426</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.425431381053961</v>
+        <v>-1.281049733148713</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-3.368492961598925</v>
+        <v>-3.218904886915269</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-3.04471356350691</v>
+        <v>-2.895848235317253</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.8515679074577065</v>
+        <v>-0.7100513255246454</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.8528894430405174</v>
+        <v>0.9663222947033034</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.04138</t>
+          <t>X ≈ 0.04136</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>271</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.758684924154245</v>
+        <v>-1.745965216662718</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-2.261911127864913</v>
+        <v>-2.250777719690383</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-3.024891913853608</v>
+        <v>-3.013491404515861</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-5.460994292189419</v>
+        <v>-5.452240967875355</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-7.460632545813155</v>
+        <v>-7.455168989742766</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-4.600311445421355</v>
+        <v>-4.591027384341466</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-5.053959476301081</v>
+        <v>-5.044189381642951</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-4.962329952211697</v>
+        <v>-5.144504180610951</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.358900353836908</v>
+        <v>-1.345944137167358</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.098584295326262</v>
+        <v>-1.085380790092806</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.5398369857801697</v>
+        <v>0.5531442505792157</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.9452647961017391</v>
+        <v>0.9586175998387958</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.2095564953049873</v>
+        <v>-0.1960501656495239</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-2.17100998200025</v>
+        <v>-2.181439617698402</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.05864</t>
+          <t>X ≈ 0.05862</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>200</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.49774113180689</v>
+        <v>-1.484501706865125</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.8852895097938145</v>
+        <v>0.899815745541872</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.4854976778002893</v>
+        <v>0.5009417562893717</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.1240561229524317</v>
+        <v>0.138087993664918</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>5.059261725128891</v>
+        <v>5.077820788276419</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>5.835598224267983</v>
+        <v>5.857606952431034</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>6.238620694133523</v>
+        <v>6.262693415779708</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>4.778201669647409</v>
+        <v>4.801261750572444</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.240617142108334</v>
+        <v>1.253444851882001</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>1.400700485925725</v>
+        <v>1.413793497345381</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.284455324600302</v>
+        <v>-1.271254540928894</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.2473934056611782</v>
+        <v>0.2606810661346728</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-5.161818319826118</v>
+        <v>-5.14835403894817</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.414552417424595</v>
+        <v>-1.424982053122747</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.0759</t>
+          <t>X ≈ 0.07588</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>137</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2.20329859601501</v>
+        <v>2.223785657560683</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>1.348623648087028</v>
+        <v>1.365002953243646</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.220077218763123</v>
+        <v>-1.206258735372373</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2.527936408537236</v>
+        <v>2.547039326542802</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2.006982442373314</v>
+        <v>2.023305814204022</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.8319132747088389</v>
+        <v>0.8502782535891882</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>2.176816506405423</v>
+        <v>2.200241020896854</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.4562593940349871</v>
+        <v>-0.4367015445886366</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.967439675931878</v>
+        <v>-1.954852527036813</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>1.547961129979761</v>
+        <v>1.560893467013237</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>1.361437170992673</v>
+        <v>1.37451367947785</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.6748087924582435</v>
+        <v>0.6880076256253531</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>1.721210739865718</v>
+        <v>1.734638769021302</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.9400998626800785</v>
+        <v>-0.9505294983782306</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>126</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-4.068569687794167</v>
+        <v>-4.058075768071433</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.1491732226185363</v>
+        <v>-0.1341942034261123</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>2.580491817960088</v>
+        <v>2.603913063565365</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-1.983774366593217</v>
+        <v>-1.971612017464388</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.6357858499009907</v>
+        <v>0.6508501515124365</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-3.020038024139694</v>
+        <v>-3.007539656691748</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-5.480333286784862</v>
+        <v>-5.468710033927422</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-5.157378102974981</v>
+        <v>-5.145054726612848</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-8.368137831265358</v>
+        <v>-8.356068193544282</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-5.284061564768123</v>
+        <v>-5.271514343623785</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-6.263420990165784</v>
+        <v>-6.250675102367012</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-3.866555332720722</v>
+        <v>-3.853543313980367</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-4.283091984884017</v>
+        <v>-4.2697653223969</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-4.827250830123006</v>
+        <v>-4.837680465821194</v>
       </c>
     </row>
     <row r="29">
@@ -1771,98 +1771,98 @@
         <v>97</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-6.044134379413784</v>
+        <v>-6.041203983650945</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-2.535064273685563</v>
+        <v>-2.526080448594776</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-10.03998010994135</v>
+        <v>-10.04864024895922</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-11.90778539955206</v>
+        <v>-11.92710640223657</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-6.343843707325668</v>
+        <v>-6.349165697531973</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-5.081992603506968</v>
+        <v>-5.076296056969056</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-5.201346365785263</v>
+        <v>-5.189856453740227</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-4.647863025328853</v>
+        <v>-4.634548175653464</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-10.80484917397995</v>
+        <v>-10.79372931653601</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-8.616331188184702</v>
+        <v>-8.604489531179219</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-3.699654265312375</v>
+        <v>-3.687354810299652</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-10.84562320957586</v>
+        <v>-10.83304094382093</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-8.198080538490331</v>
+        <v>-8.184950495760873</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-10.02279984010502</v>
+        <v>-10.03322947580311</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.1277</t>
+          <t>X ≈ 0.1276</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-6.051144239901667</v>
+        <v>-5.495280187087928</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-2.836728383459899</v>
+        <v>-2.212625122915867</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-5.603401036517518</v>
+        <v>-5.020130964611091</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>7.672878463674294</v>
+        <v>8.464045081721004</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>1.193713531110689</v>
+        <v>1.884595898544575</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-2.167655112913657</v>
+        <v>-1.521043146803315</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-4.691595884679266</v>
+        <v>-4.07442888939147</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-5.151290049234909</v>
+        <v>-4.535281874691329</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-8.769375384767059</v>
+        <v>-8.19982657040724</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-8.454797683555867</v>
+        <v>-7.86683696536047</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-8.652755585088812</v>
+        <v>-8.061871815711427</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-6.217041761214027</v>
+        <v>-5.592960794048487</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-10.29203848231713</v>
+        <v>-9.709671376807144</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-13.73162558815628</v>
+        <v>-13.21510550991292</v>
       </c>
     </row>
     <row r="31">
@@ -1872,49 +1872,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>5.799089820342473</v>
+        <v>4.652057703049138</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>8.28050528516971</v>
+        <v>7.059919973545895</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.5521869960286523</v>
+        <v>-1.645644615295076</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-2.458742040046836</v>
+        <v>-3.514455327449795</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1.076453098132568</v>
+        <v>-0.05467316905921393</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-11.02130854476571</v>
+        <v>-11.94030414255108</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-17.27458496553506</v>
+        <v>-18.08505202526942</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-5.191582987383498</v>
+        <v>-6.201302449335451</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-2.178931476380519</v>
+        <v>-4.34715535841196</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-2.987048686723881</v>
+        <v>-4.05518541050116</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-4.221531770268456</v>
+        <v>-6.413704227223619</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>1.170934093144091</v>
+        <v>-1.109956071254011</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.7763336805714189</v>
+        <v>-0.4031139715609129</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>3.159915667681723</v>
+        <v>1.908351280210582</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>49</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>4.507916489364014</v>
+        <v>4.567606223467372</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>2.927955099792833</v>
+        <v>2.977494945998906</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>4.605729992258603</v>
+        <v>4.644758069462313</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>2.716026564792116</v>
+        <v>2.748073397491126</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>6.21751846986789</v>
+        <v>6.2636034755145</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.4867029507547187</v>
+        <v>0.5013228740664033</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.3703570100893643</v>
+        <v>0.3955376992048514</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-2.148395172159177</v>
+        <v>-2.119515575736806</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>3.850474621880466</v>
+        <v>3.900231714419043</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-1.013541743681103</v>
+        <v>-1.003506713029864</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.8370311506509296</v>
+        <v>0.864200292413571</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-1.162582369238365</v>
+        <v>-1.138828057113784</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>6.550291005389404</v>
+        <v>6.562207708550282</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>8.891570031554991</v>
+        <v>8.881140395856839</v>
       </c>
     </row>
     <row r="33">
@@ -1976,49 +1976,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-3.711094332386544</v>
+        <v>-3.721197407802038</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-8.271678599840875</v>
+        <v>-8.146156177652216</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.6756797265287844</v>
+        <v>-0.6549594024664813</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-8.821682301683857</v>
+        <v>-8.595819042291694</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-3.918703212342024</v>
+        <v>-3.802749839371131</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.8434834968485703</v>
+        <v>-0.8026731070333284</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-9.090317670741854</v>
+        <v>-8.88442160032389</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-9.329190567240254</v>
+        <v>-9.203396945332408</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-1.22808999680155</v>
+        <v>-1.267340967830748</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-6.13112023615161</v>
+        <v>-7.4486185201769</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.9718888861397303</v>
+        <v>-0.9806952353828251</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-9.19421070963719</v>
+        <v>-9.017146533167285</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-13.70516881142928</v>
+        <v>-14.8427027918861</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-14.74788575075793</v>
+        <v>-13.18173880987951</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>23</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-9.015177450644757</v>
+        <v>-9.002655160969134</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-10.62675106360904</v>
+        <v>-10.61384125403299</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-6.673793683249116</v>
+        <v>-6.660786551831514</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>2.152111623271459</v>
+        <v>2.165090765669923</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>14.65716866906882</v>
+        <v>14.67027947344376</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1.911132345914922</v>
+        <v>1.924175242209287</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>1.826398628642643</v>
+        <v>1.839464882943119</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>10.05486740377422</v>
+        <v>10.06804841306946</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>14.3416936045484</v>
+        <v>14.35489234350317</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>13.49156841952048</v>
+        <v>13.50497354717331</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>8.938989008246381</v>
+        <v>8.952446301956599</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.2777199916787652</v>
+        <v>0.2911722803988752</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>4.205291467690387</v>
+        <v>4.21884751404199</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>4.45501279996671</v>
+        <v>4.444583164268558</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that ROC Spread-5-14 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that ROC Spread-5-14 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2214,49 +2214,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4080</v>
+        <v>4081</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.1113225127337927</v>
+        <v>-0.1115950730355735</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.1960633356429682</v>
+        <v>0.1957063298589361</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.1811264489605406</v>
+        <v>0.1807706754199927</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.01754926755452146</v>
+        <v>-0.01785589348644123</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.06871821344560658</v>
+        <v>0.06838726551352892</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.01268088671304923</v>
+        <v>0.01236518978871715</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.03918359901532398</v>
+        <v>0.03886078186257436</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.001450646660849486</v>
+        <v>0.001134231305435662</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.02739420590014419</v>
+        <v>0.02707093849352304</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.1212579821828541</v>
+        <v>0.1209067066645773</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.1262021614053168</v>
+        <v>0.1258483374716732</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.1744032032332257</v>
+        <v>0.1740376074708578</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.2580492103579246</v>
+        <v>0.2576605426085834</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.2766240531636299</v>
+        <v>0.276806724137721</v>
       </c>
     </row>
     <row r="7">
@@ -2266,49 +2266,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4061</v>
+        <v>4062</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.06339413758846746</v>
+        <v>-0.06373811642392724</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.2038513125905581</v>
+        <v>0.2034305224499278</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.1415731912704317</v>
+        <v>0.141164792653413</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.05864740399456281</v>
+        <v>-0.05900592861554799</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.03052621633944597</v>
+        <v>0.0301419151043234</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.00259498800962632</v>
+        <v>-0.00296929363087628</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.0001585942208208735</v>
+        <v>-0.0005342622372737083</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.01130678722223877</v>
+        <v>-0.01168310760088787</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.03414847932846499</v>
+        <v>-0.03451978593736271</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.01491191382501</v>
+        <v>0.01452251100917579</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.02081030232378112</v>
+        <v>0.0204178512373403</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.1182747327675173</v>
+        <v>0.1178583468145149</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.2042639164734155</v>
+        <v>0.2038232762224581</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.2217440612752313</v>
+        <v>0.2219898818846318</v>
       </c>
     </row>
     <row r="8">
@@ -2318,49 +2318,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4029</v>
+        <v>4030</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.09363624203086118</v>
+        <v>-0.09407457616877934</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.06474802723160877</v>
+        <v>0.06425611489760996</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.005069855278684088</v>
+        <v>0.004589000926664255</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.2968372125359409</v>
+        <v>-0.2972424241707969</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.07892539385510133</v>
+        <v>-0.07938951479048484</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.1642357168953552</v>
+        <v>-0.1646763201224459</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.1611482322182738</v>
+        <v>-0.1615905714946066</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.2182859823579975</v>
+        <v>-0.2187185107035532</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.3152441635531389</v>
+        <v>-0.315653424504994</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.2591188453271087</v>
+        <v>-0.2595497439822694</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.202013407212533</v>
+        <v>-0.2024604995397254</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.02968026502738041</v>
+        <v>-0.03017002463905527</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.0354781113412912</v>
+        <v>0.03496823066212329</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.02625175234457799</v>
+        <v>0.02663085010306077</v>
       </c>
     </row>
     <row r="9">
@@ -2370,101 +2370,101 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3999</v>
+        <v>4000</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.2750933551052839</v>
+        <v>-0.2755833617080441</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.003790292685572183</v>
+        <v>-0.004365333967079721</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.1357908642097243</v>
+        <v>-0.1363374824245227</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.4160231170410995</v>
+        <v>-0.416498738829695</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.1675297601596455</v>
+        <v>-0.1680733631087463</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.2058151698455148</v>
+        <v>-0.2063463233551985</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.2520055042883627</v>
+        <v>-0.2525263063885674</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.4059695934575061</v>
+        <v>-0.4064572197856151</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.5032440664761921</v>
+        <v>-0.5037083187125049</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.4403739280666272</v>
+        <v>-0.4408632247503874</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.3313758093447916</v>
+        <v>-0.3318947900504625</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.1830343849444418</v>
+        <v>-0.1835903382917508</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.1392737497008838</v>
+        <v>-0.1398454214197713</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.150486400920478</v>
+        <v>-0.1499820531227556</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.2262</t>
+          <t>X &gt; -0.2261</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3965</v>
+        <v>3966</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.2309948812959419</v>
+        <v>-0.2316071589585817</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.05641627904603297</v>
+        <v>0.05571084774420143</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.04817037820140513</v>
+        <v>-0.04885490136302906</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.3067344254023112</v>
+        <v>-0.3073525901169702</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.1269717217322182</v>
+        <v>-0.1276423203762747</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.1681199987156532</v>
+        <v>-0.168776771969803</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.3146758492241304</v>
+        <v>-0.3152971520977275</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.4407913395058713</v>
+        <v>-0.4413872014495723</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.6139519983428059</v>
+        <v>-0.6145053550285553</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.5180934162282824</v>
+        <v>-0.5186821312846632</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.4316281025530344</v>
+        <v>-0.4322415506401285</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.2319193152117478</v>
+        <v>-0.2325829790681411</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.1841930638713407</v>
+        <v>-0.1848744968960503</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.1976545611824818</v>
+        <v>-0.1970445846406506</v>
       </c>
     </row>
     <row r="11">
@@ -2474,49 +2474,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3926</v>
+        <v>3927</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.3989981069578832</v>
+        <v>-0.3996977564226754</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.06742940397158748</v>
+        <v>-0.06823819874416159</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.1945720291536048</v>
+        <v>-0.1953549710246207</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.4062128730169761</v>
+        <v>-0.4069404653490594</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.244770450316814</v>
+        <v>-0.2455476739581144</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.2893053101934413</v>
+        <v>-0.2900670648455446</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.4365050072586811</v>
+        <v>-0.4372310344768877</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.5592685597801221</v>
+        <v>-0.559970910602047</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.7335721205132231</v>
+        <v>-0.734231456753335</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.6029110582978348</v>
+        <v>-0.6036170316151086</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.5644801785142519</v>
+        <v>-0.565199455317412</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.4140802385523159</v>
+        <v>-0.4148376568569461</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.4126822039917002</v>
+        <v>-0.4134468275855383</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.3269314291413679</v>
+        <v>-0.3261788954960707</v>
       </c>
     </row>
     <row r="12">
@@ -2529,46 +2529,46 @@
         <v>3885</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.4154496080498902</v>
+        <v>-0.4029273183742674</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.03920156438800149</v>
+        <v>0.0264506092732546</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.2391003522964894</v>
+        <v>-0.2517605720082585</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.3773296894483025</v>
+        <v>-0.3900244879997743</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.2341915060054021</v>
+        <v>-0.2467612357855629</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.2823252535668388</v>
+        <v>-0.2949694880199729</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.3787937392021874</v>
+        <v>-0.3914212156314036</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.5236135947396363</v>
+        <v>-0.5361329195487343</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.6733952520515416</v>
+        <v>-0.6859034539708162</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.6095193754865846</v>
+        <v>-0.6218277988751666</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.6456862467187037</v>
+        <v>-0.6579491176175409</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.3654495478118136</v>
+        <v>-0.3777240406713318</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.4367904764121633</v>
+        <v>-0.4489678320162938</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.4042564071285923</v>
+        <v>-0.4146860428267445</v>
       </c>
     </row>
     <row r="13">
@@ -2578,49 +2578,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3825</v>
+        <v>3826</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.4611298262026793</v>
+        <v>-0.462161146449958</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.2348008307504585</v>
+        <v>-0.2359270324048524</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.4592132779355751</v>
+        <v>-0.460290240174956</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.5495492803054276</v>
+        <v>-0.5506003981329499</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.4218724050732519</v>
+        <v>-0.4229692086037034</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.3971969227927303</v>
+        <v>-0.3982941959980266</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.5721672241303111</v>
+        <v>-0.5732212863645785</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.8164001730873167</v>
+        <v>-0.8174013463931971</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.8632104708290242</v>
+        <v>-0.8642013203148551</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.7850618733247074</v>
+        <v>-0.7860924080996838</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.8447554831442616</v>
+        <v>-0.8457755064392529</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.5868464186096602</v>
+        <v>-0.5879336211957593</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.652773488331313</v>
+        <v>-0.6538533187138071</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.5975589533723138</v>
+        <v>-0.5964404953600777</v>
       </c>
     </row>
     <row r="14">
@@ -2630,101 +2630,101 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3769</v>
+        <v>3770</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.5103605835627008</v>
+        <v>-0.5115795251153656</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.4155118009340768</v>
+        <v>-0.4167980516785619</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.6109917508819365</v>
+        <v>-0.6122371687605224</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.7310987958640425</v>
+        <v>-0.7323097404262384</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.5406585687151164</v>
+        <v>-0.5419344777970423</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.4935826913241783</v>
+        <v>-0.4948640470396555</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.7493659255209266</v>
+        <v>-0.7505824285877409</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.8843782052093658</v>
+        <v>-0.8855717048376945</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.9574930501369394</v>
+        <v>-0.9586694186620761</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.7860793984999859</v>
+        <v>-0.7873238653286805</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.976175360788595</v>
+        <v>-0.9773754291073473</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.7149817481434226</v>
+        <v>-0.7162508373105396</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.7226291873666781</v>
+        <v>-0.7239078385919342</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.6437909422322505</v>
+        <v>-0.6424886844224815</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.1399</t>
+          <t>X &gt; -0.1398</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3702</v>
+        <v>3703</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.4880547401292219</v>
+        <v>-0.4895274406527577</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.4431917931634572</v>
+        <v>-0.4447266188875432</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.6620136858252224</v>
+        <v>-0.6635024798125642</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.7866533692322832</v>
+        <v>-0.7881054075873664</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.4752812741083048</v>
+        <v>-0.4768344695846878</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.3518466767031114</v>
+        <v>-0.3534248421462465</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.6646044543399654</v>
+        <v>-0.6661017407530849</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.8475292943168711</v>
+        <v>-0.8489923924916383</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.8938771722428314</v>
+        <v>-0.8953304415444094</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.8119112491718568</v>
+        <v>-0.813413523116715</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.9477680180987207</v>
+        <v>-0.9492407390344795</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.763457583680399</v>
+        <v>-0.7649798055014614</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.844668024613128</v>
+        <v>-0.8461820662002566</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.714930591384622</v>
+        <v>-0.713396851934526</v>
       </c>
     </row>
     <row r="16">
@@ -2734,49 +2734,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3609</v>
+        <v>3610</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.6160225278300757</v>
+        <v>-0.6178191494965333</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.6391185335608682</v>
+        <v>-0.6409701523116027</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.7982231812072911</v>
+        <v>-0.8000466649397922</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.8741867776800447</v>
+        <v>-0.87598538133944</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.4857159416937549</v>
+        <v>-0.4876430850338025</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.4496999556561363</v>
+        <v>-0.4516269064675882</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.7960042186062708</v>
+        <v>-0.7978396331703692</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.026977565857152</v>
+        <v>-1.028767670039429</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.017657710386246</v>
+        <v>-1.019453678506544</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.939411496001938</v>
+        <v>-0.9412621064442277</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.045844156566538</v>
+        <v>-1.047674036434934</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.9130858792710796</v>
+        <v>-0.9149522320956791</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.068705882664879</v>
+        <v>-1.070546005758587</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.8035798488460486</v>
+        <v>-0.801713355061807</v>
       </c>
     </row>
     <row r="17">
@@ -2786,49 +2786,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3474</v>
+        <v>3475</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.7297446006802986</v>
+        <v>-0.7320628195251828</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.8634743542872556</v>
+        <v>-0.8658331244585256</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.15698250490712</v>
+        <v>-1.159277409672782</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.126229114511204</v>
+        <v>-1.128527848265584</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.7880372378829179</v>
+        <v>-0.7904603059202557</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.7622437747553334</v>
+        <v>-0.7646612181134955</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.061327287198601</v>
+        <v>-1.063664253235459</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.139535394826481</v>
+        <v>-1.141873773208857</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.156263079656171</v>
+        <v>-1.158600909870117</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.9270129740840147</v>
+        <v>-0.9294591358815154</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.029624614191732</v>
+        <v>-1.032052535456174</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.8930410029677205</v>
+        <v>-0.8955078911632839</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.067151447542614</v>
+        <v>-1.069589970322816</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.9453526477066987</v>
+        <v>-0.9429676646335423</v>
       </c>
     </row>
     <row r="18">
@@ -2838,49 +2838,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3346</v>
+        <v>3347</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.9007023868964907</v>
+        <v>-0.9035350781533964</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.007930336986021</v>
+        <v>-1.010827934851527</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.297616713646306</v>
+        <v>-1.300453019967279</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.240902834934481</v>
+        <v>-1.24374994355545</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.7202692885544195</v>
+        <v>-0.7233050215554329</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.7942680844601995</v>
+        <v>-0.7972658256323228</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.041895825382923</v>
+        <v>-1.0448264239973</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.9859129220533234</v>
+        <v>-0.9888895658981198</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.9412199968424559</v>
+        <v>-0.9442152625982843</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.7303653896942848</v>
+        <v>-0.7334757152142686</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.6199968019240529</v>
+        <v>-0.6231539576150809</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.5391206919220579</v>
+        <v>-0.542301696258626</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.91285456834445</v>
+        <v>-0.9159506782596836</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.8556761472512591</v>
+        <v>-0.8528278852111981</v>
       </c>
     </row>
     <row r="19">
@@ -2890,49 +2890,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3164</v>
+        <v>3165</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.028871391076116</v>
+        <v>-1.032553310131334</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.01742529171235</v>
+        <v>-1.021235981865892</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.332531128267505</v>
+        <v>-1.336274894616608</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.296825742272048</v>
+        <v>-1.283846599873584</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.9843172378358744</v>
+        <v>-0.9712064334609352</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.7959787895639678</v>
+        <v>-0.7998960659752257</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.021420602706648</v>
+        <v>-1.025275508525681</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.9353945630341727</v>
+        <v>-0.9393145090645589</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.8215042222245117</v>
+        <v>-0.8254670036371081</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.6759216990565662</v>
+        <v>-0.6799977097037413</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.4526997384759071</v>
+        <v>-0.4568641943103913</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.4006836997161898</v>
+        <v>-0.404864292410366</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.6769119803485921</v>
+        <v>-0.6810398764383621</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.6623400280440706</v>
+        <v>-0.6587893201053845</v>
       </c>
     </row>
     <row r="20">
@@ -2942,465 +2942,465 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2967</v>
+        <v>2968</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.9487774740044728</v>
+        <v>-0.9535578566504981</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.9978570792944836</v>
+        <v>-1.002780431187162</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.542891392458998</v>
+        <v>-1.547672970899406</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.68145546415257</v>
+        <v>-1.668476321754106</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.312618614708605</v>
+        <v>-1.299507810333665</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.9635479609904181</v>
+        <v>-0.9685316301609532</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.299240972538584</v>
+        <v>-1.30412298698743</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.9411986398941536</v>
+        <v>-0.9462494144794462</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.9503070976576637</v>
+        <v>-0.9553637292676811</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.5367926944361514</v>
+        <v>-0.5420742613584579</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.2514662691653911</v>
+        <v>-0.2568669142054034</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.003875775356505073</v>
+        <v>-0.001610621079649377</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.431120110886873</v>
+        <v>-0.4365041634368581</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.4657826162786662</v>
+        <v>-0.4613701932844734</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; -0.03629</t>
+          <t>X &gt; -0.0363</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2662</v>
+        <v>2663</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.6789976168803875</v>
+        <v>-0.6858524553660672</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.8864490589227358</v>
+        <v>-0.8934489249449769</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.223954020527096</v>
+        <v>-1.230885484401128</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.505531662910236</v>
+        <v>-1.492552520511772</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.9207780370988345</v>
+        <v>-0.9076672327238953</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.5282097807745103</v>
+        <v>-0.5354148803632413</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.9298852751154456</v>
+        <v>-0.9369558954317085</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.664772776135834</v>
+        <v>-0.6720105570707986</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.5178619944799507</v>
+        <v>-0.525167626511795</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.1846767287230762</v>
+        <v>-0.1922273461932491</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.08182284461152989</v>
+        <v>0.07413976880159368</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.3250499303130781</v>
+        <v>0.3172755514650589</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.1866169716310395</v>
+        <v>-0.1942612468928289</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.366468270166898</v>
+        <v>-0.3603932435095416</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; -0.01903</t>
+          <t>X &gt; -0.01904</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2293</v>
+        <v>2295</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.059902264606151</v>
+        <v>-1.026291627581678</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.151058848899694</v>
+        <v>-1.161142505708476</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.76312998816352</v>
+        <v>-1.729600386338461</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.719757828622924</v>
+        <v>-1.686218490687565</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.302488339959204</v>
+        <v>-1.269232316471054</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.9382904003390351</v>
+        <v>-0.9284366628672416</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.390992675705149</v>
+        <v>-1.380797270949493</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.574007154162125</v>
+        <v>-1.563945238084109</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.176526397721965</v>
+        <v>-1.166846786931579</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.263026420630162</v>
+        <v>-1.253806262573811</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.7905974180526343</v>
+        <v>-0.7819162817645662</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.5577446289520651</v>
+        <v>-0.5492433846462319</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.8665405326128379</v>
+        <v>-0.8580347765200145</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.9849841662253027</v>
+        <v>-0.9565724670661098</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; -0.001772</t>
+          <t>X &gt; -0.001784</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.063381117921885</v>
+        <v>-1.050858828246263</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.8028798478908143</v>
+        <v>-0.7899700383147632</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.613765195153036</v>
+        <v>-1.600758063735434</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.535514142628735</v>
+        <v>-1.52253500023027</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.033893756036839</v>
+        <v>-1.0207829516619</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.256472619153215</v>
+        <v>-1.243429722858849</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.573592322811876</v>
+        <v>-1.588150482541039</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.909010105675122</v>
+        <v>-1.923536439665476</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.890190453422576</v>
+        <v>-1.904755032184283</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.930866272461273</v>
+        <v>-1.945660510797673</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.586014392034677</v>
+        <v>-1.601057561015487</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.62743071935067</v>
+        <v>-1.642454232726173</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.445067069116334</v>
+        <v>-1.460316034074374</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.584265211158289</v>
+        <v>-1.571119840179129</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.01549</t>
+          <t>X &gt; 0.01547</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1496</v>
+        <v>1498</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.994436324201992</v>
+        <v>-2.015490498619457</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.077733157392458</v>
+        <v>-1.100080847002431</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-2.071404259198637</v>
+        <v>-2.093256487076623</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.675016728720202</v>
+        <v>-1.697073896679754</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.281967551244144</v>
+        <v>-1.304512385945657</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.317193610867136</v>
+        <v>-1.339585164821216</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.801128924945807</v>
+        <v>-1.756742332598016</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-2.432830158895847</v>
+        <v>-2.423279061491144</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-2.791811594883832</v>
+        <v>-2.781848667228964</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-2.273648971783835</v>
+        <v>-2.265303764237537</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.24237828009074</v>
+        <v>-2.234298766548427</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.105167336352778</v>
+        <v>-2.097233516702545</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-2.288856248030882</v>
+        <v>-2.281137983536077</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-2.27016739068663</v>
+        <v>-2.219374576487247</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.03275</t>
+          <t>X &gt; 0.03273</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.932610019951134</v>
+        <v>-1.920087730275512</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.6969014931397126</v>
+        <v>-0.6839916835636615</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.609457861513704</v>
+        <v>-1.596450730096102</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.738048559794905</v>
+        <v>-1.72506941739644</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.7234067895348844</v>
+        <v>-0.7102959851599451</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.288777621448219</v>
+        <v>-1.275734725153853</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-2.150042831386585</v>
+        <v>-2.136976577086109</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-2.658206111281721</v>
+        <v>-2.690326497835748</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-3.105978410783571</v>
+        <v>-3.137786187697529</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-2.52693616901567</v>
+        <v>-2.559811692013461</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.906107923807049</v>
+        <v>-1.939685486820267</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.82460839352202</v>
+        <v>-1.858272477741508</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-2.71804651639647</v>
+        <v>-2.751237634025195</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-3.202746861869045</v>
+        <v>-3.172596970728996</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.05001</t>
+          <t>X &gt; 0.04999</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.986110248056654</v>
+        <v>-1.973587958381032</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.2154967133320653</v>
+        <v>-0.2025869037560142</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.174063277876797</v>
+        <v>-1.161056146459195</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.5928518589107838</v>
+        <v>-0.5798727165123196</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1.348997500988858</v>
+        <v>1.362108305363797</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.2701332783191503</v>
+        <v>-0.257090382024785</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.256783568308457</v>
+        <v>-1.243717314007981</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.949446110269214</v>
+        <v>-1.936265100973976</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-3.643388346575328</v>
+        <v>-3.688340831341165</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-2.96630433901548</v>
+        <v>-3.012839780925589</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-2.658492793838974</v>
+        <v>-2.705622968492897</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-2.676635220296191</v>
+        <v>-2.723779519719137</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-3.489670575097712</v>
+        <v>-3.536334917392324</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-3.520114278945599</v>
+        <v>-3.477136248134094</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.06727</t>
+          <t>X &gt; 0.06725</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-2.129537301287122</v>
+        <v>-2.1170150116115</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.5387819477302713</v>
+        <v>-0.5258721381542202</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.661452692172567</v>
+        <v>-1.648445560754965</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.8033975217193614</v>
+        <v>-0.7904183793208972</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.2593457464690232</v>
+        <v>0.2724565508439625</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-2.063299652059854</v>
+        <v>-2.050256755765488</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-3.458077037454409</v>
+        <v>-3.445010783153933</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-3.925260436235909</v>
+        <v>-3.912079426940672</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-5.077751192003724</v>
+        <v>-5.137544844016574</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-4.248831453535658</v>
+        <v>-4.310972707104767</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-3.062028027095565</v>
+        <v>-3.126258871004339</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-3.53538077858029</v>
+        <v>-3.59898790266746</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-2.998584600140774</v>
+        <v>-3.063602037170668</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-4.138487806558231</v>
+        <v>-4.078940997404281</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.08453</t>
+          <t>X &gt; 0.08451</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-3.220711047482702</v>
+        <v>-3.208188757807079</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-1.014102842265146</v>
+        <v>-1.001193032689095</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-1.772607912498103</v>
+        <v>-1.759600781080501</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-1.642354779890603</v>
+        <v>-1.629375637492139</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.1807759949627652</v>
+        <v>-0.1676651905878259</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-2.792424966338011</v>
+        <v>-2.779382070043646</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-4.87715868361029</v>
+        <v>-4.864092429309814</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-4.798887536937244</v>
+        <v>-4.785706527642006</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-5.861046555426228</v>
+        <v>-5.937597775073876</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-5.708685468134199</v>
+        <v>-5.787019800415159</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-4.17602569646705</v>
+        <v>-4.25764573231821</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-4.595667490404331</v>
+        <v>-4.676636319871342</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-4.187209529517403</v>
+        <v>-4.2697653223969</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-4.943964182130486</v>
+        <v>-4.865349025599819</v>
       </c>
     </row>
     <row r="29">
@@ -3410,101 +3410,101 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-2.96513643341752</v>
+        <v>-2.952614143741897</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-1.27482325392895</v>
+        <v>-1.261913444352899</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-3.084786300148174</v>
+        <v>-3.071779168730572</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-1.53943882791804</v>
+        <v>-1.526459685519576</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.4269166467638001</v>
+        <v>-0.4138058423888609</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-2.723814331689645</v>
+        <v>-2.71077143539528</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-4.69534050179211</v>
+        <v>-4.682274247491634</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-4.690825787366059</v>
+        <v>-4.677644778070821</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-5.105320477063245</v>
+        <v>-5.210325047801149</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-5.836682147139292</v>
+        <v>-5.942040534438341</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-3.546810847170306</v>
+        <v>-3.658309931301154</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-4.815447710184564</v>
+        <v>-4.924153548373162</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-4.158307162588713</v>
+        <v>-4.2697653223969</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-4.979145718860011</v>
+        <v>-4.873669403958068</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.1191</t>
+          <t>X &gt; 0.119</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-2.034722723879703</v>
+        <v>-2.02220043420408</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.8940027588622996</v>
+        <v>-0.8810929492862485</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.9830610679053748</v>
+        <v>-0.9700539364877727</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1.59367524513025</v>
+        <v>1.606654387528714</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>1.361064427611602</v>
+        <v>1.374175231986541</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-2.011218405314942</v>
+        <v>-1.998175509020577</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-4.54243530301536</v>
+        <v>-4.529369048714884</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-4.703808304243339</v>
+        <v>-4.690627294948101</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-3.383032989209902</v>
+        <v>-3.528367861256804</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-4.996725894860766</v>
+        <v>-5.13999844535801</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-3.50062451832364</v>
+        <v>-3.649560387006581</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-2.993245144947934</v>
+        <v>-3.144147096949453</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-2.937565675166731</v>
+        <v>-3.090346186321426</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-3.455050859792209</v>
+        <v>-3.31939199101096</v>
       </c>
     </row>
     <row r="31">
@@ -3514,101 +3514,101 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.6567036263324226</v>
+        <v>-0.8548997703717518</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.2274609127660696</v>
+        <v>-0.4335655382323225</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.6021601765556994</v>
+        <v>0.3911752721345891</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.4920764867551597</v>
+        <v>-0.6981117793989995</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1.418481890009403</v>
+        <v>1.202623057749207</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-1.957545560030034</v>
+        <v>-2.158539497981565</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-4.491258869139045</v>
+        <v>-4.682274247491634</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-4.550279002614431</v>
+        <v>-4.742838826237723</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-1.534999196591976</v>
+        <v>-1.958292527475948</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-3.81027448618714</v>
+        <v>-4.223509150253456</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-1.732947750646879</v>
+        <v>-2.166584346653494</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-1.887172665726943</v>
+        <v>-2.321101829459749</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.4142737497008895</v>
+        <v>-0.8655937364071349</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.07080323111095765</v>
+        <v>0.006553216586787869</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.1536</t>
+          <t>X &gt; 0.1535</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-2.23702806379972</v>
+        <v>-2.224505774124097</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-2.31014013830243</v>
+        <v>-2.297230328726378</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.8847347448445646</v>
+        <v>0.8977418762621667</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.01065314818896468</v>
+        <v>0.002325994209499527</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>1.502207688020917</v>
+        <v>1.515318492395856</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.2611880872750447</v>
+        <v>0.2742309835694101</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-1.362007168458774</v>
+        <v>-1.348940914158298</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-4.393293131342844</v>
+        <v>-4.380112122047606</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-1.377369940602065</v>
+        <v>-1.364171201647302</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-4.01179330168074</v>
+        <v>-4.265372049259206</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-1.123763120843684</v>
+        <v>-1.110305827133466</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-2.635771716075574</v>
+        <v>-2.622319427355464</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.7057245269029622</v>
+        <v>-0.9806146105657803</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.6853857507579377</v>
+        <v>-0.4664328303248269</v>
       </c>
     </row>
     <row r="33">
@@ -3618,49 +3618,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-4.548232840757926</v>
+        <v>-4.535710551082303</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-4.105011933174232</v>
+        <v>-4.092102123598181</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.3902915986749278</v>
+        <v>-0.3772844672573257</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.9449699729167449</v>
+        <v>-0.9319908305182807</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.1135281742902876</v>
+        <v>-0.1004173699153483</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.1839137634253731</v>
+        <v>0.1969566597197385</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-1.955614474394849</v>
+        <v>-1.942548220094373</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-5.162523900573611</v>
+        <v>-5.149342891278373</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-3.168729266207968</v>
+        <v>-3.155530527253205</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-5.039166213163149</v>
+        <v>-5.375312337281692</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-1.795643675411768</v>
+        <v>-1.78218638170155</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-3.140570862893924</v>
+        <v>-3.127118574173814</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-3.192051527478668</v>
+        <v>-3.547269427487223</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-3.966999969872155</v>
+        <v>-3.647204275344976</v>
       </c>
     </row>
     <row r="34">
@@ -3673,98 +3673,98 @@
         <v>107</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-4.829886918340819</v>
+        <v>-4.817364628665196</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-2.703142774295735</v>
+        <v>-2.690232964719684</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.2942731631353155</v>
+        <v>-0.2812660317177134</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>1.705138847976862</v>
+        <v>1.718117990375326</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>1.166717632904692</v>
+        <v>1.179828437279632</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.5295801313680144</v>
+        <v>0.5426230276623798</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.4448464140957356</v>
+        <v>0.4579126683962116</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-3.760654741695113</v>
+        <v>-3.747473732399875</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-3.821654627877415</v>
+        <v>-3.808455888922651</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-4.671779812905342</v>
+        <v>-4.658374685252511</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-2.072794819465912</v>
+        <v>-2.059337525755694</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-1.103832222868142</v>
+        <v>-1.090379934148032</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.3450720446916264</v>
+        <v>0.3586280910432293</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.3397860622844178</v>
+        <v>-0.3502156979825699</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.2054</t>
+          <t>X &gt; 0.2053</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-3.683914510686165</v>
+        <v>-3.671392221010542</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.5335833617456629</v>
+        <v>-0.5206735521696118</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>1.452500312610134</v>
+        <v>1.465507444027736</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>1.582753445217634</v>
+        <v>1.595732587616098</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-2.527096341283105</v>
+        <v>-2.513985536908166</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.1512979773849352</v>
+        <v>0.1643408736793006</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.06656426011265637</v>
+        <v>0.0796305144131324</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-7.543476281525997</v>
+        <v>-7.530295272230759</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-8.794952358184482</v>
+        <v>-8.781753619229718</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-9.645077543212409</v>
+        <v>-9.631672415559578</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-5.087926105625229</v>
+        <v>-5.074468811915011</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-1.482114376851221</v>
+        <v>-1.468662088131111</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.7118927973199334</v>
+        <v>-0.6983367509683305</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-1.652647655519836</v>
+        <v>-1.663077291217988</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that ROC Spread-5-14 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that ROC Spread-5-14 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3911,46 +3911,46 @@
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>5.83989501312336</v>
+        <v>5.852417302798983</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-4.105011933174232</v>
+        <v>-4.092102123598181</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-5.690356830247012</v>
+        <v>-5.67734969882941</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>5.154182016646203</v>
+        <v>5.167161159044667</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1.044332230145464</v>
+        <v>1.057443034520404</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>4.913202739289694</v>
+        <v>4.92624563558406</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>4.828469022017416</v>
+        <v>4.841535276317892</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>5.551761813712098</v>
+        <v>5.564942823007335</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>5.490761927529796</v>
+        <v>5.503960666484559</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>1.069208171073299</v>
+        <v>1.08261329872613</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.86445484675572</v>
+        <v>0.8779121404659378</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-1.482114376851221</v>
+        <v>-1.468662088131111</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-5.4737975592247</v>
+        <v>-5.460241512873097</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-7.605028607900792</v>
+        <v>-7.615458243598944</v>
       </c>
     </row>
     <row r="7">
@@ -3963,46 +3963,46 @@
         <v>103</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>2.846367505032738</v>
+        <v>2.858889794708361</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-3.61957503997035</v>
+        <v>-3.606665230394299</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-3.043569960159175</v>
+        <v>-3.030562828741573</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>5.824547250118229</v>
+        <v>5.837526392516693</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>2.373504675822758</v>
+        <v>2.386615480197698</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>4.612694186353949</v>
+        <v>4.625737082648314</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>5.498834255489442</v>
+        <v>5.511900509789918</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>5.031650856707941</v>
+        <v>5.044831866003179</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>6.912398543341169</v>
+        <v>6.925597282295932</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>5.091399571905477</v>
+        <v>5.104804699558308</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>4.886646247587898</v>
+        <v>4.900103541298115</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>1.037534259302262</v>
+        <v>1.050986548022372</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-2.295341710865941</v>
+        <v>-2.281785664514338</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-3.987367951405183</v>
+        <v>-3.997797587103335</v>
       </c>
     </row>
     <row r="8">
@@ -4015,46 +4015,46 @@
         <v>135</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>3.062117235345582</v>
+        <v>3.074639525021205</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1.450543622381325</v>
+        <v>1.463453431957376</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1.796415656525475</v>
+        <v>1.809422787943078</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>11.5562984187626</v>
+        <v>11.56927756116107</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>5.091951277764508</v>
+        <v>5.105062082139447</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>8.352356178443131</v>
+        <v>8.365399074737496</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>9.0083632019116</v>
+        <v>9.021429456212076</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>10.02266128461158</v>
+        <v>10.03584229390682</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>13.66536510213297</v>
+        <v>13.67856384108774</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>12.07449917636431</v>
+        <v>12.08790430401714</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>10.38826437056524</v>
+        <v>10.40172166427546</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>5.237462342725493</v>
+        <v>5.250914631445603</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>3.335726250299111</v>
+        <v>3.349282296650713</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>2.84470684183465</v>
+        <v>2.834277206136498</v>
       </c>
     </row>
     <row r="9">
@@ -4067,98 +4067,98 @@
         <v>165</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>6.900501073729423</v>
+        <v>6.913023363405046</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>2.864685036522737</v>
+        <v>2.877594846098788</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>4.894058754168576</v>
+        <v>4.907065885586178</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>12.29703915950333</v>
+        <v>12.3100183019018</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>6.304072489885712</v>
+        <v>6.317183294260651</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>7.813635639722598</v>
+        <v>7.826678536016964</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>9.547083740632139</v>
+        <v>9.560149994932615</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>12.71626397821428</v>
+        <v>12.72944498750952</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>15.68556712233499</v>
+        <v>15.69876586128976</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>14.22938133124646</v>
+        <v>14.24278645889929</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>11.60038558268647</v>
+        <v>11.61384287639669</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>7.998405103668262</v>
+        <v>8.011857392388372</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>6.972089886662744</v>
+        <v>6.985645933014347</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>6.615750612878422</v>
+        <v>6.60532097718027</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.2262</t>
+          <t>X &lt; -0.2261</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>199</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>4.79299384059405</v>
+        <v>4.805516130269673</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1.171369976373505</v>
+        <v>1.184279785949556</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2.284038958219128</v>
+        <v>2.29704608963673</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>7.941930281781403</v>
+        <v>7.954909424179867</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>4.388433689824808</v>
+        <v>4.401544494199747</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>5.690900753168606</v>
+        <v>5.703943649462971</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>9.123754975594821</v>
+        <v>9.136821229895297</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>11.16913439088368</v>
+        <v>11.18231540017891</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>15.12823500721394</v>
+        <v>15.1414337461687</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>13.27308469655787</v>
+        <v>13.2864898242107</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>11.56079368379808</v>
+        <v>11.5742509775083</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>7.575076338630943</v>
+        <v>7.588528627351053</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>6.652309164871973</v>
+        <v>6.665865211223576</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>6.399517934334199</v>
+        <v>6.389088298636047</v>
       </c>
     </row>
     <row r="11">
@@ -4171,46 +4171,46 @@
         <v>238</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>6.750259158781624</v>
+        <v>6.762781448457247</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>3.037845209682906</v>
+        <v>3.050755019258958</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>4.323648771993888</v>
+        <v>4.33665590341149</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>8.235414509643398</v>
+        <v>8.248393652041862</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>5.596152958436775</v>
+        <v>5.609263762811715</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>6.733931030606222</v>
+        <v>6.746973926900587</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>9.590373783922182</v>
+        <v>9.603440038222658</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>11.22403072127512</v>
+        <v>11.23721173057036</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>14.52437537290795</v>
+        <v>14.53757411186271</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>12.41374598619936</v>
+        <v>12.42715111385219</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>11.78882459465488</v>
+        <v>11.8022818883651</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>9.302199348638965</v>
+        <v>9.315651637359075</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>9.302112804920959</v>
+        <v>9.315668851272562</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>7.450993801062786</v>
+        <v>7.440564165364634</v>
       </c>
     </row>
     <row r="12">
@@ -4220,49 +4220,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>5.92950074789038</v>
+        <v>5.733369683751363</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1.092120683313219</v>
+        <v>1.26504073354468</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>4.281481367397639</v>
+        <v>4.441697920218211</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>6.562272134413739</v>
+        <v>6.714780206663718</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>4.59015916306916</v>
+        <v>4.747919224996586</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>5.604446978921032</v>
+        <v>5.759578968917388</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>7.311827956989248</v>
+        <v>7.460582895365512</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>8.995182192616348</v>
+        <v>9.136371394435919</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>11.44314287991075</v>
+        <v>11.57538923791313</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>10.59301769488282</v>
+        <v>10.72547044158327</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>11.10511024870145</v>
+        <v>11.2350549976088</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>7.196841076297773</v>
+        <v>7.340861721392692</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>8.210278221625281</v>
+        <v>8.349282296650713</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>7.384730736697264</v>
+        <v>7.503589375448669</v>
       </c>
     </row>
     <row r="13">
@@ -4275,46 +4275,46 @@
         <v>339</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>5.323670824332801</v>
+        <v>5.336193114008424</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>4.007082462105998</v>
+        <v>4.01999227168205</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>5.972095761409115</v>
+        <v>5.985102892826717</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>7.282289896966475</v>
+        <v>7.295269039364939</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>5.858912929681914</v>
+        <v>5.872023734056853</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>5.861369616660106</v>
+        <v>5.874412512954471</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>8.136517905287533</v>
+        <v>8.149584159588009</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>10.61918701388066</v>
+        <v>10.63236802317589</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>11.44314287991075</v>
+        <v>11.45634161886551</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>10.59301769488282</v>
+        <v>10.60642282253565</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>11.27322012277763</v>
+        <v>11.28667741648785</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>8.357750772748432</v>
+        <v>8.371203061468542</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>9.117437164753376</v>
+        <v>9.130993211104979</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>8.187217494079817</v>
+        <v>8.176787858381665</v>
       </c>
     </row>
     <row r="14">
@@ -4327,98 +4327,98 @@
         <v>395</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>4.974916110169765</v>
+        <v>4.987438399845388</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>5.135494395939695</v>
+        <v>5.148404205515746</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>6.512777588077284</v>
+        <v>6.525784719494887</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>7.908853505494903</v>
+        <v>7.921832647893368</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>6.104609505612615</v>
+        <v>6.117720309987554</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>5.895722329404222</v>
+        <v>5.908765225698588</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>8.595798738714223</v>
+        <v>8.608864993014699</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>9.647602681704875</v>
+        <v>9.660783691000113</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>10.59926102337067</v>
+        <v>10.61245976232543</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>8.989642167456665</v>
+        <v>9.003047295109496</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>10.8102052988353</v>
+        <v>10.82366259254552</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>8.312942886560464</v>
+        <v>8.326395175280574</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>8.399017389539615</v>
+        <v>8.412573435891218</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>7.382915937005777</v>
+        <v>7.372486301307625</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.1399</t>
+          <t>X &lt; -0.1398</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>462</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>4.000068173296519</v>
+        <v>4.012590462972142</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>4.552996724834422</v>
+        <v>4.565906534410473</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>5.889729749839574</v>
+        <v>5.902736881257177</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>7.102233964698144</v>
+        <v>7.115213107096608</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>4.615760801574034</v>
+        <v>4.628871605948973</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>3.830951657038611</v>
+        <v>3.843994553332976</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>6.560070753619144</v>
+        <v>6.57313700791962</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>7.824489086439378</v>
+        <v>7.837670095734616</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>8.412839849607721</v>
+        <v>8.426038588562484</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>7.779164881030013</v>
+        <v>7.792570008682844</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>8.873112855413737</v>
+        <v>8.886570149123955</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>7.392344497607645</v>
+        <v>7.405796786327755</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>8.054340968913827</v>
+        <v>8.06789701526543</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>6.788910786038606</v>
+        <v>6.778481150340454</v>
       </c>
     </row>
     <row r="16">
@@ -4431,46 +4431,46 @@
         <v>555</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>4.083138256366603</v>
+        <v>4.095660546042225</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>4.99408716592486</v>
+        <v>5.006996975500911</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>5.680299540409351</v>
+        <v>5.693306671826953</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>6.351093213557398</v>
+        <v>6.364072355955862</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>3.830690016503247</v>
+        <v>3.843800820878187</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>3.767771593858548</v>
+        <v>3.780814490152913</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>6.205560399108791</v>
+        <v>6.218626653409267</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>7.540178802129098</v>
+        <v>7.553359811424336</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>7.65935909612697</v>
+        <v>7.672557835081733</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>7.169594271459403</v>
+        <v>7.182999399112234</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>7.865741848042731</v>
+        <v>7.879199141752949</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>6.999224104487254</v>
+        <v>7.012676393207364</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>8.020410934983808</v>
+        <v>8.033966981335411</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>6.107970105097927</v>
+        <v>6.097540469399775</v>
       </c>
     </row>
     <row r="17">
@@ -4483,46 +4483,46 @@
         <v>690</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>3.73844573776104</v>
+        <v>3.750968027436663</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>5.025422849434463</v>
+        <v>5.038332659010514</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>6.2247570413886</v>
+        <v>6.237764172806202</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>6.210082637764209</v>
+        <v>6.223061780162674</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>4.512241132836969</v>
+        <v>4.525351937211909</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>4.519827998088864</v>
+        <v>4.53287089438323</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>6.174224715599202</v>
+        <v>6.187290969899678</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>6.431678997977109</v>
+        <v>6.444860007272347</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>6.66053418425858</v>
+        <v>6.673732923213343</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>5.52055392676688</v>
+        <v>5.533959054419711</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>6.040438283608722</v>
+        <v>6.05389557731894</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>5.350183759794731</v>
+        <v>5.363636048514842</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>6.23427697493679</v>
+        <v>6.247833021288393</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>5.46950555358989</v>
+        <v>5.459075917891738</v>
       </c>
     </row>
     <row r="18">
@@ -4535,46 +4535,46 @@
         <v>818</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>3.741280506195899</v>
+        <v>3.753802795871522</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>4.696944057045812</v>
+        <v>4.709853866621863</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>5.646818626732845</v>
+        <v>5.659825758150447</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>5.532572981834235</v>
+        <v>5.545552124232699</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>3.404909712972341</v>
+        <v>3.41802051734728</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>3.824601039441049</v>
+        <v>3.837643935735414</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>4.962361209699331</v>
+        <v>4.975427463999807</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>4.617427199670892</v>
+        <v>4.63060820896613</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>4.556427313488591</v>
+        <v>4.569626052443354</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>3.706302128460663</v>
+        <v>3.719707256113495</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>3.257050026636975</v>
+        <v>3.270507320347193</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>2.924685017723228</v>
+        <v>2.938137306443338</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>4.460420626827229</v>
+        <v>4.473976673178832</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>4.098895015338229</v>
+        <v>4.088465379640077</v>
       </c>
     </row>
     <row r="19">
@@ -4587,46 +4587,46 @@
         <v>1000</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>3.294984833482637</v>
+        <v>3.30750712315826</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>3.679419204550314</v>
+        <v>3.692329014126365</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>4.482155288372894</v>
+        <v>4.495162419790496</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>4.471531333995515</v>
+        <v>4.425786764975662</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>3.491951277764507</v>
+        <v>3.446720423797792</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>2.989393215480163</v>
+        <v>3.002436111774529</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>3.80465949820789</v>
+        <v>3.817725752508366</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>3.437476099426384</v>
+        <v>3.450657108721622</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>3.176476213244086</v>
+        <v>3.18967495219885</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>2.726351028216158</v>
+        <v>2.739756155868989</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>2.021597703898578</v>
+        <v>2.035054997608796</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.855980861244007</v>
+        <v>1.869433149964117</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.735726250299109</v>
+        <v>2.749282296650712</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.585447582575398</v>
+        <v>2.575017946877246</v>
       </c>
     </row>
     <row r="20">
@@ -4639,462 +4639,462 @@
         <v>1197</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2.385627568030223</v>
+        <v>2.398149857705846</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>2.859124847476309</v>
+        <v>2.87203465705236</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>4.048910019111574</v>
+        <v>4.061917150529176</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>4.478452626392603</v>
+        <v>4.442350801206786</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>3.571483441507198</v>
+        <v>3.53577994524462</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>2.782876924753353</v>
+        <v>2.795919821047718</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>3.700649473145234</v>
+        <v>3.71371572744571</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>2.732212941531657</v>
+        <v>2.745393950826895</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>2.838297432960047</v>
+        <v>2.85149617191481</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.821087870321428</v>
+        <v>1.834492997974259</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.115081413171765</v>
+        <v>1.128538706881983</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.4811270600744209</v>
+        <v>0.4945793487945309</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.564631847625762</v>
+        <v>1.578187893977365</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.563726613486004</v>
+        <v>1.553296977787852</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; -0.03629</t>
+          <t>X &lt; -0.0363</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1502</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.229965935109178</v>
+        <v>1.2424882247848</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.879030620017261</v>
+        <v>1.891940429593312</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>2.348523615548331</v>
+        <v>2.361530746965933</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>2.915801634553247</v>
+        <v>2.890692060767051</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.882896683889676</v>
+        <v>1.858222428114168</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.248248075666581</v>
+        <v>1.261290971960946</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>2.029027008194575</v>
+        <v>2.042093262495051</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.495265713274584</v>
+        <v>1.508446722569822</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.301110034815324</v>
+        <v>1.314308773770087</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.7172964343413284</v>
+        <v>0.7307015619941595</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.2462315254698169</v>
+        <v>0.2596888191800346</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.1854305901541267</v>
+        <v>-0.1719783014340166</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.7258727216706191</v>
+        <v>0.739428768022222</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.9755940539469066</v>
+        <v>0.9651644182487544</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; -0.01903</t>
+          <t>X &lt; -0.01904</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1871</v>
+        <v>1870</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.319895013123357</v>
+        <v>1.279083969465646</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.658061706100042</v>
+        <v>1.670971515676094</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2.307380438712897</v>
+        <v>2.266997287161992</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.307722920187103</v>
+        <v>2.267283259166767</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.799594249437405</v>
+        <v>1.759257699456384</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.402220580525594</v>
+        <v>1.391740924608762</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>2.012302469880787</v>
+        <v>2.002217731117995</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2.186487323370805</v>
+        <v>2.176860317277779</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.751355956696791</v>
+        <v>1.741546609952856</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.863283150076121</v>
+        <v>1.854194658542781</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.28439834526683</v>
+        <v>1.275161949480463</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.9980973764765082</v>
+        <v>0.9886844868625104</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.379553080870998</v>
+        <v>1.370672670982266</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.468932350079413</v>
+        <v>1.435980513722164</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; -0.001772</t>
+          <t>X &lt; -0.001784</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>2249</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.9227107481130048</v>
+        <v>0.9115451668048919</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.8883302772119208</v>
+        <v>0.8768419757806996</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.494790763426337</v>
+        <v>1.482944512063995</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.472220560362224</v>
+        <v>1.460403145004229</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.047506833320064</v>
+        <v>1.035759549931534</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.280900552074208</v>
+        <v>1.269102778441201</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.596344691627188</v>
+        <v>1.609410945927664</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.840588593868368</v>
+        <v>1.853769603163606</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1.868517120313896</v>
+        <v>1.88171585926866</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>1.90767606156431</v>
+        <v>1.921081189217141</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>1.613994324618901</v>
+        <v>1.627451618329118</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>1.648377481964332</v>
+        <v>1.661829770684442</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1.494908108902933</v>
+        <v>1.508464155254536</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>1.566772615923547</v>
+        <v>1.556342980225395</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.01549</t>
+          <t>X &lt; 0.01547</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2668</v>
+        <v>2667</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.134085987942612</v>
+        <v>1.146608277618235</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.7771429489806536</v>
+        <v>0.7900527585567048</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.263592414121398</v>
+        <v>1.276599545539</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.077770471121958</v>
+        <v>1.090749613520423</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.8597415399367989</v>
+        <v>0.8728523443117382</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.915807602891185</v>
+        <v>0.9288504991855504</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.226698478717637</v>
+        <v>1.202283473647796</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.546621526712748</v>
+        <v>1.543570494548398</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.78547171549296</v>
+        <v>1.782550842712531</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>1.497565421019758</v>
+        <v>1.495061742670643</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>1.480218393553756</v>
+        <v>1.477837149839772</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>1.402157772788236</v>
+        <v>1.399729362937499</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>1.506640793027749</v>
+        <v>1.504512892826192</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1.456512050341516</v>
+        <v>1.430286038365814</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.03275</t>
+          <t>X &lt; 0.03273</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>3012</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.7537452450650406</v>
+        <v>0.7486301768190771</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.4193500157816814</v>
+        <v>0.4141934363753137</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.7056896520063631</v>
+        <v>0.7003986162739011</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.7879180981434786</v>
+        <v>0.7826089296648533</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.400511330850108</v>
+        <v>0.395277670862491</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.6499308855764241</v>
+        <v>0.644639164196569</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>1.015150866069767</v>
+        <v>1.009727080088851</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1.17877756024977</v>
+        <v>1.191958569545008</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1.383381923735463</v>
+        <v>1.396580662690226</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>1.164066831669018</v>
+        <v>1.177471959321849</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.9261129761429387</v>
+        <v>0.9395702698531565</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.8940950710713764</v>
+        <v>0.9075473597914865</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>1.237452677921958</v>
+        <v>1.251008724273561</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1.387572416572745</v>
+        <v>1.377142780874593</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.05001</t>
+          <t>X &lt; 0.04999</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>3283</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.5460753576015662</v>
+        <v>0.5424811131909593</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.1972075864365976</v>
+        <v>0.1936121621161035</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.3967130341951091</v>
+        <v>0.3930291976364373</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.2698613884861985</v>
+        <v>0.2662226814638586</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.2519318628319667</v>
+        <v>-0.2554490222110317</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.2143551637297847</v>
+        <v>0.210713652857919</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.5117240536281074</v>
+        <v>0.5079845044109561</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.6705555998832864</v>
+        <v>0.666735062436608</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.157834726798768</v>
+        <v>1.171033465753531</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.9778283355570068</v>
+        <v>0.9912334632098379</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.8949147919278246</v>
+        <v>0.9083720856380424</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.898838004101151</v>
+        <v>0.9122902928212611</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>1.118242241770325</v>
+        <v>1.131798288121928</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>1.093824067497728</v>
+        <v>1.083394431799576</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.06727</t>
+          <t>X &lt; 0.06725</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>3483</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.4291977829418911</v>
+        <v>0.4265603372685689</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.2372064675136514</v>
+        <v>0.2345454408717274</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.4026422960089988</v>
+        <v>0.399913536645343</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.2618608782682799</v>
+        <v>0.2591773233085348</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.05465925252067194</v>
+        <v>0.05200788082026264</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.5400388395834668</v>
+        <v>0.5372611261176274</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.8442691422951398</v>
+        <v>0.8413986362960202</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.9098275206150177</v>
+        <v>0.9069142843817914</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1.164647330097381</v>
+        <v>1.177846069052144</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>1.003583299246884</v>
+        <v>1.016988426899715</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.7701190935052438</v>
+        <v>0.7835763872154615</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.8619240136987969</v>
+        <v>0.875376302418907</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.7574890984185529</v>
+        <v>0.7710451447701558</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.9497886678467182</v>
+        <v>0.9393590321485661</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.08453</t>
+          <t>X &lt; 0.08451</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>3620</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.4980146712430198</v>
+        <v>0.4959307169849367</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.2799853089658697</v>
+        <v>0.2779006335013534</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.3414986705740048</v>
+        <v>0.339381317901605</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.3489155391942944</v>
+        <v>0.3467999110972073</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.1292132153852634</v>
+        <v>0.1271371373270824</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.5522866445248908</v>
+        <v>0.5501037904938286</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.8970372943967888</v>
+        <v>0.8947550181074888</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.8595755469401993</v>
+        <v>0.8572851120356262</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1.047194445288291</v>
+        <v>1.060393184243054</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>1.025798542028312</v>
+        <v>1.039203669681143</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.793420908318474</v>
+        <v>0.8068782020286918</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.8554283750561638</v>
+        <v>0.8688806637762738</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.7942897862107117</v>
+        <v>0.8078458325623146</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.8782652621334037</v>
+        <v>0.8678356264352516</v>
       </c>
     </row>
     <row r="29">
@@ -5107,98 +5107,98 @@
         <v>3746</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.3442914959371066</v>
+        <v>0.3427387377128568</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.2659901990219353</v>
+        <v>0.2644126645712817</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.418807710002568</v>
+        <v>0.4171776643546679</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.2703724928366782</v>
+        <v>0.2687848530437265</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.1466325260973989</v>
+        <v>0.1450620821394466</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.4320826498451709</v>
+        <v>0.4304435804328506</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.6822949398945681</v>
+        <v>0.6805859446108258</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.6570169429928612</v>
+        <v>0.655300823693608</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.7294927642318072</v>
+        <v>0.7426915031865704</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.8136975311526271</v>
+        <v>0.8271026588054582</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.5555539238665403</v>
+        <v>0.5690112175767581</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.6967176471489793</v>
+        <v>0.7101699358690894</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.62349987549932</v>
+        <v>0.6370559218509229</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.6863552173858594</v>
+        <v>0.6759255816877072</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.1191</t>
+          <t>X &lt; 0.119</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>3843</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.181886355114699</v>
+        <v>0.1807302950953513</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.1948062014061804</v>
+        <v>0.1936121621161035</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.1518865119963309</v>
+        <v>0.150694691179126</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.04157967768581017</v>
+        <v>-0.04271905083555083</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.01985319441437383</v>
+        <v>-0.02101018196245263</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.2918639567025352</v>
+        <v>0.2906316395956523</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.5335876979997707</v>
+        <v>0.5322901218191589</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.5231383424656784</v>
+        <v>0.5218329672023785</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.4361171187866262</v>
+        <v>0.4493158577413894</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.5748027586351085</v>
+        <v>0.5882078862879396</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.448113446807767</v>
+        <v>0.4615707405179847</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.4044325916629603</v>
+        <v>0.4178848803830704</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.4005193806660046</v>
+        <v>0.4140754270176075</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.416048675471572</v>
+        <v>0.4056190397734198</v>
       </c>
     </row>
     <row r="31">
@@ -5208,101 +5208,101 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3925</v>
+        <v>3924</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.04979667470355764</v>
+        <v>0.06231896437918039</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.1305515366807626</v>
+        <v>0.1434613462568137</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.029381446743173</v>
+        <v>0.04238857816077513</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.1226097033228015</v>
+        <v>0.1355888457212657</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.005393232957992211</v>
+        <v>0.01850403733293149</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.2404245370997273</v>
+        <v>0.2534674333940927</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.4243742205716217</v>
+        <v>0.4374404748720977</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.404355080318112</v>
+        <v>0.4175360896133498</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.2414443661103363</v>
+        <v>0.2687779083660331</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.3849497543308118</v>
+        <v>0.4127429040850927</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.2566295510323329</v>
+        <v>0.2844943452132753</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.2655350013714042</v>
+        <v>0.2933882977724807</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.1764905815093059</v>
+        <v>0.2045320418087115</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.1204794297091496</v>
+        <v>0.1244572944817222</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.1536</t>
+          <t>X &lt; 0.1535</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>3972</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.1183145677860011</v>
+        <v>0.1176277806632342</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.2280702069915534</v>
+        <v>0.227335345010566</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.02273242555580879</v>
+        <v>0.02204384909465062</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.0912923219394699</v>
+        <v>0.09058781613966715</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.01905032251061556</v>
+        <v>0.0183568798273086</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.1040022172402857</v>
+        <v>0.1032908126292398</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.2090860575640221</v>
+        <v>0.2083468236675259</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.3343314453383428</v>
+        <v>0.3335544930274708</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.2118058559214901</v>
+        <v>0.2110585999975925</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.3430596341547627</v>
+        <v>0.3564647618075938</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.2028461307800313</v>
+        <v>0.2020907298684875</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.2766253728250732</v>
+        <v>0.2758514736489914</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.1836617991409994</v>
+        <v>0.1972178454926024</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.1564445614273566</v>
+        <v>0.1460149257292045</v>
       </c>
     </row>
     <row r="33">
@@ -5315,46 +5315,46 @@
         <v>4021</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.1733937313901208</v>
+        <v>0.1728538107354822</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.262233724394008</v>
+        <v>0.2616562490140808</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.07941943468934909</v>
+        <v>0.07888331546812566</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.1239176765506755</v>
+        <v>0.1233714912788244</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.09567613497831928</v>
+        <v>0.09513159554560957</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.1087176069357056</v>
+        <v>0.108172391883798</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.2114917963445322</v>
+        <v>0.2109199899648999</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.3046729185118764</v>
+        <v>0.3040732577899519</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.257460553288837</v>
+        <v>0.256871771284338</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.3270470262275893</v>
+        <v>0.3404521538804204</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.210906505489838</v>
+        <v>0.2103222111310501</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.2593382350316205</v>
+        <v>0.258741951555379</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.2618640269715797</v>
+        <v>0.2754200733231826</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.2628910046097204</v>
+        <v>0.2524613689115682</v>
       </c>
     </row>
     <row r="34">
@@ -5364,101 +5364,101 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4057</v>
+        <v>4058</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.1355543087826589</v>
+        <v>0.1351488183971128</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.1835110454445896</v>
+        <v>0.1830821515860919</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.07239074665986323</v>
+        <v>0.07198616232754063</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.04394515081553863</v>
+        <v>0.04354829206896227</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.05997882326377635</v>
+        <v>0.05957400739147545</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.1003403249512687</v>
+        <v>0.09992750380601478</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.1274941438771862</v>
+        <v>0.127073845989301</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.2152757548534154</v>
+        <v>0.2148303370680864</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.2417642486946079</v>
+        <v>0.2413116738331098</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.2671537861575501</v>
+        <v>0.2666887014130523</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.1994302162138553</v>
+        <v>0.1989801391995414</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.1738177668857972</v>
+        <v>0.1733740366636312</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.1371062404420442</v>
+        <v>0.1366683523294512</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.1296920982273662</v>
+        <v>0.1299711257831078</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.2054</t>
+          <t>X &lt; 0.2053</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4080</v>
+        <v>4081</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.08413314326425336</v>
+        <v>0.08381284098494035</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.1227495526517686</v>
+        <v>0.1224104588596688</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.03446304148070567</v>
+        <v>0.03414310943758636</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.05580036569730851</v>
+        <v>0.05547581025346915</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.1420857849789883</v>
+        <v>0.141736898765366</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.1105282448343772</v>
+        <v>0.1101886184998975</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.137054898256828</v>
+        <v>0.1367081399839023</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.2706625898816029</v>
+        <v>0.2702803042195541</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.3211518558389415</v>
+        <v>0.3207566947343352</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.3416301663160652</v>
+        <v>0.341224944118693</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.2486611376482699</v>
+        <v>0.2482773286567976</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.1744032032332257</v>
+        <v>0.1740376074708578</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.1600340180031097</v>
+        <v>0.1596693618148493</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.1540750335557917</v>
+        <v>0.154287733694197</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/roc/roc_spread_5_14.xlsx
+++ b/workspaces/btc_daily_14days/roc/roc_spread_5_14.xlsx
@@ -568,521 +568,521 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.2865</t>
+          <t>X ≈ -0.2862</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-10.34290863916792</v>
+        <v>-4.875847250107384</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-1.455644738805205</v>
+        <v>-1.706730220069772</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>8.648091506886324</v>
+        <v>12.14730443005361</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>8.779588458850377</v>
+        <v>12.27931719348409</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>8.244840600364256</v>
+        <v>11.79434842389599</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>3.290716329282368</v>
+        <v>7.316800150073782</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>8.461106525737222</v>
+        <v>12.01181469935365</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>2.741346370121448</v>
+        <v>6.794652281398086</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>13.19451949840241</v>
+        <v>16.27154978895447</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>22.86472790415152</v>
+        <v>24.96706894457353</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>22.66577649978042</v>
+        <v>20.01078361298197</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>12.18457217515881</v>
+        <v>10.55469494616502</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>11.7675013878959</v>
+        <v>10.16220451537814</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>11.99607057845619</v>
+        <v>15.1755881350175</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.2693</t>
+          <t>X ≈ -0.269</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>3.756759782693031</v>
+        <v>0.8203058421914307</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>17.73070747357002</v>
+        <v>19.18368610125497</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>17.3411785632404</v>
+        <v>15.47118174934033</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>29.94390273037373</v>
+        <v>28.90446146960763</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>13.82425636748257</v>
+        <v>11.79402194526201</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>20.36200935515063</v>
+        <v>18.72261023251626</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>20.28249468485792</v>
+        <v>18.66669363726402</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>26.0618379706409</v>
+        <v>24.86293654475981</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>35.37074782117324</v>
+        <v>34.81977648652306</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>34.5304971239938</v>
+        <v>34.00543319216</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>28.08916015222421</v>
+        <v>30.47901760856153</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>18.7601813767485</v>
+        <v>20.54968377226671</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>21.46900557647702</v>
+        <v>23.49220844071677</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>24.82501794687582</v>
+        <v>23.74701670644543</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.252</t>
+          <t>X ≈ -0.2517</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>30</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>24.10709682906593</v>
+        <v>24.07821465432219</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>9.213782630189243</v>
+        <v>9.212674045746112</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>18.79478678108523</v>
+        <v>18.79477511553937</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>15.6035995303498</v>
+        <v>15.60321706761771</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>11.74512359431053</v>
+        <v>11.79363011356832</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>5.39132411091159</v>
+        <v>5.415263380739709</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>11.96317408103384</v>
+        <v>12.01115789120868</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>24.81310936690419</v>
+        <v>24.86238436960951</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>24.75833246982963</v>
+        <v>24.83158193111358</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>23.91558102510017</v>
+        <v>24.01489266480274</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>17.05544490189253</v>
+        <v>17.15531139891894</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>20.4258717957205</v>
+        <v>20.54953257368229</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>23.34345517491489</v>
+        <v>23.49212224824038</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>23.57501794687877</v>
+        <v>23.74701670644239</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.2348</t>
+          <t>X ≈ -0.2345</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-5.405278070659293</v>
+        <v>-3.926738662008169</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-7.012075235934766</v>
+        <v>-5.505257851917712</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-10.34092326153933</v>
+        <v>-8.748912586763325</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-13.14807596808507</v>
+        <v>-11.47219101188161</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-4.884235583020065</v>
+        <v>-3.41048495863631</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-4.588723993780199</v>
+        <v>-3.139135077870662</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>7.069508225450541</v>
+        <v>8.207982478175587</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>3.668022406075991</v>
+        <v>4.891907518881688</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>12.42044009391877</v>
+        <v>13.41685252681612</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>8.63648334333638</v>
+        <v>9.743140478103541</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>11.37325969520207</v>
+        <v>12.39678479518544</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>5.531257112271881</v>
+        <v>6.746784002081142</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>5.112663794431469</v>
+        <v>6.353479999369839</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>5.339723829228845</v>
+        <v>6.604159563588063</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.2175</t>
+          <t>X ≈ -0.2172</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>16.69382300107984</v>
+        <v>15.85779474827851</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>12.53642637491795</v>
+        <v>11.66078610647893</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>14.70257518994718</v>
+        <v>13.89504477152833</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>9.720380385176377</v>
+        <v>8.777654722259399</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>11.74451982105675</v>
+        <v>10.91780705613284</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>12.04422271836472</v>
+        <v>11.19276147071686</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>11.96250685054218</v>
+        <v>11.13483450778614</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>11.49908012782563</v>
+        <v>10.67242566703187</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>11.44099211864378</v>
+        <v>10.63810121115609</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>8.03360898660361</v>
+        <v>7.189153713633765</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>12.95559669724882</v>
+        <v>12.24634537670016</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>18.1190611152055</v>
+        <v>17.56829106083834</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>22.83060095483656</v>
+        <v>22.43959041760299</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>12.80578717764764</v>
+        <v>12.16806933802166</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.2002</t>
+          <t>X ≈ -0.2</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.1009632759000141</v>
+        <v>1.830275675147796</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-8.826952940354559</v>
+        <v>-6.248146944814557</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>5.022163119961348</v>
+        <v>6.364001108501121</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-1.971668370159129</v>
+        <v>-0.01033280889847532</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.1332932049185374</v>
+        <v>1.670909862539439</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.1634070787884241</v>
+        <v>-0.2259137421517465</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-4.674639277684236</v>
+        <v>-4.62673082024844</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-2.764985083033217</v>
+        <v>-2.92254253192602</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-5.204571714136186</v>
+        <v>-7.302546139397748</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1.080878939940824</v>
+        <v>-1.612038823256128</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>8.014144307444795</v>
+        <v>4.700465705261131</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-3.847847154026816</v>
+        <v>-6.103950208879986</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>2.872246082259544</v>
+        <v>2.192952189733646</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>7.860732232591538</v>
+        <v>8.964408010791736</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.183</t>
+          <t>X ≈ -0.1828</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>3.438235837856126</v>
+        <v>2.027041674622687</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>17.04097361029737</v>
+        <v>16.76339130457107</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>13.27085824842835</v>
+        <v>12.748372352798</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>10.02291504029764</v>
+        <v>9.25403317944513</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>11.17987781509914</v>
+        <v>10.58269605634091</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>6.405375134421853</v>
+        <v>7.228895483434499</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>11.39785116784529</v>
+        <v>12.61474036914586</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>17.70340947209416</v>
+        <v>19.4141663825103</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>10.87625987877932</v>
+        <v>13.93482357655734</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>10.03031448744696</v>
+        <v>13.11571792723527</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>11.52211467275326</v>
+        <v>14.73204116409842</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>13.25383282520078</v>
+        <v>16.61155913641259</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>12.83733508501233</v>
+        <v>14.40319100479218</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>11.37162811636876</v>
+        <v>11.01974397917117</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.1658</t>
+          <t>X ≈ -0.1656</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>56</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>2.864754702988769</v>
+        <v>2.835705905090002</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>11.94056837227141</v>
+        <v>11.93950021947031</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>9.768994059246559</v>
+        <v>9.76893155261692</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>11.68233210982596</v>
+        <v>11.68193734613243</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>7.585942663876502</v>
+        <v>7.63442108667126</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>6.102926133053941</v>
+        <v>6.126870771692225</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>11.36698418115913</v>
+        <v>11.41496640113897</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>3.771924570316877</v>
+        <v>3.821111861909266</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>5.495526014846561</v>
+        <v>5.568705262245224</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.7031889482184823</v>
+        <v>-0.6039536277039588</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>8.013719287466898</v>
+        <v>8.113563248818892</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>8.050564677959606</v>
+        <v>8.174204105828487</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>4.062317037367734</v>
+        <v>4.210967788062682</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>2.503589375447866</v>
+        <v>2.675588135016149</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.1484</t>
+          <t>X ≈ -0.1483</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-1.730368611160785</v>
+        <v>-1.03766543862811</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.126776341976267</v>
+        <v>1.781962204457862</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2.221127709235056</v>
+        <v>2.855645763645228</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>2.351441834165726</v>
+        <v>2.985790449776857</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-4.139924483921988</v>
+        <v>-4.835992448386783</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-8.312018908536764</v>
+        <v>-8.967119408241892</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-5.419716563688716</v>
+        <v>-6.09478122089854</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-2.907261161814731</v>
+        <v>-3.625084632341981</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-4.459329601747065</v>
+        <v>-5.131455686889169</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.6546164748064811</v>
+        <v>-0.07931541241465112</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.532341956568224</v>
+        <v>-3.222053288399763</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>1.976933777778925</v>
+        <v>1.245008437314155</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>6.034024472357821</v>
+        <v>5.261062067134503</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>3.276510484191363</v>
+        <v>2.57054611820795</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.1312</t>
+          <t>X ≈ -0.1311</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>93</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>4.490398031670018</v>
+        <v>3.389907338988195</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>7.172898710799032</v>
+        <v>7.171749291677173</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>4.636761050394966</v>
+        <v>4.63662103649694</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.623149487519775</v>
+        <v>2.622654621401054</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.05727423548443511</v>
+        <v>1.063780623543906</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>3.458504751402742</v>
+        <v>4.555358066057067</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>4.447594943401889</v>
+        <v>5.568754824942701</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>6.12938128436349</v>
+        <v>7.25208675891799</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>3.922786606125477</v>
+        <v>5.069757608583117</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>4.14931105551036</v>
+        <v>5.32265087607373</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>2.871664676187834</v>
+        <v>4.04588123009637</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>5.056530517134348</v>
+        <v>6.254843538710631</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>7.862998813429385</v>
+        <v>9.086625392109475</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>2.714802893113564</v>
+        <v>3.962070469884772</v>
       </c>
     </row>
     <row r="16">
@@ -1092,101 +1092,101 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>2.322897541981931</v>
+        <v>2.701467773641895</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>5.14716931591456</v>
+        <v>4.843020411635877</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>8.446818801335361</v>
+        <v>8.171199163509421</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>5.624644785833709</v>
+        <v>5.326528117935823</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>7.307096489635903</v>
+        <v>7.074335024571631</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>7.606108152566094</v>
+        <v>7.348756475738668</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>6.044682994431085</v>
+        <v>5.800213698989076</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.882667207840321</v>
+        <v>1.611748073218855</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>2.562299128814914</v>
+        <v>2.320797467809271</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.245079311669585</v>
+        <v>-1.482692178198945</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.449783043110592</v>
+        <v>-1.686896347769569</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.415463970910942</v>
+        <v>-1.628865352075735</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.095155066049784</v>
+        <v>-1.27809732040437</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>2.834277206136669</v>
+        <v>2.702240587040926</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.09669</t>
+          <t>X ≈ -0.09668</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>128</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>3.751668818198439</v>
+        <v>3.722673971690838</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>2.925554612927343</v>
+        <v>2.924426967873138</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>2.532244212637089</v>
+        <v>2.532142943230738</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.884349909040473</v>
+        <v>1.883897123398313</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-2.54646606192852</v>
+        <v>-2.498084820120596</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.08789832380452367</v>
+        <v>0.1117997012877368</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.556244053705178</v>
+        <v>-1.508348779556357</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-5.142171756560863</v>
+        <v>-5.093046773532116</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-6.764450608454545</v>
+        <v>-6.691346343313839</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-6.054119362235333</v>
+        <v>-5.954930633473467</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-11.72411144197289</v>
+        <v>-11.62433903798302</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-10.1312980032405</v>
+        <v>-10.0077062586604</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-5.087017396379736</v>
+        <v>-4.938383977856219</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-3.299982053122577</v>
+        <v>-3.127983293555914</v>
       </c>
     </row>
     <row r="18">
@@ -1196,881 +1196,881 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.340106153770627</v>
+        <v>1.285312556105886</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.8298308535303391</v>
+        <v>-0.8330777860787961</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.677506683345598</v>
+        <v>-0.6847978760546454</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.5464646839571472</v>
+        <v>-0.5549519739858511</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>3.587727773394711</v>
+        <v>3.294362349068741</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.7515256570319835</v>
+        <v>-1.311449284149973</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.384818992500911</v>
+        <v>-1.914970878848756</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.851005252042192</v>
+        <v>-2.380091066214504</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-3.009260535192475</v>
+        <v>-3.502626576862319</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.663464107746194</v>
+        <v>-2.154785461593903</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-3.51495121508399</v>
+        <v>-3.987965020464088</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-2.932353252191362</v>
+        <v>-3.387704162077007</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-5.001075336306407</v>
+        <v>-5.413665242912366</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-4.22717985532055</v>
+        <v>-4.622548510947524</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.06219</t>
+          <t>X ≈ -0.06222</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>197</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-2.22269801028925</v>
+        <v>-2.250928097571489</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.299287121025579</v>
+        <v>-1.300270239064027</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.848646376486705</v>
+        <v>1.846408002836327</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>4.510980885108097</v>
+        <v>4.506670456065329</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>3.974978777494712</v>
+        <v>4.021776574906063</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.740765632010785</v>
+        <v>1.764757013998008</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>3.175837771040129</v>
+        <v>3.223818189669288</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.8348332944889876</v>
+        <v>-0.7856406867489412</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.131555745964704</v>
+        <v>1.204722875595898</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.757950982235648</v>
+        <v>-2.65873811328904</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-3.470021185942777</v>
+        <v>-3.370218130803615</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-6.480280010733111</v>
+        <v>-6.356680827013257</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-4.365212445923007</v>
+        <v>-4.216579924970922</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-3.633103880534151</v>
+        <v>-3.461105120967382</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ -0.04493</t>
+          <t>X ≈ -0.04498</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-3.290933212783145</v>
+        <v>-3.157214523684573</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.957369943065665</v>
+        <v>-1.787117447671058</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-4.313591254653339</v>
+        <v>-4.147357536411533</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-3.204492986371534</v>
+        <v>-3.036212786202597</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-4.720725705988833</v>
+        <v>-4.50663606536942</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-4.75013787511601</v>
+        <v>-4.562760255117695</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-4.509913035554256</v>
+        <v>-4.297421239833653</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-3.340669339985098</v>
+        <v>-3.121483981792245</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-4.711469373985459</v>
+        <v>-4.80090833994452</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-3.596639294423888</v>
+        <v>-3.653610455755128</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-3.146935100591101</v>
+        <v>-3.2012085048963</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-2.785852842346976</v>
+        <v>-2.815300713129346</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-2.551562808540908</v>
+        <v>-2.553875532338814</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.343014840007854</v>
+        <v>-1.318772767240226</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ -0.02767</t>
+          <t>X ≈ -0.02776</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.437266838750276</v>
+        <v>0.9908147714744899</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.7759988137839073</v>
+        <v>0.4824330574240037</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.879306635017869</v>
+        <v>1.169291889006338</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.2847715380296023</v>
+        <v>-1.129435165460549</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.3472019716232</v>
+        <v>0.8083052444237779</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.915631290415774</v>
+        <v>1.351475020158851</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.831022248082725</v>
+        <v>1.293885611425935</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>4.890462521531241</v>
+        <v>4.61315254327284</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>3.476608659258339</v>
+        <v>3.493901110920575</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>6.428217254604043</v>
+        <v>6.455422220547071</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>5.412858888500871</v>
+        <v>5.708345220364201</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>5.721245547050437</v>
+        <v>5.918001234660238</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>3.945304651189794</v>
+        <v>4.050051187211459</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>3.357626642529361</v>
+        <v>3.638615622433072</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ -0.01041</t>
+          <t>X ≈ -0.01054</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>379</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.9020943809501247</v>
+        <v>-0.6685871014024585</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-3.037571127150024</v>
+        <v>-3.037772917608663</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-2.380951019867162</v>
+        <v>-2.381018659541148</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-2.513705476746139</v>
+        <v>-2.251552689158778</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-2.525245464160626</v>
+        <v>-3.004360323397393</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.6639820784096102</v>
+        <v>0.6904000533081245</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.3325419849088931</v>
+        <v>-0.4227934025475832</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.2539353482744815</v>
+        <v>0.1657583611674767</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2.563581175876244</v>
+        <v>2.502224524516606</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>2.243799910505075</v>
+        <v>2.206103063349836</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>3.359177889857484</v>
+        <v>3.201717651041783</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>4.97738454390565</v>
+        <v>4.842997844870929</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>2.186743295971148</v>
+        <v>1.809317490866533</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2.150215836059367</v>
+        <v>2.0583623528819</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.006843</t>
+          <t>X ≈ 0.006695</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>418</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2.406122612469119</v>
+        <v>1.775989894790861</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.321384008130515</v>
+        <v>0.6697560688875939</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.1642243242193189</v>
+        <v>0.2774507208111956</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.897034361758152</v>
+        <v>-0.7843427823048614</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.003972682386617521</v>
+        <v>0.3951844750855926</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.8988343830032903</v>
+        <v>-0.5239148335105099</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.9839624648726968</v>
+        <v>-0.5830040263040033</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.1325927853715783</v>
+        <v>0.1475439845236792</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1.238513545081119</v>
+        <v>1.434054004472813</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.8001447365083934</v>
+        <v>-0.6977386240995855</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.6683092473298231</v>
+        <v>0.5335276269288798</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.01264713369125303</v>
+        <v>-0.126008984988438</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1.481289899642448</v>
+        <v>1.631943136294566</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.7520514397001818</v>
+        <v>0.6848157495061429</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.0241</t>
+          <t>X ≈ 0.02393</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>345</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-2.334329315722542</v>
+        <v>-2.073582093011971</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-2.490662891770278</v>
+        <v>-3.068898808558508</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-3.753595727072373</v>
+        <v>-4.043339212950151</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.603512054980257</v>
+        <v>-1.892404733091496</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-3.290400821035256</v>
+        <v>-3.536023477724882</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.552975184926922</v>
+        <v>-1.819078316809822</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.4859884662363925</v>
+        <v>-0.7220748697718378</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.530798788722088</v>
+        <v>-1.76676199555132</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.592295156793426</v>
+        <v>-1.803734604688117</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.281049733148713</v>
+        <v>-1.757997968111766</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-3.218904886915269</v>
+        <v>-3.121558705502991</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.895848235317253</v>
+        <v>-3.063391968138063</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.7100513255246454</v>
+        <v>-0.8498542425279823</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.9663222947033034</v>
+        <v>0.8484659818061573</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.04136</t>
+          <t>X ≈ 0.04115</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.745965216662718</v>
+        <v>-1.780327555109075</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-2.250777719690383</v>
+        <v>-2.273267811826976</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-3.013491404515861</v>
+        <v>-2.300968179421481</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-5.452240967875355</v>
+        <v>-4.907623037805649</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-7.455168989742766</v>
+        <v>-6.503276017508334</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-4.591027384341466</v>
+        <v>-3.664283310249829</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-5.044189381642951</v>
+        <v>-4.460080685946011</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-5.144504180610951</v>
+        <v>-4.364801211237619</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.345944137167358</v>
+        <v>-0.7253032321391046</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.085380790092806</v>
+        <v>-0.07854357766000675</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.5531442505792157</v>
+        <v>0.8202571512745322</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.9586175998387958</v>
+        <v>1.246070947462954</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.1960501656495239</v>
+        <v>0.11561890325207</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-2.181439617698402</v>
+        <v>-1.84121858767368</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.05862</t>
+          <t>X ≈ 0.05837</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.484501706865125</v>
+        <v>-0.285680810456121</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.899815745541872</v>
+        <v>1.353132820000347</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.5009417562893717</v>
+        <v>-0.261697487053894</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.138087993664918</v>
+        <v>-0.1298715600091427</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>5.077820788276419</v>
+        <v>3.852722412137489</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>5.857606952431034</v>
+        <v>4.623134162413976</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>6.262693415779708</v>
+        <v>5.564742406623068</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>4.801261750572444</v>
+        <v>3.60637233280692</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.253444851882001</v>
+        <v>0.5843250968044202</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>1.413793497345381</v>
+        <v>0.7555213916113246</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.271254540928894</v>
+        <v>-1.438668807168554</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.2606810661346728</v>
+        <v>0.1120352436292151</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-5.14835403894817</v>
+        <v>-5.258247061044095</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.424982053122747</v>
+        <v>-1.029102696541194</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.07588</t>
+          <t>X ≈ 0.07561</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>137</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2.223785657560683</v>
+        <v>2.220300661046693</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>1.365002953243646</v>
+        <v>1.325152014577753</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.206258735372373</v>
+        <v>0.2083404086124148</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2.547039326542802</v>
+        <v>2.516667718295395</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2.023305814204022</v>
+        <v>2.409951361060976</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.8502782535891882</v>
+        <v>1.245710139786858</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>2.200241020896854</v>
+        <v>3.029971008141061</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.4367015445886366</v>
+        <v>0.3743572258598675</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.954852527036813</v>
+        <v>-1.85239640517478</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>1.560893467013237</v>
+        <v>1.703337057805861</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>1.37451367947785</v>
+        <v>0.7692696029705388</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.6880076256253531</v>
+        <v>0.8274363403354315</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>1.734638769021302</v>
+        <v>1.89213242837014</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.9505294983782306</v>
+        <v>-0.7785307388116109</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.09316</t>
+          <t>X ≈ 0.09281</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-4.058075768071433</v>
+        <v>-4.079931420222387</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.1341942034261123</v>
+        <v>-0.1811988073816693</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>2.603913063565365</v>
+        <v>2.577517248813948</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-1.971612017464388</v>
+        <v>-0.4436288818328364</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.6508501515124365</v>
+        <v>1.413664102487544</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-3.007539656691748</v>
+        <v>-2.605102542267986</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-5.468710033927422</v>
+        <v>-5.815364930706103</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-5.145054726612848</v>
+        <v>-5.493796116286227</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-8.356068193544282</v>
+        <v>-7.892973449832432</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-5.271514343623785</v>
+        <v>-4.779794156631667</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-6.250675102367012</v>
+        <v>-4.9839346041678</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-3.853543313980367</v>
+        <v>-2.563563142393498</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-4.2697653223969</v>
+        <v>-2.958721068957303</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-4.837680465821194</v>
+        <v>-4.284479356548175</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.1104</t>
+          <t>X ≈ 0.1101</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-6.041203983650945</v>
+        <v>-4.593445158220348</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-2.526080448594776</v>
+        <v>-0.9682889100428369</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-10.04864024895922</v>
+        <v>-8.653693565024241</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-11.92710640223657</v>
+        <v>-11.6488095238095</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-6.349165697531973</v>
+        <v>-4.846391998094745</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-5.076296056969056</v>
+        <v>-3.531939812609188</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-5.189856453740227</v>
+        <v>-3.592595901834613</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-4.634548175653464</v>
+        <v>-3.016761995551356</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-10.79372931653601</v>
+        <v>-10.34540127135478</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-8.604489531179219</v>
+        <v>-8.044229852169764</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-3.687354810299652</v>
+        <v>-3.040036966372526</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-10.83304094382093</v>
+        <v>-10.2735368956743</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-8.184950495760873</v>
+        <v>-7.543694822238095</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-10.03322947580311</v>
+        <v>-9.377983293556092</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.1276</t>
+          <t>X ≈ 0.1273</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-5.495280187087928</v>
+        <v>-6.726979294766466</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-2.212625122915867</v>
+        <v>-3.490879271488659</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-5.020130964611091</v>
+        <v>-6.294255814020225</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>8.464045081721004</v>
+        <v>7.08864027538722</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>1.884595898544575</v>
+        <v>0.575294748893171</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-1.521043146803315</v>
+        <v>-2.766377563613204</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-4.07442888939147</v>
+        <v>-5.236672207055534</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-4.535281874691329</v>
+        <v>-5.702504967438834</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-8.19982657040724</v>
+        <v>-9.35393540790097</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-7.86683696536047</v>
+        <v>-8.972944711607518</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-8.061871815711427</v>
+        <v>-9.177085159143644</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-5.592960794048487</v>
+        <v>-6.709279867561854</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-9.709671376807144</v>
+        <v>-10.71889562545101</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-13.21510550991292</v>
+        <v>-14.08430859476095</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 0.1449</t>
+          <t>X ≈ 0.1445</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>4.652057703049138</v>
+        <v>4.632745317970191</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>7.059919973545895</v>
+        <v>5.090384559344976</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-1.645644615295076</v>
+        <v>-3.466618735092176</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-3.514455327449795</v>
+        <v>-5.377551020408106</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.05467316905921393</v>
+        <v>-1.78516750829889</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-11.94030414255108</v>
+        <v>-13.75727994866361</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-18.08505202526942</v>
+        <v>-19.94038501748088</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-6.201302449335451</v>
+        <v>-8.161319818680575</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-4.34715535841196</v>
+        <v>-6.157476101286733</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-4.05518541050116</v>
+        <v>-6.981304682101744</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-6.413704227223619</v>
+        <v>-9.226261456168388</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-1.109956071254011</v>
+        <v>-5.086462065742289</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.4031139715609129</v>
+        <v>-5.481619992306094</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>1.908351280210582</v>
+        <v>-3.191758803760116</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 0.1622</t>
+          <t>X ≈ 0.1618</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>4.567606223467372</v>
+        <v>4.352633273152229</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>2.977494945998906</v>
+        <v>4.730240501721873</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>4.644758069462313</v>
+        <v>6.297286827132631</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>2.748073397491126</v>
+        <v>4.466386554621849</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>6.2636034755145</v>
+        <v>7.898706041120938</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.5013228740664033</v>
+        <v>2.28913861876336</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.3955376992048514</v>
+        <v>2.228482529537878</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-2.119515575736806</v>
+        <v>-0.1981345445709266</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>3.900231714419043</v>
+        <v>5.647245787468719</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-1.003506713029864</v>
+        <v>0.9018485792027775</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.864200292413571</v>
+        <v>2.658492445392149</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-1.138828057113784</v>
+        <v>0.7558748690315582</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>6.562207708550282</v>
+        <v>8.203854197369715</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>8.881140395856839</v>
+        <v>10.41368337311055</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.1794</t>
+          <t>X ≈ 0.179</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-3.721197407802038</v>
+        <v>-5.141690772255444</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-8.146156177652216</v>
+        <v>-9.356446804779679</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.6549594024664813</v>
+        <v>-1.855447950989081</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-8.595819042291694</v>
+        <v>-6.988721804511286</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-3.802749839371131</v>
+        <v>-4.846391998094759</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.8026731070333284</v>
+        <v>-1.942027531907435</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-8.88442160032389</v>
+        <v>-7.265841515869738</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-9.203396945332408</v>
+        <v>-10.3632532236215</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-1.267340967830748</v>
+        <v>-2.505488990653035</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-7.4486185201769</v>
+        <v>-8.59247546620486</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.9806952353828251</v>
+        <v>-3.533458019004065</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-9.017146533167285</v>
+        <v>-11.37002812374448</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-14.8427027918861</v>
+        <v>-17.02834394504514</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-13.18173880987951</v>
+        <v>-19.41087803039814</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.1967</t>
+          <t>X ≈ 0.1962</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-9.002655160969134</v>
+        <v>-6.676778491553655</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-10.61384125403299</v>
+        <v>-8.259955576709508</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-6.660786551831514</v>
+        <v>-4.487026898357541</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>2.165090765669923</v>
+        <v>-0.1904761904761969</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>14.67027947344376</v>
+        <v>15.98694133523849</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1.924175242209287</v>
+        <v>3.759726854057483</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>1.839464882943119</v>
+        <v>-0.4675959018346489</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>10.06804841306946</v>
+        <v>11.56657133778204</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>14.35489234350317</v>
+        <v>15.69626539531189</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>13.50497354717331</v>
+        <v>14.87243681449691</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>8.952446301956599</v>
+        <v>10.50162970029413</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.2911722803988752</v>
+        <v>2.226463104325703</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>4.21884751404199</v>
+        <v>5.997971844428541</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>4.444583164268558</v>
+        <v>6.247016706443873</v>
       </c>
     </row>
   </sheetData>
@@ -2210,573 +2210,573 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.2952</t>
+          <t>X &gt; -0.2948</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4081</v>
+        <v>4092</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.1115950730355735</v>
+        <v>-0.1105990356056168</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.1957063298589361</v>
+        <v>0.1952101152982948</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.1807706754199927</v>
+        <v>0.1802896992539615</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.01785589348644123</v>
+        <v>-0.01779619697708767</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.06838726551352892</v>
+        <v>0.06704374928391132</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.01236518978871715</v>
+        <v>0.01175937438269159</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.03886078186257436</v>
+        <v>0.0376086195933425</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.001134231305435662</v>
+        <v>-4.652458987663977e-05</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.02707093849352304</v>
+        <v>0.02524595018943643</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.1209067066645773</v>
+        <v>0.1182050436635649</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.1258483374716732</v>
+        <v>0.1231193217837614</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.1740376074708578</v>
+        <v>0.1706090089015007</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.2576605426085834</v>
+        <v>0.2534079548609824</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.276806724137721</v>
+        <v>0.2719433926609227</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.2779</t>
+          <t>X &gt; -0.2776</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4062</v>
+        <v>4071</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.06373811642392724</v>
+        <v>-0.08601779942175369</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.2034305224499278</v>
+        <v>0.205021156085003</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.141164792653413</v>
+        <v>0.1185585989477005</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.05900592861554799</v>
+        <v>-0.08123009066405729</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.0301419151043234</v>
+        <v>0.006549178375813369</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.00296929363087628</v>
+        <v>-0.0259232235759228</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.0005342622372737083</v>
+        <v>-0.02415957683873415</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.01168310760088787</v>
+        <v>-0.03509655527661693</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.03451978593736271</v>
+        <v>-0.05855959651016462</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.01452251100917579</v>
+        <v>-0.009976273437665384</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.0204178512373403</v>
+        <v>0.02053004393675195</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.1178583468145149</v>
+        <v>0.1170433482081776</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.2038232762224581</v>
+        <v>0.2022940448214712</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.2219898818846318</v>
+        <v>0.195063869303155</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.2607</t>
+          <t>X &gt; -0.2603</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4030</v>
+        <v>4041</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.09407457616877934</v>
+        <v>-0.09274626001278818</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.06425611489760996</v>
+        <v>0.06412535099836703</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.004589000926664255</v>
+        <v>0.004582183577305443</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.2972424241707969</v>
+        <v>-0.2964171104136639</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.07938951479048484</v>
+        <v>-0.08095989932935055</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.1646763201224459</v>
+        <v>-0.1651105543561187</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.1615905714946066</v>
+        <v>-0.1629186949835244</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.2187185107035532</v>
+        <v>-0.219937187051201</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.315653424504994</v>
+        <v>-0.3174930492424082</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.2595497439822694</v>
+        <v>-0.2625034409625187</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.2024604995397254</v>
+        <v>-0.2055908733952734</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.03017002463905527</v>
+        <v>-0.03464663266827728</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.03496823066212329</v>
+        <v>0.02939193349336477</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.02663085010306077</v>
+        <v>0.02021640948770198</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.2434</t>
+          <t>X &gt; -0.2431</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4000</v>
+        <v>4011</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.2755833617080441</v>
+        <v>-0.273531307988371</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.004365333967079721</v>
+        <v>-0.004300592866606223</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.1363374824245227</v>
+        <v>-0.1359577785166621</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.416498738829695</v>
+        <v>-0.4153373361281893</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.1680733631087463</v>
+        <v>-0.1697750826718973</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.2063463233551985</v>
+        <v>-0.2068485793007397</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.2525263063885674</v>
+        <v>-0.2539738676551195</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.4064572197856151</v>
+        <v>-0.4075386945804453</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.5037083187125049</v>
+        <v>-0.5055938344357997</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.4408632247503874</v>
+        <v>-0.4440845636683122</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.3318947900504625</v>
+        <v>-0.3354405538164755</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.1835903382917508</v>
+        <v>-0.1886045923268469</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.1398454214197713</v>
+        <v>-0.146095952181625</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.1499820531227556</v>
+        <v>-0.1572465695471195</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.2261</t>
+          <t>X &gt; -0.2259</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3966</v>
+        <v>3976</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.2316071589585817</v>
+        <v>-0.2413727925480558</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.05571084774420143</v>
+        <v>0.04412332666728958</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.04885490136302906</v>
+        <v>-0.06013951435954823</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.3073525901169702</v>
+        <v>-0.3180058777148673</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.1276423203762747</v>
+        <v>-0.1412477070031883</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.168776771969803</v>
+        <v>-0.1810361981513537</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.3152971520977275</v>
+        <v>-0.3284629199951681</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.4413872014495723</v>
+        <v>-0.4541887492764189</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.6145053550285553</v>
+        <v>-0.6281505805735819</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.5186821312846632</v>
+        <v>-0.5337608404444794</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.4322415506401285</v>
+        <v>-0.447520002311208</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.2325829790681411</v>
+        <v>-0.2496555482635401</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.1848744968960503</v>
+        <v>-0.2033105292199338</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.1970445846406506</v>
+        <v>-0.2167659897331617</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.2089</t>
+          <t>X &gt; -0.2086</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3927</v>
+        <v>3938</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.3996977564226754</v>
+        <v>-0.3967228094478585</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.06823819874416159</v>
+        <v>-0.06797245434663068</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.1953549710246207</v>
+        <v>-0.1948010183879276</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.4069404653490594</v>
+        <v>-0.4057750759878473</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.2455476739581144</v>
+        <v>-0.2479628113706838</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.2900670648455446</v>
+        <v>-0.2907884356874106</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.4372310344768877</v>
+        <v>-0.439078791568484</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.559970910602047</v>
+        <v>-0.5615557751321134</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.734231456753335</v>
+        <v>-0.7368650468218618</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.6036170316151086</v>
+        <v>-0.608283631976974</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.565199455317412</v>
+        <v>-0.5700103233885159</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.4148376568569461</v>
+        <v>-0.4215910411903749</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.4134468275855383</v>
+        <v>-0.4218047486153864</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.3261788954960707</v>
+        <v>-0.3362743042214049</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.1916</t>
+          <t>X &gt; -0.1914</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3885</v>
+        <v>3892</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.4029273183742674</v>
+        <v>-0.4230439631712315</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.0264506092732546</v>
+        <v>0.005071745694870344</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.2517605720082585</v>
+        <v>-0.2723202624364589</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.3900244879997743</v>
+        <v>-0.4104488540675177</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.2467612357855629</v>
+        <v>-0.270642190353179</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.2949694880199729</v>
+        <v>-0.2915551972245751</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.3914212156314036</v>
+        <v>-0.3895844459057756</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.5361329195487343</v>
+        <v>-0.5336509984588034</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.6859034539708162</v>
+        <v>-0.6592644994789794</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.6218277988751666</v>
+        <v>-0.5964201327994729</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.6579491176175409</v>
+        <v>-0.6323026916613514</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.3777240406713318</v>
+        <v>-0.3544305782628996</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.4489678320162938</v>
+        <v>-0.4527088645362625</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.4146860428267445</v>
+        <v>-0.4462001486434488</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.1744</t>
+          <t>X &gt; -0.1742</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3826</v>
+        <v>3837</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.462161146449958</v>
+        <v>-0.4581637729389314</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.2359270324048524</v>
+        <v>-0.2351439373226469</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.460290240174956</v>
+        <v>-0.4589603702910097</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.5506003981329499</v>
+        <v>-0.5489806528278152</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.4229692086037034</v>
+        <v>-0.4262151910224929</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.3982941959980266</v>
+        <v>-0.3993542035931554</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.5732212863645785</v>
+        <v>-0.5759899358270175</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.8174013463931971</v>
+        <v>-0.8195853106697228</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.8642013203148551</v>
+        <v>-0.8684578391146331</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.7860924080996838</v>
+        <v>-0.7929714993102692</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.8457755064392529</v>
+        <v>-0.8525369663725257</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.5879336211957593</v>
+        <v>-0.5976230292160238</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.6538533187138071</v>
+        <v>-0.6656550445761482</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.5964404953600777</v>
+        <v>-0.6105543125813711</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.1571</t>
+          <t>X &gt; -0.157</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3770</v>
+        <v>3781</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.5115795251153656</v>
+        <v>-0.5069489361152364</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.4167980516785619</v>
+        <v>-0.4154613329270944</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.6122371687605224</v>
+        <v>-0.6104446198765316</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.7323097404262384</v>
+        <v>-0.7301315144892087</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.5419344777970423</v>
+        <v>-0.5456004413665454</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.4948640470396555</v>
+        <v>-0.496013446813464</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.7505824285877409</v>
+        <v>-0.7535867501274964</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.8855717048376945</v>
+        <v>-0.8883181965899638</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.9586694186620761</v>
+        <v>-0.9637979961302747</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.7873238653286805</v>
+        <v>-0.7957710234599489</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.9773754291073473</v>
+        <v>-0.985332949459206</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.7162508373105396</v>
+        <v>-0.727541653802767</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.7239078385919342</v>
+        <v>-0.7378822010500414</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.6424886844224815</v>
+        <v>-0.6592250285468424</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.1398</t>
+          <t>X &gt; -0.1397</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3703</v>
+        <v>3713</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.4895274406527577</v>
+        <v>-0.4972293772219274</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.4447266188875432</v>
+        <v>-0.4557050174253874</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.6635024798125642</v>
+        <v>-0.6739227093135014</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.7881054075873664</v>
+        <v>-0.7981850274356432</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.4768344695846878</v>
+        <v>-0.4670260658003187</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.3534248421462465</v>
+        <v>-0.3408733430221531</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.6661017407530849</v>
+        <v>-0.655767944845401</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.8489923924916383</v>
+        <v>-0.8381969691105269</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.8953304415444094</v>
+        <v>-0.8874713807325918</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.813413523116715</v>
+        <v>-0.8088922142897559</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.9492407390344795</v>
+        <v>-0.9443695820883562</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.7649798055014614</v>
+        <v>-0.7636669988595841</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.8461820662002566</v>
+        <v>-0.8477470570254155</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.713396851934526</v>
+        <v>-0.7183751599713872</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.1226</t>
+          <t>X &gt; -0.1225</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3610</v>
+        <v>3620</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.6178191494965333</v>
+        <v>-0.597092281809644</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.6409701523116027</v>
+        <v>-0.6516589540957014</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.8000466649397922</v>
+        <v>-0.8103538055456454</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.87598538133944</v>
+        <v>-0.8860684769775773</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.4876430850338025</v>
+        <v>-0.5063534199740829</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.4516269064675882</v>
+        <v>-0.4666605035316422</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.7978396331703692</v>
+        <v>-0.8156797176604016</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.028767670039429</v>
+        <v>-1.0460412748306</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.019453678506544</v>
+        <v>-1.040516213883521</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.9412621064442277</v>
+        <v>-0.9664152826333492</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.047674036434934</v>
+        <v>-1.072572158202497</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.9149522320956791</v>
+        <v>-0.9439767999629112</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.070546005758587</v>
+        <v>-1.102967122707611</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.801713355061807</v>
+        <v>-0.8386186526721175</v>
       </c>
     </row>
     <row r="17">
@@ -2786,985 +2786,985 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3475</v>
+        <v>3486</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.7320628195251828</v>
+        <v>-0.7238871892768017</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.8658331244585256</v>
+        <v>-0.8628715286820636</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.159277409672782</v>
+        <v>-1.155599960982649</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.128527848265584</v>
+        <v>-1.1248774109186</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.7904603059202557</v>
+        <v>-0.7977510825010796</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.7646612181134955</v>
+        <v>-0.7670810070377314</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.063664253235459</v>
+        <v>-1.069991168558573</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.141873773208857</v>
+        <v>-1.148205294520395</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.158600909870117</v>
+        <v>-1.169723337620418</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.9294591358815154</v>
+        <v>-0.9465698712719615</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.032052535456174</v>
+        <v>-1.048957860611566</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.8955078911632839</v>
+        <v>-0.9176500455213912</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.069589970322816</v>
+        <v>-1.096235210346343</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.9429676646335423</v>
+        <v>-0.974727412890573</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.08808</t>
+          <t>X &gt; -0.08806</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3347</v>
+        <v>3358</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.9035350781533964</v>
+        <v>-0.8933808845132063</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.010827934851527</v>
+        <v>-1.007235497579927</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.300453019967279</v>
+        <v>-1.296169077045576</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.24374994355545</v>
+        <v>-1.239565659993218</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.7233050215554329</v>
+        <v>-0.7329378846406627</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.7972658256323228</v>
+        <v>-0.8005821180161945</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.0448264239973</v>
+        <v>-1.053281884994625</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.9888895658981198</v>
+        <v>-0.9978361136646825</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.9442152625982843</v>
+        <v>-0.9592505131032212</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.7334757152142686</v>
+        <v>-0.7556615396573747</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.6231539576150809</v>
+        <v>-0.6458462493240305</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.542301696258626</v>
+        <v>-0.5711559432933413</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.9159506782596836</v>
+        <v>-0.9497804628057622</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.8528278852111981</v>
+        <v>-0.8926497616918923</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.07082</t>
+          <t>X &gt; -0.07083</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3165</v>
+        <v>3174</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.032553310131334</v>
+        <v>-1.019681953534608</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.021235981865892</v>
+        <v>-1.017331596797391</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.336274894616608</v>
+        <v>-1.331610885798675</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.283846599873584</v>
+        <v>-1.27925340990668</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.9712064334609352</v>
+        <v>-0.9664045648556936</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.7998960659752257</v>
+        <v>-0.7709666301243772</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.025275508525681</v>
+        <v>-1.003328899843659</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.9393145090645589</v>
+        <v>-0.91770539177773</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.8254670036371081</v>
+        <v>-0.8118084224505182</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.6799977097037413</v>
+        <v>-0.6745529065016385</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.4568641943103913</v>
+        <v>-0.452100233605762</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.404864292410366</v>
+        <v>-0.4078777856827003</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.6810398764383621</v>
+        <v>-0.6910045335242216</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.6587893201053845</v>
+        <v>-0.6764237472422963</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -0.05356</t>
+          <t>X &gt; -0.0536</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2968</v>
+        <v>2977</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.9535578566504981</v>
+        <v>-0.9382054703719334</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.002780431187162</v>
+        <v>-0.9986084148939511</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.547672970899406</v>
+        <v>-1.541913109870258</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.668476321754106</v>
+        <v>-1.662131139700605</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.299507810333665</v>
+        <v>-1.296492466949438</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.9685316301609532</v>
+        <v>-0.9387656082540801</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.30412298698743</v>
+        <v>-1.28305613418496</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.9462494144794462</v>
+        <v>-0.926444641657028</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.9553637292676811</v>
+        <v>-0.9452503659221847</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.5420742613584579</v>
+        <v>-0.543251433294671</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.2568669142054034</v>
+        <v>-0.258996697916146</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.001610621079649377</v>
+        <v>-0.01422168922918843</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.4365041634368581</v>
+        <v>-0.4577031052020857</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.4613701932844734</v>
+        <v>-0.4921502401466142</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; -0.0363</t>
+          <t>X &gt; -0.03637</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2663</v>
+        <v>2673</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.6858524553660672</v>
+        <v>-0.6858378114841557</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.8934489249449769</v>
+        <v>-0.9089313681433993</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.230885484401128</v>
+        <v>-1.245596197910452</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.492552520511772</v>
+        <v>-1.505856983121248</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.9076672327238953</v>
+        <v>-0.9314031837771068</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.5354148803632413</v>
+        <v>-0.5266090902419052</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.9369558954317085</v>
+        <v>-0.9402327177550376</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.6720105570707986</v>
+        <v>-0.6768030556483779</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.525167626511795</v>
+        <v>-0.5067468028459459</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.1922273461932491</v>
+        <v>-0.1895106391203427</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.07413976880159368</v>
+        <v>0.07562073168428185</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.3172755514650589</v>
+        <v>0.3043447242633945</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.1942612468928289</v>
+        <v>-0.2193056424824604</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.3603932435095416</v>
+        <v>-0.3981385498224554</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; -0.01904</t>
+          <t>X &gt; -0.01915</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2295</v>
+        <v>2304</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.026291627581678</v>
+        <v>-0.9543642017236351</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.161142505708476</v>
+        <v>-1.131767076925669</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.729600386338461</v>
+        <v>-1.632355618080723</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.686218490687565</v>
+        <v>-1.566143289855972</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.269232316471054</v>
+        <v>-1.21002836173114</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.9284366628672416</v>
+        <v>-0.8273959985482691</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.380797270949493</v>
+        <v>-1.298040731412918</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.563945238084109</v>
+        <v>-1.524022507038104</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.166846786931579</v>
+        <v>-1.147475570285117</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.253806262573811</v>
+        <v>-1.253738167426455</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.7819162817645662</v>
+        <v>-0.8264952997058614</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.5492433846462319</v>
+        <v>-0.5947174512298545</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.8580347765200145</v>
+        <v>-0.9030698222381233</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.9565724670661098</v>
+        <v>-1.044649960222756</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; -0.001784</t>
+          <t>X &gt; -0.00192</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1916</v>
+        <v>1925</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.050858828246263</v>
+        <v>-1.010628887968679</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.7899700383147632</v>
+        <v>-0.7565067062145872</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.600758063735434</v>
+        <v>-1.484956504982797</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.52253500023027</v>
+        <v>-1.431197750980253</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.0207829516619</v>
+        <v>-0.856754692395306</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.243429722858849</v>
+        <v>-1.126224416030645</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.588150482541039</v>
+        <v>-1.470362153563556</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.923536439665476</v>
+        <v>-1.85671183121989</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.904755032184283</v>
+        <v>-1.866039900638278</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.945660510797673</v>
+        <v>-1.934922492862412</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.601057561015487</v>
+        <v>-1.619582420917986</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.642454232726173</v>
+        <v>-1.665311787449184</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.460316034074374</v>
+        <v>-1.437093090636395</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.571119840179129</v>
+        <v>-1.655580696153493</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.01547</t>
+          <t>X &gt; 0.01531</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1498</v>
+        <v>1507</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-2.015490498619457</v>
+        <v>-1.783559645230447</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.100080847002431</v>
+        <v>-1.152112439454598</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-2.093256487076623</v>
+        <v>-1.973799385130029</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.697073896679754</v>
+        <v>-1.610617377328175</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.304512385945657</v>
+        <v>-1.20400789213452</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.339585164821216</v>
+        <v>-1.29328838782456</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.756742332598016</v>
+        <v>-1.716490685212193</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-2.423279061491144</v>
+        <v>-2.41263680201007</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-2.781848667228964</v>
+        <v>-2.781394414464721</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-2.265303764237537</v>
+        <v>-2.2780829820083</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.234298766548427</v>
+        <v>-2.216795426890116</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.097233516702545</v>
+        <v>-2.092271688861651</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-2.281137983536077</v>
+        <v>-2.28835861343476</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-2.219374576487247</v>
+        <v>-2.304741754073682</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.03273</t>
+          <t>X &gt; 0.03254</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1153</v>
+        <v>1162</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.920087730275512</v>
+        <v>-1.697451431388266</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.6839916835636615</v>
+        <v>-0.5830149374400975</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.596450730096102</v>
+        <v>-1.359349092016494</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.72506941739644</v>
+        <v>-1.526954177897579</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.7102959851599451</v>
+        <v>-0.5116280495969292</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.275734725153853</v>
+        <v>-1.137180362437363</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-2.136976577086109</v>
+        <v>-2.011734623531403</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-2.690326497835748</v>
+        <v>-2.604398254874326</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-3.137786187697529</v>
+        <v>-3.071663462978421</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-2.559811692013461</v>
+        <v>-2.4324972073046</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.939685486820267</v>
+        <v>-1.948169496493009</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.858272477741508</v>
+        <v>-1.803944239334655</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-2.751237634025195</v>
+        <v>-2.71545328465924</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-3.172596970728996</v>
+        <v>-3.240935100785002</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.04999</t>
+          <t>X &gt; 0.04976</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>882</v>
+        <v>890</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.973587958381032</v>
+        <v>-1.672122998071345</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.2025869037560142</v>
+        <v>-0.06644327245894033</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.161056146459195</v>
+        <v>-1.071573370921932</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.5798727165123196</v>
+        <v>-0.4937609982402904</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1.362108305363797</v>
+        <v>1.319527284416431</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.257090382024785</v>
+        <v>-0.364852270521645</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.243717314007981</v>
+        <v>-1.26347605164738</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.936265100973976</v>
+        <v>-2.066387463716111</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-3.688340831341165</v>
+        <v>-3.788753331279878</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-3.012839780925589</v>
+        <v>-3.151907754791495</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-2.705622968492897</v>
+        <v>-2.794250449518593</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-2.723779519719137</v>
+        <v>-2.7360837121537</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-3.536334917392324</v>
+        <v>-3.58067984096472</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-3.477136248134094</v>
+        <v>-3.668713630634748</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.06725</t>
+          <t>X &gt; 0.06699</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>682</v>
+        <v>689</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-2.1170150116115</v>
+        <v>-2.07658581332629</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.5258721381542202</v>
+        <v>-0.4805721470370514</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.648445560754965</v>
+        <v>-1.307836146912457</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.7904183793208972</v>
+        <v>-0.5999174236168514</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.2724565508439625</v>
+        <v>0.5805255127590527</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-2.050256755765488</v>
+        <v>-1.819983290870056</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-3.445010783153933</v>
+        <v>-3.255452699125406</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-3.912079426940672</v>
+        <v>-3.721285459508749</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-5.137544844016574</v>
+        <v>-5.064498997527984</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-4.310972707104767</v>
+        <v>-4.291810887486648</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-3.126258871004339</v>
+        <v>-3.189710406140307</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-3.59898790266746</v>
+        <v>-3.566957311736232</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-3.063602037170668</v>
+        <v>-3.09128795237843</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-4.078940997404281</v>
+        <v>-4.438759781219368</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.08451</t>
+          <t>X &gt; 0.08422</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-3.208188757807079</v>
+        <v>-3.143023217292047</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-1.001193032689095</v>
+        <v>-0.9287319480175285</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-1.759600781080501</v>
+        <v>-1.684133589135122</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-1.629375637492139</v>
+        <v>-1.37341772151899</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.1676651905878259</v>
+        <v>0.1264832279450019</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-2.779382070043646</v>
+        <v>-2.580852856087446</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-4.864092429309814</v>
+        <v>-4.815421988791172</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-4.785706527642006</v>
+        <v>-4.737776488304945</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-5.937597775073876</v>
+        <v>-5.861705619180867</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-5.787019800415159</v>
+        <v>-5.779737098546576</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-4.25764573231821</v>
+        <v>-4.17228334318412</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-4.676636319871342</v>
+        <v>-4.657594866688797</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-4.2697653223969</v>
+        <v>-4.328115112093201</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-4.865349025599819</v>
+        <v>-5.347186192106811</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.1018</t>
+          <t>X &gt; 0.1014</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-2.952614143741897</v>
+        <v>-2.863053001357571</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-1.261913444352899</v>
+        <v>-1.152112439454598</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-3.071779168730572</v>
+        <v>-2.957615133651665</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-1.526459685519576</v>
+        <v>-1.65126050420168</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.4138058423888609</v>
+        <v>-0.2581567039771286</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-2.71077143539528</v>
+        <v>-2.573606479275853</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-4.682274247491634</v>
+        <v>-4.516615509677777</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-4.677644778070821</v>
+        <v>-4.511860034767011</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-5.210325047801149</v>
+        <v>-5.254714996844982</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-5.942040534438341</v>
+        <v>-6.078543577659964</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-3.658309931301154</v>
+        <v>-3.929742848725468</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-4.924153548373162</v>
+        <v>-5.28334081724293</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-4.2697653223969</v>
+        <v>-4.73732227321851</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-4.873669403958068</v>
+        <v>-5.664747999438447</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.119</t>
+          <t>X &gt; 0.1187</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-2.02220043420408</v>
+        <v>-2.3581361409964</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.8810929492862485</v>
+        <v>-1.205750916121865</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.9700539364877727</v>
+        <v>-1.295537536655416</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1.606654387528714</v>
+        <v>1.265957446808507</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>1.374175231986541</v>
+        <v>1.08065967363774</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-1.998175509020577</v>
+        <v>-2.293971220917193</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-4.529369048714884</v>
+        <v>-4.78623825239189</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-4.690627294948101</v>
+        <v>-4.948119644994073</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-3.528367861256804</v>
+        <v>-3.769286783006251</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-5.13999844535801</v>
+        <v>-5.504969467164699</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-3.649560387006581</v>
+        <v>-4.189353075795019</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-3.144147096949453</v>
+        <v>-3.827234970648973</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-3.090346186321426</v>
+        <v>-3.918441529431639</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-3.31939199101096</v>
+        <v>-4.581250770759738</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.1363</t>
+          <t>X &gt; 0.1359</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.8548997703717518</v>
+        <v>-0.8840955647243831</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.4335655382323225</v>
+        <v>-0.4347523246769782</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.3911752721345891</v>
+        <v>0.3910218821302678</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.6981117793989995</v>
+        <v>-0.6986062717770025</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1.202623057749207</v>
+        <v>1.251168977514979</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-2.158539497981565</v>
+        <v>-2.134582089031952</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-4.682274247491634</v>
+        <v>-4.634262568501313</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-4.742838826237723</v>
+        <v>-4.693591263844006</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-1.958292527475948</v>
+        <v>-1.885035417696251</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-4.223509150253456</v>
+        <v>-4.334880258673834</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-2.166584346653494</v>
+        <v>-2.506500381006667</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-2.321101829459749</v>
+        <v>-2.854837708682432</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.8655937364071349</v>
+        <v>-1.62397937508365</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.006553216586787869</v>
+        <v>-1.374934513068283</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.1535</t>
+          <t>X &gt; 0.1531</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-2.224505774124097</v>
+        <v>-2.256304718288007</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-2.297230328726378</v>
+        <v>-1.809024950651974</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.8977418762621667</v>
+        <v>1.350536553419111</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.002325994209499527</v>
+        <v>0.4651921682378486</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>1.515318492395856</v>
+        <v>2.006399880077815</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.2742309835694101</v>
+        <v>0.7563427593028251</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-1.348940914158298</v>
+        <v>-0.8271559695165465</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-4.380112122047606</v>
+        <v>-3.831059795889736</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-1.364171201647302</v>
+        <v>-0.8223471258387178</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-4.265372049259206</v>
+        <v>-3.676632559445572</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-1.110305827133466</v>
+        <v>-0.835087727793848</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-2.622319427355464</v>
+        <v>-2.299763630022866</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.9806146105657803</v>
+        <v>-0.6644647037948062</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.4664328303248269</v>
+        <v>-0.9230340549774141</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.1708</t>
+          <t>X &gt; 0.1704</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-4.535710551082303</v>
+        <v>-4.564906345434935</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-4.092102123598181</v>
+        <v>-4.093288910042837</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.3772844672573257</v>
+        <v>-0.377437857261647</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.9319908305182807</v>
+        <v>-0.9324853228962837</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.1004173699153483</v>
+        <v>-0.0518714501495765</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.1969566597197385</v>
+        <v>0.2209140686693516</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-1.942548220094373</v>
+        <v>-1.894536541104053</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-5.149342891278373</v>
+        <v>-5.100095328884656</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-3.155530527253205</v>
+        <v>-3.082273417473509</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-5.375312337281692</v>
+        <v>-5.275965011987118</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-1.78218638170155</v>
+        <v>-2.055447925276631</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-3.127118574173814</v>
+        <v>-3.367144201610373</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-3.547269427487223</v>
+        <v>-3.762302128174198</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-3.647204275344976</v>
+        <v>-4.883120279857458</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 0.1881</t>
+          <t>X &gt; 0.1876</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-4.817364628665196</v>
+        <v>-4.361963676738839</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-2.690232964719684</v>
+        <v>-2.241437058190989</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.2812660317177134</v>
+        <v>0.1426027312720848</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>1.718117990375326</v>
+        <v>1.198412698412696</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>1.179828437279632</v>
+        <v>1.635089483386693</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.5426230276623798</v>
+        <v>0.9819490762797045</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.4579126683962116</v>
+        <v>-0.004632938871687031</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-3.747473732399875</v>
+        <v>-3.248243477032808</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-3.808455888922651</v>
+        <v>-3.285216086169605</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-4.658374685252511</v>
+        <v>-4.109044666984587</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-2.059337525755694</v>
+        <v>-1.5354073367429</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-1.090379934148032</v>
+        <v>-0.551314673452076</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.3586280910432293</v>
+        <v>0.9053792518359458</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.3502156979825699</v>
+        <v>0.228498187925382</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.2053</t>
+          <t>X &gt; 0.2048</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-3.671392221010542</v>
+        <v>-3.700588015363174</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.5206735521696118</v>
+        <v>-0.5218603386142675</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>1.465507444027736</v>
+        <v>1.465354054023415</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>1.595732587616098</v>
+        <v>1.595238095238095</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-2.513985536908166</v>
+        <v>-2.465439617142394</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.1643408736793006</v>
+        <v>0.1882982826289137</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.0796305144131324</v>
+        <v>0.1276421934034531</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-7.530295272230759</v>
+        <v>-7.481047709837043</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-8.781753619229718</v>
+        <v>-8.708496509450022</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-9.631672415559578</v>
+        <v>-9.532325090265005</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-5.074468811915011</v>
+        <v>-4.974560775896336</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-1.468662088131111</v>
+        <v>-1.344965467102867</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.6983367509683305</v>
+        <v>-0.5496472031905029</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-1.663077291217988</v>
+        <v>-1.491078531651326</v>
       </c>
     </row>
   </sheetData>
@@ -3904,573 +3904,573 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.2952</t>
+          <t>X &lt; -0.2948</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>5.852417302798983</v>
+        <v>5.823221508446352</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-4.092102123598181</v>
+        <v>-4.093288910042837</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-5.67734969882941</v>
+        <v>-5.677503088833731</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>5.167161159044667</v>
+        <v>5.166666666666664</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1.057443034520404</v>
+        <v>1.105988954286175</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>4.92624563558406</v>
+        <v>4.950203044533673</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>4.841535276317892</v>
+        <v>4.889546955308212</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>5.564942823007335</v>
+        <v>5.614190385401052</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>5.503960666484559</v>
+        <v>5.577217776264256</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>1.08261329872613</v>
+        <v>1.181960624020704</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.8779121404659378</v>
+        <v>0.9778201764846131</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-1.468662088131111</v>
+        <v>-1.344965467102867</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-5.460241512873097</v>
+        <v>-5.311551965095269</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-7.615458243598944</v>
+        <v>-7.443459484032282</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.2779</t>
+          <t>X &lt; -0.2776</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>2.858889794708361</v>
+        <v>3.680364365589206</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-3.606665230394299</v>
+        <v>-3.617098433852362</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-3.030562828741573</v>
+        <v>-2.106074517405155</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>5.837526392516693</v>
+        <v>6.595238095238095</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>2.386615480197698</v>
+        <v>3.248846097143321</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>4.625737082648314</v>
+        <v>5.426393520724147</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>5.511900509789918</v>
+        <v>6.318118383879643</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>5.044831866003179</v>
+        <v>5.8522856234963</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>6.925597282295932</v>
+        <v>7.720074919121402</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>5.104804699558308</v>
+        <v>5.94386538592547</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>4.900103541298115</v>
+        <v>4.78734398600843</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>1.050986548022372</v>
+        <v>1.035986913849506</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-2.281785664514338</v>
+        <v>-2.216313869857174</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-3.997797587103335</v>
+        <v>-2.919649960222756</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.2607</t>
+          <t>X &lt; -0.2603</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>135</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>3.074639525021205</v>
+        <v>3.045443730668573</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1.463453431957376</v>
+        <v>1.46226664551272</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1.809422787943078</v>
+        <v>1.809269397938756</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>11.56927756116107</v>
+        <v>11.56878306878306</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>5.105062082139447</v>
+        <v>5.153608001905219</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>8.365399074737496</v>
+        <v>8.389356483687109</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>9.021429456212076</v>
+        <v>9.069441135202396</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>10.03584229390682</v>
+        <v>10.08508985630053</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>13.67856384108774</v>
+        <v>13.75182095086743</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>12.08790430401714</v>
+        <v>12.18725162931172</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>10.40172166427546</v>
+        <v>10.50162970029413</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>5.250914631445603</v>
+        <v>5.374611252473848</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>3.349282296650713</v>
+        <v>3.497971844428541</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>2.834277206136498</v>
+        <v>3.006275965703161</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.2434</t>
+          <t>X &lt; -0.2431</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>165</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>6.913023363405046</v>
+        <v>6.883827569052414</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>2.877594846098788</v>
+        <v>2.876408059654132</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>4.907065885586178</v>
+        <v>4.906912495581857</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>12.3100183019018</v>
+        <v>12.3095238095238</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>6.317183294260651</v>
+        <v>6.365729214026423</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>7.826678536016964</v>
+        <v>7.850635944966577</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>9.560149994932615</v>
+        <v>9.608161673922936</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>12.72944498750952</v>
+        <v>12.77869254990323</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>15.69876586128976</v>
+        <v>15.77202297106945</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>14.24278645889929</v>
+        <v>14.34213378419386</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>11.61384287639669</v>
+        <v>11.71375091241536</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>8.011857392388372</v>
+        <v>8.135554013416616</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>6.985645933014347</v>
+        <v>7.134335480792174</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>6.60532097718027</v>
+        <v>6.777319736746932</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.2261</t>
+          <t>X &lt; -0.2259</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>4.805516130269673</v>
+        <v>4.989888175113009</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1.184279785949556</v>
+        <v>1.40671108995717</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2.29704608963673</v>
+        <v>2.512973101642451</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>7.954909424179867</v>
+        <v>8.142857142857139</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>4.401544494199747</v>
+        <v>4.653608001905219</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>5.703943649462971</v>
+        <v>5.926393520724147</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>9.136821229895297</v>
+        <v>9.365737431498687</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>11.18231540017891</v>
+        <v>11.39990467111534</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>15.1414337461687</v>
+        <v>15.36293206197855</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>13.2864898242107</v>
+        <v>13.53910348116356</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>11.5742509775083</v>
+        <v>11.83496303362747</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>7.588528627351053</v>
+        <v>7.893129770992367</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>6.665865211223576</v>
+        <v>6.997971844428541</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>6.389088298636047</v>
+        <v>6.747016706443908</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.2089</t>
+          <t>X &lt; -0.2086</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>238</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>6.762781448457247</v>
+        <v>6.733585654104616</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>3.050755019258958</v>
+        <v>3.049568232814302</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>4.33665590341149</v>
+        <v>4.336502513407169</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>8.248393652041862</v>
+        <v>8.247899159663859</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>5.609263762811715</v>
+        <v>5.657809682577486</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>6.746973926900587</v>
+        <v>6.7709313358502</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>9.603440038222658</v>
+        <v>9.651451717212979</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>11.23721173057036</v>
+        <v>11.28645929296408</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>14.53757411186271</v>
+        <v>14.61083122164241</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>12.42715111385219</v>
+        <v>12.52649843914676</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>11.8022818883651</v>
+        <v>11.90218992438378</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>9.315651637359075</v>
+        <v>9.439348258387319</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>9.315668851272562</v>
+        <v>9.46435839905039</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>7.440564165364634</v>
+        <v>7.612562924931296</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.1916</t>
+          <t>X &lt; -0.1914</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>5.733369683751363</v>
+        <v>5.940592400465128</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1.26504073354468</v>
+        <v>1.540513906858578</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>4.441697920218211</v>
+        <v>4.667902679107243</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>6.714780206663718</v>
+        <v>6.910462776659955</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>4.747919224996586</v>
+        <v>5.012762931482683</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>5.759578968917388</v>
+        <v>5.637661126357948</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>7.460582895365512</v>
+        <v>7.337568417414175</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>9.136371394435919</v>
+        <v>8.984411713368864</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>11.57538923791313</v>
+        <v>11.0601151605701</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>10.72547044158327</v>
+        <v>10.23628657975512</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>11.2350549976088</v>
+        <v>10.7363714843317</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>7.340861721392692</v>
+        <v>6.921298785076878</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>8.349282296650713</v>
+        <v>8.286704238794748</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>7.503589375448669</v>
+        <v>7.831523748697428</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.1744</t>
+          <t>X &lt; -0.1742</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>339</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>5.336193114008424</v>
+        <v>5.306997319655792</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>4.01999227168205</v>
+        <v>4.018805485237394</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>5.985102892826717</v>
+        <v>5.984949502822396</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>7.295269039364939</v>
+        <v>7.294774546986936</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>5.872023734056853</v>
+        <v>5.920569653822625</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>5.874412512954471</v>
+        <v>5.898369921904084</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>8.149584159588009</v>
+        <v>8.19759583857833</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>10.63236802317589</v>
+        <v>10.68161558556961</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>11.45634161886551</v>
+        <v>11.5295987286452</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>10.60642282253565</v>
+        <v>10.70577014783022</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>11.28667741648785</v>
+        <v>11.38658545250652</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>8.371203061468542</v>
+        <v>8.494899682496786</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>9.130993211104979</v>
+        <v>9.279682758882807</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>8.176787858381665</v>
+        <v>8.348786617948328</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.1571</t>
+          <t>X &lt; -0.157</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>395</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>4.987438399845388</v>
+        <v>4.958242605492757</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>5.148404205515746</v>
+        <v>5.14721741907109</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>6.525784719494887</v>
+        <v>6.525631329490565</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>7.921832647893368</v>
+        <v>7.921338155515365</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>6.117720309987554</v>
+        <v>6.166266229753326</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>5.908765225698588</v>
+        <v>5.932722634648201</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>8.608864993014699</v>
+        <v>8.656876672005019</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>9.660783691000113</v>
+        <v>9.710031253393829</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>10.61245976232543</v>
+        <v>10.68571687210513</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>9.003047295109496</v>
+        <v>9.10239462040407</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>10.82366259254552</v>
+        <v>10.92357062856419</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>8.326395175280574</v>
+        <v>8.450091796308818</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>8.412573435891218</v>
+        <v>8.561262983669046</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>7.372486301307625</v>
+        <v>7.544485060874287</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.1398</t>
+          <t>X &lt; -0.1397</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>4.012590462972142</v>
+        <v>4.077361177272842</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>4.565906534410473</v>
+        <v>4.654011305939889</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>5.902736881257177</v>
+        <v>5.988135088683492</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>7.115213107096608</v>
+        <v>7.197932736809619</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>4.628871605948973</v>
+        <v>4.548856382034813</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>3.843994553332976</v>
+        <v>3.741728293942288</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>6.57313700791962</v>
+        <v>6.488847582686596</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>7.837670095734616</v>
+        <v>7.750876593361568</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>8.426038588562484</v>
+        <v>8.361852148371632</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>7.792570008682844</v>
+        <v>7.754006288938939</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>8.886570149123955</v>
+        <v>8.845762169696599</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>7.405796786327755</v>
+        <v>7.392049857385452</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>8.06789701526543</v>
+        <v>8.076805537733073</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>6.778481150340454</v>
+        <v>6.813971350072421</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.1226</t>
+          <t>X &lt; -0.1225</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>4.095660546042225</v>
+        <v>3.964708318997914</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>5.006996975500911</v>
+        <v>5.079372960460759</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>5.693306671826953</v>
+        <v>5.764771662793542</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>6.364072355955862</v>
+        <v>6.434224049331959</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>3.843800820878187</v>
+        <v>3.966557642192988</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>3.780814490152913</v>
+        <v>3.87963093079609</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>6.218626653409267</v>
+        <v>6.336960453081417</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>7.553359811424336</v>
+        <v>7.669688843777216</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>7.672557835081733</v>
+        <v>7.812572349748329</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>7.182999399112234</v>
+        <v>7.348455999149174</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>7.879199141752949</v>
+        <v>8.043596127152654</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>7.012676393207364</v>
+        <v>7.202482288977976</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>8.033966981335411</v>
+        <v>8.246173283277464</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>6.097540469399775</v>
+        <v>6.336944763997863</v>
       </c>
     </row>
     <row r="17">
@@ -4483,982 +4483,982 @@
         <v>690</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>3.750968027436663</v>
+        <v>3.721772233084032</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>5.038332659010514</v>
+        <v>5.037145872565858</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>6.237764172806202</v>
+        <v>6.23761078280188</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>6.223061780162674</v>
+        <v>6.22256728778467</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>4.525351937211909</v>
+        <v>4.57389785697768</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>4.53287089438323</v>
+        <v>4.556828303332843</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>6.187290969899678</v>
+        <v>6.235302648889999</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>6.444860007272347</v>
+        <v>6.494107569666063</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>6.673732923213343</v>
+        <v>6.74699003299304</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>5.533959054419711</v>
+        <v>5.633306379714284</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>6.05389557731894</v>
+        <v>6.153803613337615</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>5.363636048514842</v>
+        <v>5.487332669543086</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>6.247833021288393</v>
+        <v>6.396522569066221</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>5.459075917891738</v>
+        <v>5.6310746774584</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.08808</t>
+          <t>X &lt; -0.08806</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>818</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>3.753802795871522</v>
+        <v>3.724607001518891</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>4.709853866621863</v>
+        <v>4.708667080177207</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>5.659825758150447</v>
+        <v>5.659672368146126</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>5.545552124232699</v>
+        <v>5.545057631854696</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>3.41802051734728</v>
+        <v>3.466566437113052</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>3.837643935735414</v>
+        <v>3.861601344685027</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>4.975427463999807</v>
+        <v>5.023439142990128</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>4.63060820896613</v>
+        <v>4.679855771359847</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>4.569626052443354</v>
+        <v>4.64288316222305</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>3.719707256113495</v>
+        <v>3.819054581408068</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>3.270507320347193</v>
+        <v>3.370415356365868</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>2.938137306443338</v>
+        <v>3.061833927471582</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>4.473976673178832</v>
+        <v>4.62266622095666</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>4.088465379640077</v>
+        <v>4.260464139206739</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.07082</t>
+          <t>X &lt; -0.07083</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>3.30750712315826</v>
+        <v>3.278311328805628</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>3.692329014126365</v>
+        <v>3.691142227681709</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>4.495162419790496</v>
+        <v>4.495009029786175</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>4.425786764975662</v>
+        <v>4.425292272597659</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>3.446720423797792</v>
+        <v>3.437041135637749</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>3.002436111774529</v>
+        <v>2.911423460843906</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>3.817725752508366</v>
+        <v>3.748970964432814</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>3.450657108721622</v>
+        <v>3.382938603251077</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>3.18967495219885</v>
+        <v>3.146365195711077</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>2.739756155868989</v>
+        <v>2.721738211702487</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>2.035054997608796</v>
+        <v>2.01859576815842</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.869433149964117</v>
+        <v>1.877161707120109</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.749282296650712</v>
+        <v>2.779408970177045</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.575017946877246</v>
+        <v>2.629252235386026</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -0.05356</t>
+          <t>X &lt; -0.0536</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2.398149857705846</v>
+        <v>2.368954063353215</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>2.87203465705236</v>
+        <v>2.870847870607705</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>4.061917150529176</v>
+        <v>4.061763760524855</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>4.442350801206786</v>
+        <v>4.441856308828783</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>3.53577994524462</v>
+        <v>3.535592989394793</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>2.795919821047718</v>
+        <v>2.724141644160348</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>3.71371572744571</v>
+        <v>3.664319583291849</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>2.745393950826895</v>
+        <v>2.698069808730018</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>2.85149617191481</v>
+        <v>2.827902870986058</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.834492997974259</v>
+        <v>1.837268618778239</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.128538706881983</v>
+        <v>1.132711157063675</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.4945793487945309</v>
+        <v>0.5236552088572566</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.578187893977365</v>
+        <v>1.629748324828874</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.553296977787852</v>
+        <v>1.628584679754994</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; -0.0363</t>
+          <t>X &lt; -0.03637</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.2424882247848</v>
+        <v>1.249036545039829</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.891940429593312</v>
+        <v>1.928001841786838</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>2.361530746965933</v>
+        <v>2.399200646552643</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>2.890692060767051</v>
+        <v>2.928286284573709</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.858222428114168</v>
+        <v>1.90676834787994</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.261290971960946</v>
+        <v>1.248083474150626</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>2.042093262495051</v>
+        <v>2.052364178005675</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.508446722569822</v>
+        <v>1.519997818154593</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.314308773770087</v>
+        <v>1.283424410614614</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.7307015619941595</v>
+        <v>0.7257302276705531</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.2596888191800346</v>
+        <v>0.2554553822635413</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.1719783014340166</v>
+        <v>-0.1521130766456906</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.739428768022222</v>
+        <v>0.7834009861451108</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.9651644182487544</v>
+        <v>1.032445848160478</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; -0.01904</t>
+          <t>X &lt; -0.01915</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1870</v>
+        <v>1872</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.279083969465646</v>
+        <v>1.196554841779687</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.670971515676094</v>
+        <v>1.640044423290497</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2.266997287161992</v>
+        <v>2.152973101642459</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.267283259166767</v>
+        <v>2.122857142857136</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.759257699456384</v>
+        <v>1.686941335238558</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.391740924608762</v>
+        <v>1.266393520724151</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>2.002217731117995</v>
+        <v>1.899070764832025</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2.176860317277779</v>
+        <v>2.126571337782018</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.741546609952856</v>
+        <v>1.716265395311879</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.854194658542781</v>
+        <v>1.852436814496905</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.275161949480463</v>
+        <v>1.328296366960807</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.9886844868625104</v>
+        <v>1.04361002712897</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.370672670982266</v>
+        <v>1.426428865250749</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.435980513722164</v>
+        <v>1.546162005589203</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; -0.001784</t>
+          <t>X &lt; -0.00192</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2249</v>
+        <v>2251</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.9115451668048919</v>
+        <v>0.8823493724522606</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.8768419757806996</v>
+        <v>0.8512787174516205</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.482944512063995</v>
+        <v>1.388804587230041</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.460403145004229</v>
+        <v>1.385650934431411</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.035759549931534</v>
+        <v>0.896401793479491</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.269102778441201</v>
+        <v>1.169187312298419</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.609410945927664</v>
+        <v>1.507644305112876</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.853769603163606</v>
+        <v>1.795691810804925</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1.88171585926866</v>
+        <v>1.847410997676995</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>1.921081189217141</v>
+        <v>1.910500376950708</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>1.627451618329118</v>
+        <v>1.64330376122286</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>1.661829770684442</v>
+        <v>1.68274361919476</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1.508464155254536</v>
+        <v>1.490867048691413</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>1.556342980225395</v>
+        <v>1.632400980100059</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.01547</t>
+          <t>X &lt; 0.01531</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2667</v>
+        <v>2669</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.146608277618235</v>
+        <v>1.022598455486843</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.7900527585567048</v>
+        <v>0.8225989404244558</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.276599545539</v>
+        <v>1.213907681081714</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.090749613520423</v>
+        <v>1.044726301735643</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.8728523443117382</v>
+        <v>0.8171594037743759</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.9288504991855504</v>
+        <v>0.9030290347428362</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.202283473647796</v>
+        <v>1.178821543648226</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.543570494548398</v>
+        <v>1.535418689806932</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.782550842712531</v>
+        <v>1.781406257939658</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>1.495061742670643</v>
+        <v>1.50262761135437</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>1.477837149839772</v>
+        <v>1.469693572549623</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>1.399729362937499</v>
+        <v>1.399681624230851</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>1.504512892826192</v>
+        <v>1.51295311783678</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1.430286038365814</v>
+        <v>1.483996848819338</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.03273</t>
+          <t>X &lt; 0.03254</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3012</v>
+        <v>3014</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.7486301768190771</v>
+        <v>0.6686961221328858</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.4141934363753137</v>
+        <v>0.3769097654538456</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.7003986162739011</v>
+        <v>0.6123108499868266</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.7826089296648533</v>
+        <v>0.7090823084200508</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.395277670862491</v>
+        <v>0.3191709158125065</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.644639164196569</v>
+        <v>0.5919564346314345</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>1.009727080088851</v>
+        <v>0.9617639215649163</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1.191958569545008</v>
+        <v>1.158182816810708</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1.396580662690226</v>
+        <v>1.371709802952381</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>1.177471959321849</v>
+        <v>1.129892082886563</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.9395702698531565</v>
+        <v>0.9446746677010509</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.9075473597914865</v>
+        <v>0.8891509911515243</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>1.251008724273561</v>
+        <v>1.242582126352254</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1.377142780874593</v>
+        <v>1.41125028308624</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.04999</t>
+          <t>X &lt; 0.04976</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3283</v>
+        <v>3286</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.5424811131909593</v>
+        <v>0.4649944289077936</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.1936121621161035</v>
+        <v>0.1568628810925574</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.3930291976364373</v>
+        <v>0.3702894343686296</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.2662226814638586</v>
+        <v>0.243525226671288</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.2554490222110317</v>
+        <v>-0.2457239142806316</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.210713652857919</v>
+        <v>0.2396337272227811</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.5079845044109561</v>
+        <v>0.513019545072936</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.666735062436608</v>
+        <v>0.7018487780412244</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.171033465753531</v>
+        <v>1.198392408377813</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.9912334632098379</v>
+        <v>1.029984940130134</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.9083720856380424</v>
+        <v>0.9343853504410902</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.9122902928212611</v>
+        <v>0.9186772162478434</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>1.131798288121928</v>
+        <v>1.149325662499734</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>1.083394431799576</v>
+        <v>1.142025836084812</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.06725</t>
+          <t>X &lt; 0.06699</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3483</v>
+        <v>3487</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.4265603372685689</v>
+        <v>0.4209719612153862</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.2345454408717274</v>
+        <v>0.2259330579205425</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.399913536645343</v>
+        <v>0.3341462060773637</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.2591773233085348</v>
+        <v>0.222135906451868</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.05200788082026264</v>
+        <v>-0.009528804047846506</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.5372611261176274</v>
+        <v>0.4922206529508202</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.8413986362960202</v>
+        <v>0.8036309632674303</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.9069142843817914</v>
+        <v>0.8689856902965687</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1.177846069052144</v>
+        <v>1.163046609515774</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>1.016988426899715</v>
+        <v>1.014182255153827</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.7835763872154615</v>
+        <v>0.7977137499598541</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.875376302418907</v>
+        <v>0.8722068704477977</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.7710451447701558</v>
+        <v>0.780081936171662</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.9393590321485661</v>
+        <v>1.016876184505279</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.08451</t>
+          <t>X &lt; 0.08422</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3620</v>
+        <v>3624</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.4959307169849367</v>
+        <v>0.4876879550910118</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.2779006335013534</v>
+        <v>0.2670962343863224</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.339381317901605</v>
+        <v>0.3286032612462009</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.3467999110972073</v>
+        <v>0.3084227910817532</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.1271371373270824</v>
+        <v>0.08202209882151834</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.5501037904938286</v>
+        <v>0.5200058555259162</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.8947550181074888</v>
+        <v>0.8876322263210525</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.8572851120356262</v>
+        <v>0.8503178942558378</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1.060393184243054</v>
+        <v>1.049209273331535</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>1.039203669681143</v>
+        <v>1.040206016995981</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.8068782020286918</v>
+        <v>0.796639350142506</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.8688806637762738</v>
+        <v>0.8705153198064863</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.8078458325623146</v>
+        <v>0.8221097754630193</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.8678356264352516</v>
+        <v>0.9490034614107898</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.1018</t>
+          <t>X &lt; 0.1014</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3746</v>
+        <v>3751</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.3427387377128568</v>
+        <v>0.3326086852086618</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.2644126645712817</v>
+        <v>0.2516486397844275</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.4171776643546679</v>
+        <v>0.4039885189736623</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.2687848530437265</v>
+        <v>0.282580620655601</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.1450620821394466</v>
+        <v>0.127012257224365</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.4304435804328506</v>
+        <v>0.4144222517696363</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.6805859446108258</v>
+        <v>0.6611073090931541</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.655300823693608</v>
+        <v>0.6358642133032646</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.7426915031865704</v>
+        <v>0.746851124811343</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.8271026588054582</v>
+        <v>0.8433644665164266</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.5690112175767581</v>
+        <v>0.6010791764085042</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.7101699358690894</v>
+        <v>0.7543074954794449</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.6370559218509229</v>
+        <v>0.694133891336854</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.6759255816877072</v>
+        <v>0.7718100948736577</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.119</t>
+          <t>X &lt; 0.1187</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3843</v>
+        <v>3847</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.1807302950953513</v>
+        <v>0.2100954289990256</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.1936121621161035</v>
+        <v>0.2213003617892468</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.150694691179126</v>
+        <v>0.1786029616735618</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.04271905083555083</v>
+        <v>-0.01438942183044389</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.02101018196245263</v>
+        <v>0.003193064145889934</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.2906316395956523</v>
+        <v>0.3161470875205197</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.5322901218191589</v>
+        <v>0.5551510277623137</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.5218329672023785</v>
+        <v>0.5448566565812172</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.4493158577413894</v>
+        <v>0.4704086974925659</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.5882078862879396</v>
+        <v>0.6218092718672779</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.4615707405179847</v>
+        <v>0.5102877089521556</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.4178848803830704</v>
+        <v>0.4792560375551105</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.4140754270176075</v>
+        <v>0.4886163350730328</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.4056190397734198</v>
+        <v>0.5185269741850078</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.1363</t>
+          <t>X &lt; 0.1359</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3924</v>
+        <v>3930</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.06231896437918039</v>
+        <v>0.06407026996465959</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.1434613462568137</v>
+        <v>0.1431392989881175</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.04238857816077513</v>
+        <v>0.04228038405808832</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.1355888457212657</v>
+        <v>0.1352429296591708</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.01850403733293149</v>
+        <v>0.01524801206008419</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.2534674333940927</v>
+        <v>0.2511776751172405</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.4374404748720977</v>
+        <v>0.4330475661189581</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.4175360896133498</v>
+        <v>0.4131160532291673</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.2687779083660331</v>
+        <v>0.2631861915846443</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.4127429040850927</v>
+        <v>0.4193780109042891</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.2844943452132753</v>
+        <v>0.3058503969633506</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.2933882977724807</v>
+        <v>0.3275143081235967</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.2045320418087115</v>
+        <v>0.2519784585216556</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.1244572944817222</v>
+        <v>0.210121032143654</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.1535</t>
+          <t>X &lt; 0.1531</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3972</v>
+        <v>3979</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.1176277806632342</v>
+        <v>0.1201486961550984</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.227335345010566</v>
+        <v>0.2038797193733473</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.02204384909465062</v>
+        <v>-0.0008113595104219939</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.09058781613966715</v>
+        <v>0.06752497940765068</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.0183568798273086</v>
+        <v>-0.006873442427782095</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.1032908126292398</v>
+        <v>0.07901453903365763</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.2083468236675259</v>
+        <v>0.1825964380215197</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.3335544930274708</v>
+        <v>0.3076838430099471</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.2110585999975925</v>
+        <v>0.1842172025407933</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.3564647618075938</v>
+        <v>0.328332705366428</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.2020907298684875</v>
+        <v>0.1885541938484678</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.2758514736489914</v>
+        <v>0.2608765682794782</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.1972178454926024</v>
+        <v>0.1813889298556788</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.1460149257292045</v>
+        <v>0.1682280660820084</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.1708</t>
+          <t>X &lt; 0.1704</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4021</v>
+        <v>4030</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.1728538107354822</v>
+        <v>0.1735389295033158</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.2616562490140808</v>
+        <v>0.2609911493337123</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.07888331546812566</v>
+        <v>0.07867466066250017</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.1233714912788244</v>
+        <v>0.1230551626591208</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.09513159554560957</v>
+        <v>0.09294942304907039</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.108172391883798</v>
+        <v>0.1069284390005194</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.2109199899648999</v>
+        <v>0.2084424104434461</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.3040732577899519</v>
+        <v>0.3012921835038469</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.256871771284338</v>
+        <v>0.2532666344692558</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.3404521538804204</v>
+        <v>0.3355834018378374</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.2103222111310501</v>
+        <v>0.2197882257921222</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.258741951555379</v>
+        <v>0.2671377075003107</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.2754200733231826</v>
+        <v>0.2828887384994871</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.2524613689115682</v>
+        <v>0.2978851927962651</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 0.1881</t>
+          <t>X &lt; 0.1876</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4058</v>
+        <v>4068</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.1351488183971128</v>
+        <v>0.1240464696486683</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.1830821515860919</v>
+        <v>0.171416972310098</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.07198616232754063</v>
+        <v>0.06065635734238839</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.04354829206896227</v>
+        <v>0.05678553912981954</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.05957400739147545</v>
+        <v>0.04691190183163485</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.09992750380601478</v>
+        <v>0.08782629795672392</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.127073845989301</v>
+        <v>0.1387435664680154</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.2148303370680864</v>
+        <v>0.2018192513804422</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.2413116738331098</v>
+        <v>0.2275281827740301</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.2666887014130523</v>
+        <v>0.2522665459965694</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.1989801391995414</v>
+        <v>0.1847542397193465</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.1733740366636312</v>
+        <v>0.1584860363486342</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.1366683523294512</v>
+        <v>0.121220799945867</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.1299711257831078</v>
+        <v>0.1137817015274791</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.2053</t>
+          <t>X &lt; 0.2048</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4081</v>
+        <v>4092</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.08381284098494035</v>
+        <v>0.08428525184870495</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.1224104588596688</v>
+        <v>0.1221107000936144</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.03414310943758636</v>
+        <v>0.0340552366656155</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.05547581025346915</v>
+        <v>0.0553388590931192</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.141736898765366</v>
+        <v>0.140196638823042</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.1101886184998975</v>
+        <v>0.1093203499924442</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.1367081399839023</v>
+        <v>0.1351933963681731</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.2702803042195541</v>
+        <v>0.2683770966887877</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.3207566947343352</v>
+        <v>0.318143192073741</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.341224944118693</v>
+        <v>0.3379316061635649</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.2482773286567976</v>
+        <v>0.2452194438838831</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.1740376074708578</v>
+        <v>0.1706090089015007</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.1596693618148493</v>
+        <v>0.1556801268619665</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.154287733694197</v>
+        <v>0.1497537543422496</v>
       </c>
     </row>
   </sheetData>
